--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_FY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SET_vs_CFA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WC_3bases" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External_MINT" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -963,7 +963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -972,7 +972,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DSO/DIO/DPO/CCC รายปี FY2568 — 2 ฐาน</t>
+          <t>วงจรเงินสดรายปี FY2568 — 3 ฐาน (DSO/DIO/DPO วัน)</t>
         </is>
       </c>
     </row>
@@ -980,20 +980,25 @@
       <c r="A2" s="3" t="inlineStr"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>SET basis (เทียบเว็บ)</t>
+          <t>CFA-broad (หน้างบดุล ครบ 10)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>CFA basis (ตามงบ)</t>
-        </is>
-      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>CFA-notes (การค้าล้วน)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>SET (เทียบเว็บ)</t>
+        </is>
+      </c>
       <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1018,27 +1023,32 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>DSO</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>DIO</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>DPO</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>DSO</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>DIO</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>DPO</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>CCC</t>
         </is>
       </c>
     </row>
@@ -1049,28 +1059,22 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H4" t="n">
         <v>25.7</v>
       </c>
-      <c r="C4" t="n">
+      <c r="I4" t="n">
         <v>17.8</v>
       </c>
-      <c r="D4" t="n">
+      <c r="J4" t="n">
         <v>12.7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="F4" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>28.9</v>
       </c>
     </row>
     <row r="5">
@@ -1080,28 +1084,22 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="H5" t="n">
         <v>14.7</v>
       </c>
-      <c r="C5" t="n">
+      <c r="I5" t="n">
         <v>23.7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="J5" t="n">
         <v>116.3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-78</v>
-      </c>
-      <c r="F5" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>114.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-74.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1111,28 +1109,25 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>135</v>
+      </c>
+      <c r="E6" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H6" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="C6" t="n">
+      <c r="I6" t="n">
         <v>9.1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="J6" t="n">
         <v>181.6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-104.1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>135</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-72.3</v>
       </c>
     </row>
     <row r="7">
@@ -1142,28 +1137,22 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="H7" t="n">
         <v>10.7</v>
       </c>
-      <c r="C7" t="n">
+      <c r="I7" t="n">
         <v>4.5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="J7" t="n">
         <v>99.7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-84.40000000000001</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-14.1</v>
       </c>
     </row>
     <row r="8">
@@ -1173,28 +1162,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
         <v>2.8</v>
       </c>
       <c r="D8" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J8" t="n">
         <v>52</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-38.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-45.4</v>
       </c>
     </row>
     <row r="9">
@@ -1204,28 +1187,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>32.9</v>
       </c>
       <c r="C9" t="n">
         <v>16.6</v>
       </c>
       <c r="D9" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26</v>
+      </c>
+      <c r="H9" t="n">
+        <v>36</v>
+      </c>
+      <c r="I9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J9" t="n">
         <v>143.6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-91.09999999999999</v>
-      </c>
-      <c r="F9" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>105.9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-56.4</v>
       </c>
     </row>
     <row r="10">
@@ -1235,28 +1215,22 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="H10" t="n">
         <v>15.5</v>
       </c>
-      <c r="C10" t="n">
+      <c r="I10" t="n">
         <v>10</v>
       </c>
-      <c r="D10" t="n">
+      <c r="J10" t="n">
         <v>168</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-142.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H10" t="n">
-        <v>133.3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-110.5</v>
       </c>
     </row>
     <row r="11">
@@ -1266,28 +1240,22 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="H11" t="n">
         <v>15.4</v>
       </c>
-      <c r="C11" t="n">
+      <c r="I11" t="n">
         <v>14.6</v>
       </c>
-      <c r="D11" t="n">
+      <c r="J11" t="n">
         <v>147.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-117.8</v>
-      </c>
-      <c r="F11" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="G11" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H11" t="n">
-        <v>129.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-100.5</v>
       </c>
     </row>
     <row r="12">
@@ -1297,28 +1265,22 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="H12" t="n">
         <v>14.4</v>
       </c>
-      <c r="C12" t="n">
+      <c r="I12" t="n">
         <v>14.2</v>
       </c>
-      <c r="D12" t="n">
+      <c r="J12" t="n">
         <v>71</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-42.4</v>
-      </c>
-      <c r="F12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H12" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-28.4</v>
       </c>
     </row>
     <row r="13">
@@ -1328,28 +1290,43 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="H13" t="n">
         <v>12.6</v>
       </c>
-      <c r="C13" t="n">
+      <c r="I13" t="n">
         <v>8.6</v>
       </c>
-      <c r="D13" t="n">
+      <c r="J13" t="n">
         <v>104.3</v>
       </c>
-      <c r="E13" t="n">
-        <v>-83.09999999999999</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H13" t="n">
-        <v>143.2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-122.8</v>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>หมายเหตุ: CFA-broad=ลูกหนี้/เจ้าหนี้หน้างบดุล (การค้า+หมุนเวียนอื่น) นิยามเดียวครบ 10 บริษัท</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CFA-notes=การค้าล้วนจากหมายเหตุ — เฉพาะ DUSIT/MINT ที่ดึงได้สะอาด (verify ตรงบริษัท); บริษัทอื่นหมายเหตุคนละ format ต้อง hand-code รายเจ้า</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SET=สูตร settrade (ปลายงวด, รายได้ดำเนินงาน, เจ้าหนี้กว้าง)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_FY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WC_3bases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SET_vs_CFA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External_MINT" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -963,7 +963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -972,7 +972,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>วงจรเงินสดรายปี FY2568 — 3 ฐาน (DSO/DIO/DPO วัน)</t>
+          <t>DSO/DIO/DPO/CCC รายปี FY2568 — 2 ฐาน</t>
         </is>
       </c>
     </row>
@@ -980,25 +980,20 @@
       <c r="A2" s="3" t="inlineStr"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>CFA-broad (หน้างบดุล ครบ 10)</t>
+          <t>SET basis (เทียบเว็บ)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>CFA-notes (การค้าล้วน)</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>CFA basis (ตามงบ)</t>
+        </is>
+      </c>
       <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>SET (เทียบเว็บ)</t>
-        </is>
-      </c>
+      <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1023,32 +1018,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>DSO</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>DIO</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>DPO</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>DSO</t>
-        </is>
-      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>DIO</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>DPO</t>
+          <t>CCC</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1049,28 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F4" t="n">
         <v>23.8</v>
       </c>
-      <c r="C4" t="n">
+      <c r="G4" t="n">
         <v>17.9</v>
       </c>
-      <c r="D4" t="n">
+      <c r="H4" t="n">
         <v>12.8</v>
       </c>
-      <c r="H4" t="n">
-        <v>25.7</v>
-      </c>
       <c r="I4" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12.7</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="5">
@@ -1084,22 +1080,28 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-78</v>
+      </c>
+      <c r="F5" t="n">
         <v>15.8</v>
       </c>
-      <c r="C5" t="n">
+      <c r="G5" t="n">
         <v>24.2</v>
       </c>
-      <c r="D5" t="n">
+      <c r="H5" t="n">
         <v>114.1</v>
       </c>
-      <c r="H5" t="n">
-        <v>14.7</v>
-      </c>
       <c r="I5" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>116.3</v>
+        <v>-74.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1109,25 +1111,28 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-104.1</v>
+      </c>
+      <c r="F6" t="n">
         <v>53.7</v>
       </c>
-      <c r="C6" t="n">
+      <c r="G6" t="n">
         <v>9</v>
       </c>
-      <c r="D6" t="n">
+      <c r="H6" t="n">
         <v>135</v>
       </c>
-      <c r="E6" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="H6" t="n">
-        <v>68.40000000000001</v>
-      </c>
       <c r="I6" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>181.6</v>
+        <v>-72.3</v>
       </c>
     </row>
     <row r="7">
@@ -1137,22 +1142,28 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.40000000000001</v>
+      </c>
+      <c r="F7" t="n">
         <v>10.5</v>
       </c>
-      <c r="C7" t="n">
+      <c r="G7" t="n">
         <v>4.7</v>
       </c>
-      <c r="D7" t="n">
+      <c r="H7" t="n">
         <v>29.3</v>
       </c>
-      <c r="H7" t="n">
-        <v>10.7</v>
-      </c>
       <c r="I7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>99.7</v>
+        <v>-14.1</v>
       </c>
     </row>
     <row r="8">
@@ -1162,22 +1173,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>10.7</v>
       </c>
       <c r="C8" t="n">
         <v>2.8</v>
       </c>
       <c r="D8" t="n">
+        <v>52</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-38.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H8" t="n">
         <v>60.2</v>
       </c>
-      <c r="H8" t="n">
-        <v>10.7</v>
-      </c>
       <c r="I8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>52</v>
+        <v>-45.4</v>
       </c>
     </row>
     <row r="9">
@@ -1187,25 +1204,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.9</v>
+        <v>36</v>
       </c>
       <c r="C9" t="n">
         <v>16.6</v>
       </c>
       <c r="D9" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-91.09999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H9" t="n">
         <v>105.9</v>
       </c>
-      <c r="E9" t="n">
-        <v>26</v>
-      </c>
-      <c r="H9" t="n">
-        <v>36</v>
-      </c>
       <c r="I9" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>143.6</v>
+        <v>-56.4</v>
       </c>
     </row>
     <row r="10">
@@ -1215,22 +1235,28 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>168</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-142.5</v>
+      </c>
+      <c r="F10" t="n">
         <v>13.8</v>
       </c>
-      <c r="C10" t="n">
+      <c r="G10" t="n">
         <v>8.9</v>
       </c>
-      <c r="D10" t="n">
+      <c r="H10" t="n">
         <v>133.3</v>
       </c>
-      <c r="H10" t="n">
-        <v>15.5</v>
-      </c>
       <c r="I10" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" t="n">
-        <v>168</v>
+        <v>-110.5</v>
       </c>
     </row>
     <row r="11">
@@ -1240,22 +1266,28 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-117.8</v>
+      </c>
+      <c r="F11" t="n">
         <v>14.4</v>
       </c>
-      <c r="C11" t="n">
+      <c r="G11" t="n">
         <v>14.9</v>
       </c>
-      <c r="D11" t="n">
+      <c r="H11" t="n">
         <v>129.7</v>
       </c>
-      <c r="H11" t="n">
-        <v>15.4</v>
-      </c>
       <c r="I11" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>147.9</v>
+        <v>-100.5</v>
       </c>
     </row>
     <row r="12">
@@ -1265,22 +1297,28 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>71</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-42.4</v>
+      </c>
+      <c r="F12" t="n">
         <v>15.5</v>
       </c>
-      <c r="C12" t="n">
+      <c r="G12" t="n">
         <v>13.9</v>
       </c>
-      <c r="D12" t="n">
+      <c r="H12" t="n">
         <v>57.7</v>
       </c>
-      <c r="H12" t="n">
-        <v>14.4</v>
-      </c>
       <c r="I12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>71</v>
+        <v>-28.4</v>
       </c>
     </row>
     <row r="13">
@@ -1290,43 +1328,28 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-83.09999999999999</v>
+      </c>
+      <c r="F13" t="n">
         <v>12.5</v>
       </c>
-      <c r="C13" t="n">
+      <c r="G13" t="n">
         <v>7.8</v>
       </c>
-      <c r="D13" t="n">
+      <c r="H13" t="n">
         <v>143.2</v>
       </c>
-      <c r="H13" t="n">
-        <v>12.6</v>
-      </c>
       <c r="I13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>104.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>หมายเหตุ: CFA-broad=ลูกหนี้/เจ้าหนี้หน้างบดุล (การค้า+หมุนเวียนอื่น) นิยามเดียวครบ 10 บริษัท</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CFA-notes=การค้าล้วนจากหมายเหตุ — เฉพาะ DUSIT/MINT ที่ดึงได้สะอาด (verify ตรงบริษัท); บริษัทอื่นหมายเหตุคนละ format ต้อง hand-code รายเจ้า</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SET=สูตร settrade (ปลายงวด, รายได้ดำเนินงาน, เจ้าหนี้กว้าง)</t>
-        </is>
+        <v>-122.8</v>
       </c>
     </row>
   </sheetData>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -1781,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U41"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1917,77 +1917,77 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>342.6841</t>
+          <t>161.4207</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>233.1898</t>
+          <t>155.453</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14.423</t>
+          <t>-48.4999</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>83.3637</t>
+          <t>145.4437</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>45.8098</t>
+          <t>39.3743</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>17.226</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>10218.2885</t>
+          <t>9453.5764</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6021.921</t>
+          <t>5272.2078</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.0421</t>
+          <t>-0.3005</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>-0.0051</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.0024</t>
+          <t>-0.0091</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>22.4082</t>
+          <t>78.529</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>17.7647</t>
+          <t>23.0728</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>12.5444</t>
+          <t>11.255</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>27.6284</t>
+          <t>90.3468</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2024,77 +2024,77 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>306.2049</t>
+          <t>143.6546</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>233.9883</t>
+          <t>150.5483</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-14.9731</t>
+          <t>-58.8896</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>80.9068</t>
+          <t>139.6406</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>45.7666</t>
+          <t>39.4588</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.0287</t>
+          <t>13.1074</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>10013.3875</t>
+          <t>9433.0526</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5951.8987</t>
+          <t>5225.8042</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.0489</t>
+          <t>-0.4099</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.0015</t>
+          <t>-0.0062</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-0.0025</t>
+          <t>-0.0112</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>24.4095</t>
+          <t>90.2953</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>17.8074</t>
+          <t>23.8256</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>11.6437</t>
+          <t>9.1676</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>30.5733</t>
+          <t>104.9533</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2131,77 +2131,77 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>321.6484</t>
+          <t>146.7678</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>236.6086</t>
+          <t>137.1574</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.092</t>
+          <t>-37.5533</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>89.8435</t>
+          <t>198.4087</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>45.9873</t>
+          <t>39.7016</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>27.6193</t>
+          <t>18.5136</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>9975.5818</t>
+          <t>9416.7265</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5943.4917</t>
+          <t>5220.5275</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.0189</t>
+          <t>-0.2559</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.0006</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.0072</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>24.4196</t>
+          <t>105.9515</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>17.8382</t>
+          <t>26.5489</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>10.8187</t>
+          <t>10.6051</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>31.439</t>
+          <t>121.8953</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2238,77 +2238,77 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>394.0262</t>
+          <t>148.0014</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>238.8158</t>
+          <t>160.4476</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.2873</t>
+          <t>-65.6804</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>90.5727</t>
+          <t>134.4474</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>46.0018</t>
+          <t>39.693</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.8516</t>
+          <t>14.1313</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10336.3165</t>
+          <t>10500.936</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5913.1293</t>
+          <t>6070.5678</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0083</t>
+          <t>-0.4438</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>-0.0066</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0006</t>
+          <t>-0.0116</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>21.0624</t>
+          <t>103.4542</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>17.7187</t>
+          <t>22.7623</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.6477</t>
+          <t>9.3592</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>27.1333</t>
+          <t>116.8573</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -2317,12 +2317,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CENTEL</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2337,77 +2337,77 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6695.756</t>
+          <t>173.164</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3390.386</t>
+          <t>161.7755</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>761.578</t>
+          <t>-49.9775</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1141.727</t>
+          <t>140.6628</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>834.687</t>
+          <t>39.4286</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3316.245</t>
+          <t>16.5148</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>60445.465</t>
+          <t>10401.72</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21712.54</t>
+          <t>6056.5105</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.1137</t>
+          <t>-0.2886</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0126</t>
+          <t>-0.0048</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0357</t>
+          <t>-0.0082</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>71.4927</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>23.0874</t>
+          <t>22.0087</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>102.7248</t>
+          <t>8.5246</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-63.8475</t>
+          <t>84.9768</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2424,12 +2424,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CENTEL</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2444,77 +2444,77 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5752.002</t>
+          <t>210.5764</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3359.448</t>
+          <t>179.2808</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>85.859</t>
+          <t>-35.1436</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>794.157</t>
+          <t>142.2383</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>818.407</t>
+          <t>39.9545</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3165.901</t>
+          <t>21.6809</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>61666.464</t>
+          <t>10389.057</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21693.156</t>
+          <t>6057.9512</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.0149</t>
+          <t>-0.1669</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>-0.0034</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-0.0058</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>15.3134</t>
+          <t>61.1275</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>22.3893</t>
+          <t>20.1468</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>87.7935</t>
+          <t>9.6938</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-50.0908</t>
+          <t>71.5805</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -2531,12 +2531,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CENTEL</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2551,77 +2551,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5773.648</t>
+          <t>255.1191</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3214.825</t>
+          <t>201.105</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>142.249</t>
+          <t>-25.2802</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>815.54</t>
+          <t>127.5039</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>749.963</t>
+          <t>39.4302</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3237.658</t>
+          <t>24.0261</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>61162.494</t>
+          <t>10415.012</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>21785.05</t>
+          <t>6077.899</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.0246</t>
+          <t>-0.0991</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.0023</t>
+          <t>-0.0024</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0065</t>
+          <t>-0.0042</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>12.8248</t>
+          <t>48.6367</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>22.4414</t>
+          <t>18.1582</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>91.6267</t>
+          <t>10.4548</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-56.3605</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2638,12 +2638,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CENTEL</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2658,77 +2658,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6829.5242</t>
+          <t>285.4392</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3391.9525</t>
+          <t>205.8116</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>974.4597</t>
+          <t>-1.8696</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>961.7198</t>
+          <t>137.6796</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>868.2159</t>
+          <t>40.0007</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3929.7783</t>
+          <t>24.9257</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>62728.0189</t>
+          <t>10456.5518</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>22614.472</t>
+          <t>6092.0379</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.1427</t>
+          <t>-0.0066</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.0157</t>
+          <t>-0.0002</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0439</t>
+          <t>-0.0003</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>11.9707</t>
+          <t>42.7357</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>21.9449</t>
+          <t>17.7532</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>97.2013</t>
+          <t>10.941</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-63.2856</t>
+          <t>49.5479</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -2737,12 +2737,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DUSIT</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2757,77 +2757,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2344.842</t>
+          <t>299.9658</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1355.983</t>
+          <t>219.8172</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>-13.2402</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1319.728</t>
+          <t>150.6209</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>131.598</t>
+          <t>40.9245</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2054.776</t>
+          <t>27.178</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>38766.715</t>
+          <t>10324.9897</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8750.937</t>
+          <t>6072.9541</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0154</t>
+          <t>-0.0441</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.0009</t>
+          <t>-0.0013</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.0041</t>
+          <t>-0.0022</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>47.3023</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>8.7059</t>
+          <t>16.5666</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>131.5497</t>
+          <t>10.6664</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-75.5416</t>
+          <t>49.1502</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -2837,19 +2837,19 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Q1_FS.xlsx</t>
+          <t>Q1_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DUSIT</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2864,77 +2864,77 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1709.084</t>
+          <t>289.3351</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1068.566</t>
+          <t>220.3972</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-324.379</t>
+          <t>-5.8747</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1178.171</t>
+          <t>143.8846</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>119.126</t>
+          <t>41.0955</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1621.867</t>
+          <t>24.9274</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>38218.557</t>
+          <t>10277.7562</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8416.257</t>
+          <t>6068.1023</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-0.1898</t>
+          <t>-0.0203</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.0084</t>
+          <t>-0.0006</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-0.0378</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>66.5002</t>
+          <t>46.3131</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>10.6759</t>
+          <t>16.9326</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>156.553</t>
+          <t>10.7569</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-79.3769</t>
+          <t>52.4888</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Q2_FS.xlsx</t>
+          <t>Q2_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DUSIT</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2971,77 +2971,77 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1751.875</t>
+          <t>307.8305</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1139.186</t>
+          <t>223.4946</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-422.865</t>
+          <t>5.997</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1153.552</t>
+          <t>149.6624</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>124.156</t>
+          <t>42.1349</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1869.877</t>
+          <t>27.8009</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>38640.11</t>
+          <t>10250.0415</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7941.989</t>
+          <t>6085.3197</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-0.2414</t>
+          <t>0.0195</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-0.011</t>
+          <t>0.0006</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-0.0517</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>61.2254</t>
+          <t>43.8656</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>9.8237</t>
+          <t>17.1306</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>140.9956</t>
+          <t>10.8526</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-69.9465</t>
+          <t>50.1435</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Q3_FS.xlsx</t>
+          <t>Q3_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DUSIT</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3078,77 +3078,77 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3118.196</t>
+          <t>291.3503</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1814.581</t>
+          <t>212.8181</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>240.259</t>
+          <t>-47.4522</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1482.137</t>
+          <t>122.0444</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>133.654</t>
+          <t>43.5387</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2068.782</t>
+          <t>27.1355</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>39722.107</t>
+          <t>10212.2954</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8261.867</t>
+          <t>6049.8416</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.0771</t>
+          <t>-0.1629</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.0061</t>
+          <t>-0.0046</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>-0.0078</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>38.882</t>
+          <t>42.8986</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6.5355</t>
+          <t>18.5181</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>99.8458</t>
+          <t>11.8743</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-54.4283</t>
+          <t>49.5423</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -3157,12 +3157,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3177,77 +3177,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2135.663</t>
+          <t>316.0598</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>836.589</t>
+          <t>220.3095</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>362.736</t>
+          <t>0.7217</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>160.189</t>
+          <t>125.4174</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>41.126</t>
+          <t>43.1407</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>175.013</t>
+          <t>29.7245</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25917.3</t>
+          <t>10195.015</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>9919.18</t>
+          <t>6075.8064</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>0.0023</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.0139</t>
+          <t>0.0001</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.0374</t>
+          <t>0.0001</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>8.0622</t>
+          <t>35.2331</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>4.5153</t>
+          <t>17.705</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>23.7225</t>
+          <t>11.6141</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-11.145</t>
+          <t>41.324</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -3257,19 +3257,19 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Q1_FS.xlsx</t>
+          <t>Q1_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3284,77 +3284,77 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1753.339</t>
+          <t>306.9506</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>792.994</t>
+          <t>222.2752</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>69.78</t>
+          <t>-4.1173</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>120.711</t>
+          <t>115.9707</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>39.848</t>
+          <t>43.7804</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>154.434</t>
+          <t>28.1357</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>25764.928</t>
+          <t>10337.1448</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>9508.7</t>
+          <t>6073.5842</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.0398</t>
+          <t>-0.0134</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.0027</t>
+          <t>-0.0004</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.0072</t>
+          <t>-0.0007</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>7.2895</t>
+          <t>35.7815</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4.6461</t>
+          <t>17.7929</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>18.9028</t>
+          <t>11.844</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-6.9673</t>
+          <t>41.7304</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -3364,19 +3364,19 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Q2_FS.xlsx</t>
+          <t>Q2_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3391,77 +3391,77 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1788.638</t>
+          <t>326.3587</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>801.101</t>
+          <t>241.6473</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>59.797</t>
+          <t>-4.0961</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>155.074</t>
+          <t>105.3836</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>42.315</t>
+          <t>44.8648</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>180.07</t>
+          <t>34.2695</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>25461.134</t>
+          <t>10147.0933</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9481.112</t>
+          <t>5982.5796</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.0334</t>
+          <t>-0.0126</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.0023</t>
+          <t>-0.0004</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.0063</t>
+          <t>-0.0007</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>7.0926</t>
+          <t>31.1997</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.7179</t>
+          <t>16.8745</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>19.2075</t>
+          <t>11.8794</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>-7.3971</t>
+          <t>36.1948</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -3478,12 +3478,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3498,77 +3498,77 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2259.7525</t>
+          <t>325.7402</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>834.3435</t>
+          <t>237.0154</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>412.4433</t>
+          <t>1.8962</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>232.438</t>
+          <t>87.2792</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40.396</t>
+          <t>46.2466</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>257.323</t>
+          <t>33.1553</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26459.9264</t>
+          <t>10140.7512</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9787.1647</t>
+          <t>6008.7574</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.1825</t>
+          <t>0.0058</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.0159</t>
+          <t>0.0002</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.0428</t>
+          <t>0.0003</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>7.8883</t>
+          <t>27.2072</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>4.5601</t>
+          <t>17.6829</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>24.1149</t>
+          <t>13.0858</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>-11.6665</t>
+          <t>31.8043</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -3577,7 +3577,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3597,77 +3597,77 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>97.8812</t>
+          <t>342.6841</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>53.115</t>
+          <t>233.1898</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14.114</t>
+          <t>14.423</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>16.1787</t>
+          <t>83.3637</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.3477</t>
+          <t>45.8098</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>29.991</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>669.2441</t>
+          <t>10218.2885</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>452.6589</t>
+          <t>6021.921</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.0421</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.0207</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.0317</t>
+          <t>0.0024</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>13.5146</t>
+          <t>22.4082</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2.5197</t>
+          <t>17.7647</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>59.3484</t>
+          <t>12.5444</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-43.3141</t>
+          <t>27.6284</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -3677,14 +3677,14 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Q1_FS.xlsx</t>
+          <t>Q1_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3704,77 +3704,77 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>75.445</t>
+          <t>306.2049</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48.0476</t>
+          <t>233.9883</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.6651</t>
+          <t>-14.9731</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>80.9068</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.2802</t>
+          <t>45.7666</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32.1413</t>
+          <t>28.0287</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>668.5211</t>
+          <t>10013.3875</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>456.324</t>
+          <t>5951.8987</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.0486</t>
+          <t>-0.0489</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.0055</t>
+          <t>-0.0015</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.0081</t>
+          <t>-0.0025</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>18.0195</t>
+          <t>24.4095</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.4886</t>
+          <t>17.8074</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>58.8379</t>
+          <t>11.6437</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-38.3298</t>
+          <t>30.5733</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -3784,14 +3784,14 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Q2_FS.xlsx</t>
+          <t>Q2_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3811,77 +3811,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>95.0862</t>
+          <t>321.6484</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>57.5382</t>
+          <t>236.6086</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11.84</t>
+          <t>-6.092</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12.9018</t>
+          <t>89.8435</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>45.9873</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>38.2079</t>
+          <t>27.6193</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>669.4754</t>
+          <t>9975.5818</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>468.164</t>
+          <t>5943.4917</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.1245</t>
+          <t>-0.0189</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.0177</t>
+          <t>-0.0006</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.0256</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>12.8692</t>
+          <t>24.4196</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.9259</t>
+          <t>17.8382</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>56.242</t>
+          <t>10.8187</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-41.447</t>
+          <t>31.439</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Q3_FS.xlsx</t>
+          <t>Q3_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3918,77 +3918,77 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>94.8345</t>
+          <t>394.0262</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>55.0352</t>
+          <t>238.8158</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10.1986</t>
+          <t>3.2873</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>10.6145</t>
+          <t>90.5727</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.6372</t>
+          <t>46.0018</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.4437</t>
+          <t>32.8516</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>645.3267</t>
+          <t>10336.3165</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>476.4493</t>
+          <t>5913.1293</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.1075</t>
+          <t>0.0083</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.0155</t>
+          <t>0.0003</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.0216</t>
+          <t>0.0006</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>11.4067</t>
+          <t>21.0624</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.3118</t>
+          <t>17.7187</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>57.3811</t>
+          <t>11.6477</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>-43.6625</t>
+          <t>27.1333</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3997,7 +3997,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4017,77 +4017,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>37267.312</t>
+          <t>6695.756</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20008.898</t>
+          <t>3390.386</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>611.516</t>
+          <t>761.578</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14945.937</t>
+          <t>1141.727</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4088.494</t>
+          <t>834.687</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>22052.993</t>
+          <t>3316.245</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>355544.01</t>
+          <t>60445.465</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>98317.427</t>
+          <t>21712.54</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.0164</t>
+          <t>0.1137</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.0017</t>
+          <t>0.0126</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.0062</t>
+          <t>0.0357</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>34.9162</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>18.0058</t>
+          <t>23.0874</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>104.5056</t>
+          <t>102.7248</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-51.5836</t>
+          <t>-63.8475</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -4097,14 +4097,14 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Q1_FS.xlsx</t>
+          <t>Q1_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4124,77 +4124,77 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>43497.069</t>
+          <t>5752.002</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22101.435</t>
+          <t>3359.448</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3322.548</t>
+          <t>85.859</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>15751.811</t>
+          <t>794.157</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4157.115</t>
+          <t>818.407</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24610.107</t>
+          <t>3165.901</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>366301.08</t>
+          <t>61666.464</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>99185.386</t>
+          <t>21693.156</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.0764</t>
+          <t>0.0149</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.0092</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.0336</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>32.1113</t>
+          <t>15.3134</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>16.9752</t>
+          <t>22.3893</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>96.0649</t>
+          <t>87.7935</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>-46.9784</t>
+          <t>-50.0908</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -4204,14 +4204,14 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Q2_FS.xlsx</t>
+          <t>Q2_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4231,77 +4231,77 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>41174.584</t>
+          <t>5773.648</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>21956.753</t>
+          <t>3214.825</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2667.974</t>
+          <t>142.249</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17466.545</t>
+          <t>815.54</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4137.789</t>
+          <t>749.963</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>23955.136</t>
+          <t>3237.658</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>356649.372</t>
+          <t>61162.494</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>94833.336</t>
+          <t>21785.05</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.0648</t>
+          <t>0.0246</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.0074</t>
+          <t>0.0023</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.0275</t>
+          <t>0.0065</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>37.1113</t>
+          <t>12.8248</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>17.3781</t>
+          <t>22.4414</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>101.7455</t>
+          <t>91.6267</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-47.2561</t>
+          <t>-56.3605</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Q3_FS.xlsx</t>
+          <t>Q3_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4338,77 +4338,77 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>43865.7491</t>
+          <t>6829.5242</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>22154.6994</t>
+          <t>3391.9525</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3237.2946</t>
+          <t>974.4597</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>15911.6016</t>
+          <t>961.7198</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3921.4803</t>
+          <t>868.2159</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>25606.359</t>
+          <t>3929.7783</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>357329.6666</t>
+          <t>62728.0189</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>96985.6572</t>
+          <t>22614.472</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.0738</t>
+          <t>0.1427</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.0091</t>
+          <t>0.0157</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>0.0439</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>35.0021</t>
+          <t>11.9707</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>16.7335</t>
+          <t>21.9449</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>102.905</t>
+          <t>97.2013</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-51.1693</t>
+          <t>-63.2856</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -4417,7 +4417,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4437,77 +4437,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>789.301</t>
+          <t>2344.842</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>332.6197</t>
+          <t>1355.983</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>193.8595</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>89.5299</t>
+          <t>1319.728</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>23.1416</t>
+          <t>131.598</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>268.2755</t>
+          <t>2054.776</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>5725.7918</t>
+          <t>38766.715</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2677.6813</t>
+          <t>8750.937</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.2456</t>
+          <t>0.0154</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>0.0009</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.0751</t>
+          <t>0.0041</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>9.9049</t>
+          <t>47.3023</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>7.0353</t>
+          <t>8.7059</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>87.0016</t>
+          <t>131.5497</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>-70.0614</t>
+          <t>-75.5416</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -4524,7 +4524,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4544,77 +4544,77 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>433.486</t>
+          <t>1709.084</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>280.8156</t>
+          <t>1068.566</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-21.6962</t>
+          <t>-324.379</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>67.4259</t>
+          <t>1178.171</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20.6785</t>
+          <t>119.126</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>280.6725</t>
+          <t>1621.867</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5670.2721</t>
+          <t>38218.557</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2655.9851</t>
+          <t>8416.257</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-0.0501</t>
+          <t>-0.1898</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-0.0038</t>
+          <t>-0.0084</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-0.0081</t>
+          <t>-0.0378</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>16.4745</t>
+          <t>66.5002</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>7.1001</t>
+          <t>10.6759</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>88.945</t>
+          <t>156.553</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>-65.3703</t>
+          <t>-79.3769</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -4631,7 +4631,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4651,77 +4651,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>478.3312</t>
+          <t>1751.875</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>331.1909</t>
+          <t>1139.186</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-26.0182</t>
+          <t>-422.865</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>78.9921</t>
+          <t>1153.552</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>32.8947</t>
+          <t>124.156</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>503.8692</t>
+          <t>1869.877</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>5846.5963</t>
+          <t>38640.11</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2629.9669</t>
+          <t>7941.989</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-0.0544</t>
+          <t>-0.2414</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-0.0045</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-0.0098</t>
+          <t>-0.0517</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>14.0807</t>
+          <t>61.2254</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>7.4409</t>
+          <t>9.8237</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>108.9671</t>
+          <t>140.9956</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>-87.4455</t>
+          <t>-69.9465</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -4738,7 +4738,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4758,77 +4758,77 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>823.8227</t>
+          <t>3118.196</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>387.9619</t>
+          <t>1814.581</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>167.549</t>
+          <t>240.259</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>107.3732</t>
+          <t>1482.137</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>36.3419</t>
+          <t>133.654</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>598.6416</t>
+          <t>2068.782</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6047.5464</t>
+          <t>39722.107</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2797.2204</t>
+          <t>8261.867</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>0.0771</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.0282</t>
+          <t>0.0061</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.0617</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>10.4061</t>
+          <t>38.882</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>8.2093</t>
+          <t>6.5355</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>130.7229</t>
+          <t>99.8458</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>-112.1075</t>
+          <t>-54.4283</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -4837,7 +4837,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4857,77 +4857,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>659.954</t>
+          <t>2135.663</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>188.579</t>
+          <t>836.589</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>159.821</t>
+          <t>362.736</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>61.376</t>
+          <t>160.189</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>27.765</t>
+          <t>41.126</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>162.319</t>
+          <t>175.013</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8195.463</t>
+          <t>25917.3</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7595.093</t>
+          <t>9919.18</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.2422</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.0197</t>
+          <t>0.0139</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.0213</t>
+          <t>0.0374</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>9.6443</t>
+          <t>8.0622</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>13.4817</t>
+          <t>4.5153</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>94.8007</t>
+          <t>23.7225</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>-71.6747</t>
+          <t>-11.145</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4964,77 +4964,77 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>401.638</t>
+          <t>1753.339</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>145.967</t>
+          <t>792.994</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-40.895</t>
+          <t>69.78</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>42.973</t>
+          <t>120.711</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>27.609</t>
+          <t>39.848</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>137.849</t>
+          <t>154.434</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7984.993</t>
+          <t>25764.928</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7468.704</t>
+          <t>9508.7</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>-0.1018</t>
+          <t>0.0398</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-0.0051</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>-0.0054</t>
+          <t>0.0072</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>11.8213</t>
+          <t>7.2895</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>17.2609</t>
+          <t>4.6461</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>93.5667</t>
+          <t>18.9028</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>-64.4845</t>
+          <t>-6.9673</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -5044,14 +5044,14 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5071,77 +5071,77 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>467.158</t>
+          <t>1788.638</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>166.785</t>
+          <t>801.101</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>87.081</t>
+          <t>59.797</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>57.888</t>
+          <t>155.074</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25.864</t>
+          <t>42.315</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>132.189</t>
+          <t>180.07</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8034.036</t>
+          <t>25461.134</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>7505.949</t>
+          <t>9481.112</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.0334</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0023</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0063</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>9.9316</t>
+          <t>7.0926</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>14.7481</t>
+          <t>4.7179</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>74.4776</t>
+          <t>19.2075</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>-49.798</t>
+          <t>-7.3971</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5178,77 +5178,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>624.6388</t>
+          <t>2259.7525</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>193.8865</t>
+          <t>834.3435</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>34.8966</t>
+          <t>412.4433</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>90.0129</t>
+          <t>232.438</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>27.8828</t>
+          <t>40.396</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>259.24</t>
+          <t>257.323</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8261.9755</t>
+          <t>26459.9264</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>7509.0939</t>
+          <t>9787.1647</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.0559</t>
+          <t>0.1825</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.0043</t>
+          <t>0.0159</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.0046</t>
+          <t>0.0428</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>10.8918</t>
+          <t>7.8883</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>12.7515</t>
+          <t>4.5601</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>92.8674</t>
+          <t>24.1149</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>-69.2241</t>
+          <t>-11.6665</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -5257,7 +5257,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5277,77 +5277,77 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2649.224</t>
+          <t>97.8812</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1582.956</t>
+          <t>53.115</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>175.544</t>
+          <t>14.114</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>502.606</t>
+          <t>16.1787</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>223.595</t>
+          <t>1.3477</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>865.016</t>
+          <t>29.991</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>36612.798</t>
+          <t>669.2441</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>16235.452</t>
+          <t>452.6589</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.0663</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.0048</t>
+          <t>0.0207</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0317</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>16.6185</t>
+          <t>13.5146</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>12.9589</t>
+          <t>2.5197</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>52.3113</t>
+          <t>59.3484</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>-22.7338</t>
+          <t>-43.3141</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -5357,14 +5357,14 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5384,77 +5384,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2431.997</t>
+          <t>75.445</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1528.045</t>
+          <t>48.0476</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>3.6651</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>331.082</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>220.973</t>
+          <t>1.2802</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>819.563</t>
+          <t>32.1413</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>35934.539</t>
+          <t>668.5211</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>15859.504</t>
+          <t>456.324</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0486</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>0.0055</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.0015</t>
+          <t>0.0081</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>15.5974</t>
+          <t>18.0195</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>13.2377</t>
+          <t>2.4886</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>50.1611</t>
+          <t>58.8379</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>-21.3259</t>
+          <t>-38.3298</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -5464,14 +5464,14 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5491,77 +5491,77 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2604.449</t>
+          <t>95.0862</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1544.681</t>
+          <t>57.5382</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>128.587</t>
+          <t>11.84</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>361.827</t>
+          <t>12.9018</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>231.174</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>807.788</t>
+          <t>38.2079</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>35409.916</t>
+          <t>669.4754</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>15649.4</t>
+          <t>468.164</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.0494</t>
+          <t>0.1245</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0177</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.0082</t>
+          <t>0.0256</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>12.2382</t>
+          <t>12.8692</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>13.4648</t>
+          <t>1.9259</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>48.4619</t>
+          <t>56.242</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-22.7589</t>
+          <t>-41.447</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5598,77 +5598,77 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2725.5033</t>
+          <t>94.8345</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1623.9576</t>
+          <t>55.0352</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1914.3989</t>
+          <t>10.1986</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>406.2581</t>
+          <t>10.6145</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>244.4322</t>
+          <t>1.6372</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1009.863</t>
+          <t>30.4437</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>33003.4116</t>
+          <t>645.3267</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>13373.2173</t>
+          <t>476.4493</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-0.7024</t>
+          <t>0.1075</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>0.0155</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>-0.1319</t>
+          <t>0.0216</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>12.9634</t>
+          <t>11.4067</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>13.472</t>
+          <t>2.3118</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>51.4865</t>
+          <t>57.3811</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>-25.0511</t>
+          <t>-43.6625</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -5677,7 +5677,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5697,77 +5697,77 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>427.929</t>
+          <t>37267.312</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>218.02</t>
+          <t>20008.898</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>42.867</t>
+          <t>611.516</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>57.227</t>
+          <t>14945.937</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>4088.494</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>363.318</t>
+          <t>22052.993</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5699.147</t>
+          <t>355544.01</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1881.959</t>
+          <t>98317.427</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.1002</t>
+          <t>0.0164</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>0.0017</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.0062</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>11.8464</t>
+          <t>34.9162</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>6.7108</t>
+          <t>18.0058</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>165.9953</t>
+          <t>104.5056</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>-147.4381</t>
+          <t>-51.5836</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -5784,7 +5784,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5804,77 +5804,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>314.521</t>
+          <t>43497.069</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>199.239</t>
+          <t>22101.435</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>11.881</t>
+          <t>3322.548</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>34.675</t>
+          <t>15751.811</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15.557</t>
+          <t>4157.115</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>269.551</t>
+          <t>24610.107</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5664.051</t>
+          <t>366301.08</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1853.88</t>
+          <t>99185.386</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.0378</t>
+          <t>0.0764</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>0.0092</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.0064</t>
+          <t>0.0336</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>13.295</t>
+          <t>32.1113</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>7.1295</t>
+          <t>16.9752</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>144.5276</t>
+          <t>96.0649</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>-124.1032</t>
+          <t>-46.9784</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -5891,7 +5891,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5911,77 +5911,77 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>362.011</t>
+          <t>41174.584</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>21956.753</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>2667.974</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>17466.545</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15.963</t>
+          <t>4137.789</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>245.158</t>
+          <t>23955.136</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>5766.065</t>
+          <t>356649.372</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1855.722</t>
+          <t>94833.336</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.0051</t>
+          <t>0.0648</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0074</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.0275</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>10.7887</t>
+          <t>37.1113</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>6.8412</t>
+          <t>17.3781</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>111.7138</t>
+          <t>101.7455</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>-94.0839</t>
+          <t>-47.2561</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -5998,7 +5998,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6018,81 +6018,1761 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>472.7198</t>
+          <t>43865.7491</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>237.0251</t>
+          <t>22154.6994</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>44.1944</t>
+          <t>3237.2946</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>52.9387</t>
+          <t>15911.6016</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20.3805</t>
+          <t>3921.4803</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>238.7387</t>
+          <t>25606.359</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>5770.1542</t>
+          <t>357329.6666</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1894.2679</t>
+          <t>96985.6572</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.0935</t>
+          <t>0.0738</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>0.0091</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.0236</t>
+          <t>0.0338</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>10.0393</t>
+          <t>35.0021</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>7.0533</t>
+          <t>16.7335</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>93.9109</t>
+          <t>102.905</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>-76.8184</t>
+          <t>-51.1693</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>789.301</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>332.6197</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>193.8595</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>89.5299</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>23.1416</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>268.2755</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5725.7918</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2677.6813</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>0.2456</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0.0338</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0.0751</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>9.9049</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>7.0353</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>87.0016</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>-70.0614</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>433.486</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>280.8156</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-21.6962</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>67.4259</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20.6785</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>280.6725</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>5670.2721</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2655.9851</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>-0.0501</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>-0.0038</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>-0.0081</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>16.4745</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>7.1001</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>88.945</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>-65.3703</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>478.3312</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>331.1909</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-26.0182</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>78.9921</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>32.8947</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>503.8692</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>5846.5963</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2629.9669</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>-0.0544</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>-0.0045</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>-0.0098</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>14.0807</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>7.4409</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>108.9671</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>-87.4455</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>823.8227</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>387.9619</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>167.549</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>107.3732</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>36.3419</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>598.6416</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6047.5464</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2797.2204</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>0.2034</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0.0282</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0.0617</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10.4061</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>8.2093</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>130.7229</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>-112.1075</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>659.954</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>188.579</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>159.821</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>61.376</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>27.765</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>162.319</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>8195.463</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7595.093</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>0.2422</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0.0197</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0.0213</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>9.6443</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>13.4817</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>94.8007</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>-71.6747</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>401.638</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>145.967</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-40.895</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>42.973</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>27.609</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>137.849</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>7984.993</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>7468.704</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>-0.1018</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>-0.0051</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>-0.0054</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>11.8213</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>17.2609</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>93.5667</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>-64.4845</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>467.158</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>166.785</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>87.081</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>57.888</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25.864</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>132.189</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>8034.036</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>7505.949</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.1864</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.0116</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>9.9316</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>14.7481</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>74.4776</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>-49.798</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>624.6388</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>193.8865</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>34.8966</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>90.0129</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>27.8828</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>259.24</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>8261.9755</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>7509.0939</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0559</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0043</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0046</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>10.8918</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>12.7515</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>92.8674</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>-69.2241</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2649.224</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1582.956</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>175.544</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>502.606</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>223.595</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>865.016</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>36612.798</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>16235.452</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0663</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.0048</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>16.6185</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>12.9589</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>52.3113</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>-22.7338</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2431.997</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1528.045</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>331.082</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>220.973</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>819.563</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>35934.539</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>15859.504</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>15.5974</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>13.2377</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>50.1611</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>-21.3259</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2604.449</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1544.681</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>128.587</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>361.827</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>231.174</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>807.788</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>35409.916</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>15649.4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0494</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0082</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>12.2382</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>13.4648</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>48.4619</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>-22.7589</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2725.5033</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1623.9576</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-1914.3989</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>406.2581</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>244.4322</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1009.863</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>33003.4116</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>13373.2173</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>-0.7024</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>-0.1319</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>12.9634</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>13.472</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>51.4865</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>-25.0511</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>427.929</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>218.02</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>42.867</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>57.227</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15.662</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>363.318</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>5699.147</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1881.959</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>0.1002</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>11.8464</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>6.7108</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>165.9953</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>-147.4381</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>314.521</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>199.239</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>11.881</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>34.675</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15.557</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>269.551</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>5664.051</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1853.88</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0.0064</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>13.295</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>7.1295</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>144.5276</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>-124.1032</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>362.011</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>211.94</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1.842</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>50.23</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>15.963</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>245.158</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>5766.065</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1855.722</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>10.7887</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>6.8412</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>111.7138</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>-94.0839</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>472.7198</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>237.0251</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>44.1944</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>52.9387</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20.3805</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>238.7387</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>5770.1542</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1894.2679</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>0.0935</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0.0077</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0.0236</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>10.0393</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>7.0533</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>93.9109</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>-76.8184</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -1781,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4017,77 +4017,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6695.756</t>
+          <t>2754.569</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3390.386</t>
+          <t>1813.043</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>761.578</t>
+          <t>-480.758</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1141.727</t>
+          <t>547.528</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>834.687</t>
+          <t>724.063</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3316.245</t>
+          <t>1709.627</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>60445.465</t>
+          <t>35606.005</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>21712.54</t>
+          <t>9870.319</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.1137</t>
+          <t>-0.1745</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.0126</t>
+          <t>-0.0136</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.0357</t>
+          <t>-0.0479</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>17.3476</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>23.0874</t>
+          <t>37.3745</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>102.7248</t>
+          <t>88.9207</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-63.8475</t>
+          <t>-34.1986</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4124,77 +4124,77 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5752.002</t>
+          <t>2661.964</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3359.448</t>
+          <t>1848.835</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>85.859</t>
+          <t>-634.245</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>794.157</t>
+          <t>617.865</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>818.407</t>
+          <t>709.102</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3165.901</t>
+          <t>2025.123</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>61666.464</t>
+          <t>47682.473</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>21693.156</t>
+          <t>18980.132</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.0149</t>
+          <t>-0.2383</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>-0.0152</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-0.044</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>15.3134</t>
+          <t>19.9196</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>22.3893</t>
+          <t>35.2703</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>87.7935</t>
+          <t>91.9125</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>-50.0908</t>
+          <t>-36.7226</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4231,77 +4231,77 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5773.648</t>
+          <t>2396.598</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3214.825</t>
+          <t>1757.659</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>142.249</t>
+          <t>-832.299</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>815.54</t>
+          <t>636.505</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>749.963</t>
+          <t>692.58</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3237.658</t>
+          <t>2231.583</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>61162.494</t>
+          <t>47879.915</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>21785.05</t>
+          <t>18303.915</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.0246</t>
+          <t>-0.3473</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.0023</t>
+          <t>-0.0174</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.0065</t>
+          <t>-0.0446</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>12.8248</t>
+          <t>24.0762</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>22.4414</t>
+          <t>36.6837</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>91.6267</t>
+          <t>111.403</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-56.3605</t>
+          <t>-50.6431</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4338,77 +4338,77 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6829.5242</t>
+          <t>3715.3747</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3391.9525</t>
+          <t>2193.902</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>974.4597</t>
+          <t>189.9017</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>961.7198</t>
+          <t>801.3616</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>868.2159</t>
+          <t>747.7838</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3929.7783</t>
+          <t>2669.3097</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>62728.0189</t>
+          <t>48592.5427</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>22614.472</t>
+          <t>18431.6882</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.1427</t>
+          <t>0.0511</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.0157</t>
+          <t>0.0039</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.0439</t>
+          <t>0.0103</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>11.9707</t>
+          <t>17.8022</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>21.9449</t>
+          <t>30.2004</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>97.2013</t>
+          <t>102.758</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-63.2856</t>
+          <t>-54.7554</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -4417,12 +4417,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DUSIT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4437,77 +4437,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2344.842</t>
+          <t>3851.608</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1355.983</t>
+          <t>2285.245</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>-23.161</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1319.728</t>
+          <t>1000.029</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>131.598</t>
+          <t>708.707</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2054.776</t>
+          <t>2499.627</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>38766.715</t>
+          <t>48299.979</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8750.937</t>
+          <t>18406.311</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.0154</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.0009</t>
+          <t>-0.0005</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.0041</t>
+          <t>-0.0013</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>47.3023</t>
+          <t>21.0464</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>8.7059</t>
+          <t>28.6806</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>131.5497</t>
+          <t>101.7843</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>-75.5416</t>
+          <t>-52.0574</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -4517,19 +4517,19 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Q1_FS.xlsx</t>
+          <t>Q1_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DUSIT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4544,77 +4544,77 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1709.084</t>
+          <t>4296.949</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1068.566</t>
+          <t>2518.558</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-324.379</t>
+          <t>18.661</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1178.171</t>
+          <t>942.428</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>119.126</t>
+          <t>761.576</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1621.867</t>
+          <t>2692.844</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>38218.557</t>
+          <t>48024.246</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8416.257</t>
+          <t>18618.833</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-0.1898</t>
+          <t>0.0043</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-0.0084</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-0.0378</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>66.5002</t>
+          <t>20.5685</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>10.6759</t>
+          <t>26.562</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>156.553</t>
+          <t>93.8066</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>-79.3769</t>
+          <t>-46.6762</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -4624,19 +4624,19 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Q2_FS.xlsx</t>
+          <t>Q2_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DUSIT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4651,77 +4651,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1751.875</t>
+          <t>4527.85</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1139.186</t>
+          <t>2669.11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-422.865</t>
+          <t>-90.175</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1153.552</t>
+          <t>1016.611</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>124.156</t>
+          <t>810.562</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1869.877</t>
+          <t>2944.464</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>38640.11</t>
+          <t>48487.277</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>7941.989</t>
+          <t>18831.117</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-0.2414</t>
+          <t>-0.0199</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-0.011</t>
+          <t>-0.0019</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-0.0517</t>
+          <t>-0.0048</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>61.2254</t>
+          <t>19.9026</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>9.8237</t>
+          <t>27.0946</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>140.9956</t>
+          <t>97.1545</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>-69.9465</t>
+          <t>-50.1574</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -4731,19 +4731,19 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Q3_FS.xlsx</t>
+          <t>Q3_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DUSIT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4758,77 +4758,77 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3118.196</t>
+          <t>5359.91</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1814.581</t>
+          <t>3020.8034</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>240.259</t>
+          <t>509.107</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1482.137</t>
+          <t>1227.403</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>133.654</t>
+          <t>1023.8924</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2068.782</t>
+          <t>3459.7704</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>39722.107</t>
+          <t>48165.5922</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8261.867</t>
+          <t>18890.7284</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.0771</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.0061</t>
+          <t>0.0105</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>0.027</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>38.882</t>
+          <t>19.2587</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6.5355</t>
+          <t>27.9346</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>99.8458</t>
+          <t>97.522</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>-54.4283</t>
+          <t>-50.3288</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -4837,12 +4837,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4857,77 +4857,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2135.663</t>
+          <t>5804.619</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>836.589</t>
+          <t>3049.21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>362.736</t>
+          <t>680.935</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>160.189</t>
+          <t>1302.916</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>41.126</t>
+          <t>921.844</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>175.013</t>
+          <t>3104.468</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>25917.3</t>
+          <t>53217.562</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9919.18</t>
+          <t>19545.804</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>0.1173</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.0139</t>
+          <t>0.0134</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.0374</t>
+          <t>0.0354</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>8.0622</t>
+          <t>19.6162</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4.5153</t>
+          <t>28.715</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>23.7225</t>
+          <t>96.8745</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>-11.145</t>
+          <t>-48.5433</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -4937,19 +4937,19 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Q1_FS.xlsx</t>
+          <t>Q1_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4964,77 +4964,77 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1753.339</t>
+          <t>5171.518</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>792.994</t>
+          <t>3044.968</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>69.78</t>
+          <t>99.086</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>120.711</t>
+          <t>758.174</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>39.848</t>
+          <t>947.188</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>154.434</t>
+          <t>2603.264</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>25764.928</t>
+          <t>55207.933</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9508.7</t>
+          <t>19812.619</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.0398</t>
+          <t>0.0192</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.0027</t>
+          <t>0.0018</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.0072</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>7.2895</t>
+          <t>18.1339</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4.6461</t>
+          <t>27.9284</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>18.9028</t>
+          <t>85.2888</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>-6.9673</t>
+          <t>-39.2266</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -5044,19 +5044,19 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Q2_FS.xlsx</t>
+          <t>Q2_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5071,77 +5071,77 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1788.638</t>
+          <t>5351.553</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>801.101</t>
+          <t>3120.644</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>59.797</t>
+          <t>53.971</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>155.074</t>
+          <t>829.43</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>42.315</t>
+          <t>994.67</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>180.07</t>
+          <t>2676.562</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>25461.134</t>
+          <t>53693.546</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>9481.112</t>
+          <t>20005.735</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.0334</t>
+          <t>0.0101</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.0023</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.0063</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>7.0926</t>
+          <t>13.6465</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>4.7179</t>
+          <t>28.624</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>19.2075</t>
+          <t>77.8275</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>-7.3971</t>
+          <t>-35.557</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -5151,19 +5151,19 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Q3_FS.xlsx</t>
+          <t>Q3_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5178,77 +5178,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2259.7525</t>
+          <t>5933.6798</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>834.3435</t>
+          <t>3495.9385</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>412.4433</t>
+          <t>422.2214</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>232.438</t>
+          <t>1518.9778</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>40.396</t>
+          <t>982.4218</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>257.323</t>
+          <t>3445.3354</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>26459.9264</t>
+          <t>54203.6125</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>9787.1647</t>
+          <t>20017.9829</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.1825</t>
+          <t>0.0712</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.0159</t>
+          <t>0.0078</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.0428</t>
+          <t>0.0211</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>7.8883</t>
+          <t>18.2057</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4.5601</t>
+          <t>26.0148</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>24.1149</t>
+          <t>80.5527</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>-11.6665</t>
+          <t>-36.3322</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -5257,12 +5257,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5277,77 +5277,77 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>97.8812</t>
+          <t>6321.691</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>53.115</t>
+          <t>3335.369</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14.114</t>
+          <t>785.318</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>16.1787</t>
+          <t>1316.054</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.3477</t>
+          <t>833.05</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>29.991</t>
+          <t>2946.41</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>669.2441</t>
+          <t>54465.345</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>452.6589</t>
+          <t>21173.536</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.0207</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.0317</t>
+          <t>0.0381</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>13.5146</t>
+          <t>20.1807</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.5197</t>
+          <t>24.4939</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>59.3484</t>
+          <t>86.2359</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>-43.3141</t>
+          <t>-41.5612</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -5357,19 +5357,19 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Q1_FS.xlsx</t>
+          <t>Q1_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5384,77 +5384,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>75.445</t>
+          <t>5763.953</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>48.0476</t>
+          <t>3275.665</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3.6651</t>
+          <t>124.139</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>935.457</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.2802</t>
+          <t>781.03</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>32.1413</t>
+          <t>3422.567</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>668.5211</t>
+          <t>56258.126</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>456.324</t>
+          <t>20811.002</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.0486</t>
+          <t>0.0215</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.0055</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.0081</t>
+          <t>0.0059</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>18.0195</t>
+          <t>17.7732</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2.4886</t>
+          <t>22.4201</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>58.8379</t>
+          <t>88.4671</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>-38.3298</t>
+          <t>-48.2738</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -5464,19 +5464,19 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Q2_FS.xlsx</t>
+          <t>Q2_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5491,77 +5491,77 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>95.0862</t>
+          <t>5539.57</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>57.5382</t>
+          <t>3257.927</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11.84</t>
+          <t>150.556</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>12.9018</t>
+          <t>861.291</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>850.04</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>38.2079</t>
+          <t>3499.966</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>669.4754</t>
+          <t>56536.705</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>468.164</t>
+          <t>19919.18</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.1245</t>
+          <t>0.0272</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.0177</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.0256</t>
+          <t>0.0074</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>12.8692</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.9259</t>
+          <t>23.0297</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>56.242</t>
+          <t>97.7421</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-41.447</t>
+          <t>-59.7923</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -5571,19 +5571,19 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Q3_FS.xlsx</t>
+          <t>Q3_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5598,77 +5598,77 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>94.8345</t>
+          <t>6324.3146</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>55.0352</t>
+          <t>3555.4813</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10.1986</t>
+          <t>636.2611</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10.6145</t>
+          <t>1207.7371</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.6372</t>
+          <t>904.7593</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30.4437</t>
+          <t>4423.2387</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>645.3267</t>
+          <t>60760.6326</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>476.4493</t>
+          <t>20949.7375</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.1075</t>
+          <t>0.1006</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.0155</t>
+          <t>0.0108</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.0216</t>
+          <t>0.0311</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>11.4067</t>
+          <t>15.0491</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.3118</t>
+          <t>22.7032</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>57.3811</t>
+          <t>102.5086</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>-43.6625</t>
+          <t>-64.7563</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -5677,7 +5677,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5697,77 +5697,77 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>37267.312</t>
+          <t>6695.756</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20008.898</t>
+          <t>3390.386</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>611.516</t>
+          <t>761.578</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>14945.937</t>
+          <t>1141.727</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4088.494</t>
+          <t>834.687</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>22052.993</t>
+          <t>3316.245</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>355544.01</t>
+          <t>60445.465</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>98317.427</t>
+          <t>21712.54</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.0164</t>
+          <t>0.1137</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.0017</t>
+          <t>0.0126</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.0062</t>
+          <t>0.0357</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>34.9162</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>18.0058</t>
+          <t>23.0874</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>104.5056</t>
+          <t>102.7248</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>-51.5836</t>
+          <t>-63.8475</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -5777,14 +5777,14 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Q1_FS.xlsx</t>
+          <t>Q1_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5804,77 +5804,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>43497.069</t>
+          <t>5752.002</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>22101.435</t>
+          <t>3359.448</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3322.548</t>
+          <t>85.859</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>15751.811</t>
+          <t>794.157</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4157.115</t>
+          <t>818.407</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>24610.107</t>
+          <t>3165.901</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>366301.08</t>
+          <t>61666.464</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>99185.386</t>
+          <t>21693.156</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.0764</t>
+          <t>0.0149</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.0092</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.0336</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>32.1113</t>
+          <t>15.3134</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>16.9752</t>
+          <t>22.3893</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>96.0649</t>
+          <t>87.7935</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>-46.9784</t>
+          <t>-50.0908</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -5884,14 +5884,14 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Q2_FS.xlsx</t>
+          <t>Q2_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5911,77 +5911,77 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>41174.584</t>
+          <t>5773.648</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>21956.753</t>
+          <t>3214.825</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2667.974</t>
+          <t>142.249</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>17466.545</t>
+          <t>815.54</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4137.789</t>
+          <t>749.963</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>23955.136</t>
+          <t>3237.658</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>356649.372</t>
+          <t>61162.494</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>94833.336</t>
+          <t>21785.05</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.0648</t>
+          <t>0.0246</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.0074</t>
+          <t>0.0023</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.0275</t>
+          <t>0.0065</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>37.1113</t>
+          <t>12.8248</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>17.3781</t>
+          <t>22.4414</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>101.7455</t>
+          <t>91.6267</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>-47.2561</t>
+          <t>-56.3605</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -5991,14 +5991,14 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Q3_FS.xlsx</t>
+          <t>Q3_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>CENTEL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6018,77 +6018,77 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>43865.7491</t>
+          <t>6829.5242</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>22154.6994</t>
+          <t>3391.9525</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3237.2946</t>
+          <t>974.4597</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>15911.6016</t>
+          <t>961.7198</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3921.4803</t>
+          <t>868.2159</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>25606.359</t>
+          <t>3929.7783</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>357329.6666</t>
+          <t>62728.0189</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>96985.6572</t>
+          <t>22614.472</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.0738</t>
+          <t>0.1427</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.0091</t>
+          <t>0.0157</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>0.0439</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>35.0021</t>
+          <t>11.9707</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>16.7335</t>
+          <t>21.9449</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>102.905</t>
+          <t>97.2013</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>-51.1693</t>
+          <t>-63.2856</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -6097,7 +6097,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6117,77 +6117,77 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>789.301</t>
+          <t>2344.842</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>332.6197</t>
+          <t>1355.983</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>193.8595</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>89.5299</t>
+          <t>1319.728</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>23.1416</t>
+          <t>131.598</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>268.2755</t>
+          <t>2054.776</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>5725.7918</t>
+          <t>38766.715</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2677.6813</t>
+          <t>8750.937</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.2456</t>
+          <t>0.0154</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>0.0009</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.0751</t>
+          <t>0.0041</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>9.9049</t>
+          <t>47.3023</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>7.0353</t>
+          <t>8.7059</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>87.0016</t>
+          <t>131.5497</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>-70.0614</t>
+          <t>-75.5416</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -6204,7 +6204,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6224,77 +6224,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>433.486</t>
+          <t>1709.084</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>280.8156</t>
+          <t>1068.566</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-21.6962</t>
+          <t>-324.379</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>67.4259</t>
+          <t>1178.171</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20.6785</t>
+          <t>119.126</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>280.6725</t>
+          <t>1621.867</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5670.2721</t>
+          <t>38218.557</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2655.9851</t>
+          <t>8416.257</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-0.0501</t>
+          <t>-0.1898</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-0.0038</t>
+          <t>-0.0084</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-0.0081</t>
+          <t>-0.0378</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>16.4745</t>
+          <t>66.5002</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>7.1001</t>
+          <t>10.6759</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>88.945</t>
+          <t>156.553</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>-65.3703</t>
+          <t>-79.3769</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -6311,7 +6311,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6331,77 +6331,77 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>478.3312</t>
+          <t>1751.875</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>331.1909</t>
+          <t>1139.186</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-26.0182</t>
+          <t>-422.865</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>78.9921</t>
+          <t>1153.552</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>32.8947</t>
+          <t>124.156</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>503.8692</t>
+          <t>1869.877</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>5846.5963</t>
+          <t>38640.11</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2629.9669</t>
+          <t>7941.989</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>-0.0544</t>
+          <t>-0.2414</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>-0.0045</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>-0.0098</t>
+          <t>-0.0517</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>14.0807</t>
+          <t>61.2254</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>7.4409</t>
+          <t>9.8237</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>108.9671</t>
+          <t>140.9956</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>-87.4455</t>
+          <t>-69.9465</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -6418,7 +6418,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6438,77 +6438,77 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>823.8227</t>
+          <t>3118.196</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>387.9619</t>
+          <t>1814.581</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>167.549</t>
+          <t>240.259</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>107.3732</t>
+          <t>1482.137</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>36.3419</t>
+          <t>133.654</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>598.6416</t>
+          <t>2068.782</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6047.5464</t>
+          <t>39722.107</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2797.2204</t>
+          <t>8261.867</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>0.0771</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.0282</t>
+          <t>0.0061</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.0617</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>10.4061</t>
+          <t>38.882</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>8.2093</t>
+          <t>6.5355</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>130.7229</t>
+          <t>99.8458</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>-112.1075</t>
+          <t>-54.4283</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -6517,7 +6517,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6537,77 +6537,77 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>659.954</t>
+          <t>2135.663</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>188.579</t>
+          <t>836.589</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>159.821</t>
+          <t>362.736</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>61.376</t>
+          <t>160.189</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>27.765</t>
+          <t>41.126</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>162.319</t>
+          <t>175.013</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>8195.463</t>
+          <t>25917.3</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>7595.093</t>
+          <t>9919.18</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0.2422</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>0.0197</t>
+          <t>0.0139</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0.0213</t>
+          <t>0.0374</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>9.6443</t>
+          <t>8.0622</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>13.4817</t>
+          <t>4.5153</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>94.8007</t>
+          <t>23.7225</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>-71.6747</t>
+          <t>-11.145</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6644,77 +6644,77 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>401.638</t>
+          <t>1753.339</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>145.967</t>
+          <t>792.994</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-40.895</t>
+          <t>69.78</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>42.973</t>
+          <t>120.711</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>27.609</t>
+          <t>39.848</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>137.849</t>
+          <t>154.434</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>7984.993</t>
+          <t>25764.928</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>7468.704</t>
+          <t>9508.7</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>-0.1018</t>
+          <t>0.0398</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>-0.0051</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>-0.0054</t>
+          <t>0.0072</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>11.8213</t>
+          <t>7.2895</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>17.2609</t>
+          <t>4.6461</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>93.5667</t>
+          <t>18.9028</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>-64.4845</t>
+          <t>-6.9673</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6724,14 +6724,14 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6751,77 +6751,77 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>467.158</t>
+          <t>1788.638</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>166.785</t>
+          <t>801.101</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>87.081</t>
+          <t>59.797</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>57.888</t>
+          <t>155.074</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25.864</t>
+          <t>42.315</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>132.189</t>
+          <t>180.07</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8034.036</t>
+          <t>25461.134</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>7505.949</t>
+          <t>9481.112</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.0334</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0023</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0063</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>9.9316</t>
+          <t>7.0926</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>14.7481</t>
+          <t>4.7179</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>74.4776</t>
+          <t>19.2075</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>-49.798</t>
+          <t>-7.3971</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6858,77 +6858,77 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>624.6388</t>
+          <t>2259.7525</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>193.8865</t>
+          <t>834.3435</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>34.8966</t>
+          <t>412.4433</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>90.0129</t>
+          <t>232.438</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>27.8828</t>
+          <t>40.396</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>259.24</t>
+          <t>257.323</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>8261.9755</t>
+          <t>26459.9264</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>7509.0939</t>
+          <t>9787.1647</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.0559</t>
+          <t>0.1825</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.0043</t>
+          <t>0.0159</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.0046</t>
+          <t>0.0428</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>10.8918</t>
+          <t>7.8883</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>12.7515</t>
+          <t>4.5601</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>92.8674</t>
+          <t>24.1149</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>-69.2241</t>
+          <t>-11.6665</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -6937,7 +6937,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6957,77 +6957,77 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2649.224</t>
+          <t>97.8812</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1582.956</t>
+          <t>53.115</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>175.544</t>
+          <t>14.114</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>502.606</t>
+          <t>16.1787</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>223.595</t>
+          <t>1.3477</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>865.016</t>
+          <t>29.991</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>36612.798</t>
+          <t>669.2441</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>16235.452</t>
+          <t>452.6589</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.0663</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.0048</t>
+          <t>0.0207</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0317</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>16.6185</t>
+          <t>13.5146</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>12.9589</t>
+          <t>2.5197</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>52.3113</t>
+          <t>59.3484</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>-22.7338</t>
+          <t>-43.3141</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -7037,14 +7037,14 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7064,77 +7064,77 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2431.997</t>
+          <t>75.445</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1528.045</t>
+          <t>48.0476</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>3.6651</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>331.082</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>220.973</t>
+          <t>1.2802</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>819.563</t>
+          <t>32.1413</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>35934.539</t>
+          <t>668.5211</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>15859.504</t>
+          <t>456.324</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0486</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>0.0055</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.0015</t>
+          <t>0.0081</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>15.5974</t>
+          <t>18.0195</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>13.2377</t>
+          <t>2.4886</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>50.1611</t>
+          <t>58.8379</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>-21.3259</t>
+          <t>-38.3298</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7171,77 +7171,77 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2604.449</t>
+          <t>95.0862</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1544.681</t>
+          <t>57.5382</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>128.587</t>
+          <t>11.84</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>361.827</t>
+          <t>12.9018</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>231.174</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>807.788</t>
+          <t>38.2079</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>35409.916</t>
+          <t>669.4754</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>15649.4</t>
+          <t>468.164</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>0.0494</t>
+          <t>0.1245</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0177</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0.0082</t>
+          <t>0.0256</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>12.2382</t>
+          <t>12.8692</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>13.4648</t>
+          <t>1.9259</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>48.4619</t>
+          <t>56.242</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>-22.7589</t>
+          <t>-41.447</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -7251,14 +7251,14 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7278,77 +7278,77 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2725.5033</t>
+          <t>94.8345</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1623.9576</t>
+          <t>55.0352</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-1914.3989</t>
+          <t>10.1986</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>406.2581</t>
+          <t>10.6145</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>244.4322</t>
+          <t>1.6372</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1009.863</t>
+          <t>30.4437</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>33003.4116</t>
+          <t>645.3267</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>13373.2173</t>
+          <t>476.4493</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-0.7024</t>
+          <t>0.1075</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>0.0155</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>-0.1319</t>
+          <t>0.0216</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>12.9634</t>
+          <t>11.4067</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>13.472</t>
+          <t>2.3118</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>51.4865</t>
+          <t>57.3811</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>-25.0511</t>
+          <t>-43.6625</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -7357,7 +7357,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7377,77 +7377,77 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>427.929</t>
+          <t>37267.312</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>218.02</t>
+          <t>20008.898</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>42.867</t>
+          <t>611.516</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>57.227</t>
+          <t>14945.937</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>4088.494</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>363.318</t>
+          <t>22052.993</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>5699.147</t>
+          <t>355544.01</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1881.959</t>
+          <t>98317.427</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>0.1002</t>
+          <t>0.0164</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>0.0017</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.0062</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>11.8464</t>
+          <t>34.9162</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>6.7108</t>
+          <t>18.0058</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>165.9953</t>
+          <t>104.5056</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>-147.4381</t>
+          <t>-51.5836</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7484,77 +7484,77 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>314.521</t>
+          <t>43497.069</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>199.239</t>
+          <t>22101.435</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>11.881</t>
+          <t>3322.548</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>34.675</t>
+          <t>15751.811</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15.557</t>
+          <t>4157.115</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>269.551</t>
+          <t>24610.107</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>5664.051</t>
+          <t>366301.08</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1853.88</t>
+          <t>99185.386</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>0.0378</t>
+          <t>0.0764</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>0.0092</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.0064</t>
+          <t>0.0336</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>13.295</t>
+          <t>32.1113</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>7.1295</t>
+          <t>16.9752</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>144.5276</t>
+          <t>96.0649</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>-124.1032</t>
+          <t>-46.9784</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -7571,7 +7571,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7591,77 +7591,77 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>362.011</t>
+          <t>41174.584</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>21956.753</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>2667.974</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>17466.545</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>15.963</t>
+          <t>4137.789</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>245.158</t>
+          <t>23955.136</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>5766.065</t>
+          <t>356649.372</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1855.722</t>
+          <t>94833.336</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>0.0051</t>
+          <t>0.0648</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0074</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.0275</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>10.7887</t>
+          <t>37.1113</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>6.8412</t>
+          <t>17.3781</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>111.7138</t>
+          <t>101.7455</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>-94.0839</t>
+          <t>-47.2561</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -7678,7 +7678,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7698,81 +7698,1761 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>472.7198</t>
+          <t>43865.7491</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>237.0251</t>
+          <t>22154.6994</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>44.1944</t>
+          <t>3237.2946</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>52.9387</t>
+          <t>15911.6016</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20.3805</t>
+          <t>3921.4803</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>238.7387</t>
+          <t>25606.359</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>5770.1542</t>
+          <t>357329.6666</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1894.2679</t>
+          <t>96985.6572</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>0.0935</t>
+          <t>0.0738</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>0.0091</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0.0236</t>
+          <t>0.0338</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>10.0393</t>
+          <t>35.0021</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>7.0533</t>
+          <t>16.7335</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>93.9109</t>
+          <t>102.905</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>-76.8184</t>
+          <t>-51.1693</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>789.301</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>332.6197</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>193.8595</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>89.5299</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>23.1416</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>268.2755</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>5725.7918</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2677.6813</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>0.2456</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0.0338</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0.0751</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>9.9049</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>7.0353</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>87.0016</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>-70.0614</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>433.486</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>280.8156</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-21.6962</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>67.4259</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20.6785</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>280.6725</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>5670.2721</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2655.9851</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>-0.0501</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>-0.0038</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>-0.0081</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>16.4745</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>7.1001</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>88.945</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>-65.3703</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>478.3312</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>331.1909</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-26.0182</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>78.9921</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>32.8947</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>503.8692</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>5846.5963</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2629.9669</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>-0.0544</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>-0.0045</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>-0.0098</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>14.0807</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>7.4409</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>108.9671</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>-87.4455</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>823.8227</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>387.9619</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>167.549</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>107.3732</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>36.3419</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>598.6416</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>6047.5464</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2797.2204</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>0.2034</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0.0282</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0.0617</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>10.4061</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>8.2093</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>130.7229</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>-112.1075</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>659.954</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>188.579</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>159.821</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>61.376</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>27.765</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>162.319</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>8195.463</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>7595.093</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>0.2422</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0.0197</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0.0213</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>9.6443</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>13.4817</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>94.8007</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>-71.6747</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>401.638</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>145.967</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-40.895</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>42.973</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>27.609</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>137.849</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>7984.993</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>7468.704</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>-0.1018</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>-0.0051</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>-0.0054</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>11.8213</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>17.2609</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>93.5667</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>-64.4845</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>467.158</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>166.785</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>87.081</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>57.888</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>25.864</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>132.189</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>8034.036</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>7505.949</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>0.1864</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0.0116</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>9.9316</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>14.7481</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>74.4776</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>-49.798</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>624.6388</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>193.8865</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>34.8966</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>90.0129</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>27.8828</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>259.24</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>8261.9755</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>7509.0939</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>0.0559</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0.0043</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0.0046</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>10.8918</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>12.7515</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>92.8674</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>-69.2241</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2649.224</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1582.956</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>175.544</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>502.606</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>223.595</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>865.016</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>36612.798</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>16235.452</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>0.0663</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0.0048</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>16.6185</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>12.9589</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>52.3113</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>-22.7338</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2431.997</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1528.045</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>331.082</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>220.973</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>819.563</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>35934.539</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>15859.504</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>15.5974</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>13.2377</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>50.1611</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>-21.3259</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2604.449</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1544.681</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>128.587</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>361.827</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>231.174</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>807.788</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>35409.916</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>15649.4</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>0.0494</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0.0082</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>12.2382</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>13.4648</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>48.4619</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>-22.7589</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2725.5033</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1623.9576</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-1914.3989</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>406.2581</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>244.4322</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1009.863</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>33003.4116</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>13373.2173</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>-0.7024</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>-0.1319</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>12.9634</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>13.472</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>51.4865</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>-25.0511</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>427.929</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>218.02</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>42.867</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>57.227</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>15.662</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>363.318</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>5699.147</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>1881.959</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>0.1002</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>11.8464</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>6.7108</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>165.9953</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>-147.4381</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>314.521</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>199.239</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>11.881</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>34.675</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>15.557</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>269.551</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>5664.051</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>1853.88</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0.0064</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>13.295</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>7.1295</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>144.5276</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>-124.1032</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>362.011</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>211.94</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1.842</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>50.23</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>15.963</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>245.158</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>5766.065</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>1855.722</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>10.7887</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>6.8412</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>111.7138</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>-94.0839</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>472.7198</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>237.0251</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>44.1944</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>52.9387</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20.3805</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>238.7387</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>5770.1542</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>1894.2679</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>0.0935</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0.0077</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0.0236</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>10.0393</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>7.0533</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>93.9109</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>-76.8184</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -1781,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:U89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6117,77 +6117,77 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2344.842</t>
+          <t>666.595</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1355.983</t>
+          <t>508.519</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>55.029</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1319.728</t>
+          <t>690.047</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>131.598</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2054.776</t>
+          <t>1320.651</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>38766.715</t>
+          <t>22906.168</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>8750.937</t>
+          <t>5018.146</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.0154</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.0009</t>
+          <t>0.0024</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.0041</t>
+          <t>0.0111</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>47.3023</t>
+          <t>90.6937</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>8.7059</t>
+          <t>10.4955</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>131.5497</t>
+          <t>239.6632</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>-75.5416</t>
+          <t>-138.4739</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6224,77 +6224,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1709.084</t>
+          <t>632.841</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1068.566</t>
+          <t>402.241</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-324.379</t>
+          <t>-407.99</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1178.171</t>
+          <t>356.836</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>119.126</t>
+          <t>61.041</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1621.867</t>
+          <t>1288.561</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>38218.557</t>
+          <t>23480.262</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8416.257</t>
+          <t>4598.673</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-0.1898</t>
+          <t>-0.6447</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-0.0084</t>
+          <t>-0.0176</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-0.0378</t>
+          <t>-0.0848</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>66.5002</t>
+          <t>75.2688</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>10.6759</t>
+          <t>13.4429</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>156.553</t>
+          <t>295.1443</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>-79.3769</t>
+          <t>-206.4327</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6331,77 +6331,77 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1751.875</t>
+          <t>830.933</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1139.186</t>
+          <t>541.069</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-422.865</t>
+          <t>-304.231</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1153.552</t>
+          <t>391.843</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>124.156</t>
+          <t>60.491</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1869.877</t>
+          <t>1079.508</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>38640.11</t>
+          <t>23205.748</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>7941.989</t>
+          <t>4270.658</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>-0.2414</t>
+          <t>-0.3661</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>-0.011</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>-0.0517</t>
+          <t>-0.0686</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>61.2254</t>
+          <t>41.4465</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>9.8237</t>
+          <t>10.3323</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>140.9956</t>
+          <t>201.3258</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>-69.9465</t>
+          <t>-149.5471</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6438,77 +6438,77 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3118.196</t>
+          <t>1297.049</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1814.581</t>
+          <t>591.989</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>240.259</t>
+          <t>-366.781</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1482.137</t>
+          <t>437.811</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>133.654</t>
+          <t>64.645</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2068.782</t>
+          <t>1120.696</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>39722.107</t>
+          <t>23784.095</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8261.867</t>
+          <t>3894.707</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.0771</t>
+          <t>-0.2828</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.0061</t>
+          <t>-0.0156</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>-0.0898</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>38.882</t>
+          <t>29.4238</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>6.5355</t>
+          <t>9.7236</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>99.8458</t>
+          <t>170.965</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>-54.4283</t>
+          <t>-131.8176</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -6517,12 +6517,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6537,77 +6537,77 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2135.663</t>
+          <t>1112.198</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>836.589</t>
+          <t>618.443</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>362.736</t>
+          <t>-145.62</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>160.189</t>
+          <t>474.284</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>41.126</t>
+          <t>62.979</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>175.013</t>
+          <t>1183.463</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>25917.3</t>
+          <t>23633.973</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>9919.18</t>
+          <t>3745.462</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>-0.1309</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>0.0139</t>
+          <t>-0.0061</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0.0374</t>
+          <t>-0.0381</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>8.0622</t>
+          <t>36.9037</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>4.5153</t>
+          <t>9.2864</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>23.7225</t>
+          <t>167.6584</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>-11.145</t>
+          <t>-121.4683</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -6624,12 +6624,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6644,77 +6644,77 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1753.339</t>
+          <t>1033.032</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>792.994</t>
+          <t>646.479</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>69.78</t>
+          <t>-275.736</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>120.711</t>
+          <t>468.063</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>39.848</t>
+          <t>97.569</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>154.434</t>
+          <t>1340.928</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>25764.928</t>
+          <t>24406.326</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>9508.7</t>
+          <t>3382.117</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>0.0398</t>
+          <t>-0.2669</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>0.0027</t>
+          <t>-0.0115</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>0.0072</t>
+          <t>-0.0774</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>7.2895</t>
+          <t>41.5058</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>4.6461</t>
+          <t>11.2996</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>18.9028</t>
+          <t>177.6698</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>-6.9673</t>
+          <t>-124.8645</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6731,12 +6731,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6751,77 +6751,77 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1788.638</t>
+          <t>1257.963</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>801.101</t>
+          <t>721.753</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>59.797</t>
+          <t>-183.952</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>155.074</t>
+          <t>479.575</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>42.315</t>
+          <t>96.346</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>180.07</t>
+          <t>1499.649</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>25461.134</t>
+          <t>25174.767</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>9481.112</t>
+          <t>4939.511</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0.0334</t>
+          <t>-0.1462</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>0.0023</t>
+          <t>-0.0074</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>0.0063</t>
+          <t>-0.0442</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>7.0926</t>
+          <t>34.6523</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>4.7179</t>
+          <t>12.3589</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>19.2075</t>
+          <t>181.0405</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>-7.3971</t>
+          <t>-134.0293</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -6838,12 +6838,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ERW</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6858,77 +6858,77 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2259.7525</t>
+          <t>1700.886</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>834.3435</t>
+          <t>864.34</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>412.4433</t>
+          <t>58.161</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>232.438</t>
+          <t>533.587</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>40.396</t>
+          <t>108.936</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>257.323</t>
+          <t>1924.155</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>26459.9264</t>
+          <t>26229.168</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>9787.1647</t>
+          <t>5044.523</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.1825</t>
+          <t>0.0342</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.0159</t>
+          <t>0.0023</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.0428</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>7.8883</t>
+          <t>27.4007</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>4.5601</t>
+          <t>10.9251</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>24.1149</t>
+          <t>182.2142</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>-11.6665</t>
+          <t>-143.8884</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -6937,12 +6937,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6957,77 +6957,77 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>97.8812</t>
+          <t>1688.672</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>53.115</t>
+          <t>897.178</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14.114</t>
+          <t>11.324</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>16.1787</t>
+          <t>608.309</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.3477</t>
+          <t>101.163</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>29.991</t>
+          <t>1590.817</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>669.2441</t>
+          <t>26120.156</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>452.6589</t>
+          <t>4996.057</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.0067</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.0207</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.0317</t>
+          <t>0.0023</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>13.5146</t>
+          <t>30.4294</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2.5197</t>
+          <t>10.538</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>59.3484</t>
+          <t>176.3014</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>-43.3141</t>
+          <t>-135.334</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -7044,12 +7044,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7064,77 +7064,77 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>75.445</t>
+          <t>1348.349</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>48.0476</t>
+          <t>772.196</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3.6651</t>
+          <t>-193.65</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>551.16</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.2802</t>
+          <t>96.155</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>32.1413</t>
+          <t>1583.687</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>668.5211</t>
+          <t>26372.37</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>456.324</t>
+          <t>4779.847</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.0486</t>
+          <t>-0.1436</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.0055</t>
+          <t>-0.0074</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.0081</t>
+          <t>-0.0396</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>18.0195</t>
+          <t>39.1262</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2.4886</t>
+          <t>11.6265</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>58.8379</t>
+          <t>187.0509</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>-38.3298</t>
+          <t>-136.2981</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -7151,12 +7151,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7171,77 +7171,77 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>95.0862</t>
+          <t>1415.732</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>57.5382</t>
+          <t>843.255</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>11.84</t>
+          <t>-253.504</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>12.9018</t>
+          <t>541.537</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>104.491</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>38.2079</t>
+          <t>1535.035</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>669.4754</t>
+          <t>26866.736</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>468.164</t>
+          <t>4459.141</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>0.1245</t>
+          <t>-0.1791</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>0.0177</t>
+          <t>-0.0095</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0.0256</t>
+          <t>-0.0549</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>12.8692</t>
+          <t>35.5039</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1.9259</t>
+          <t>10.9453</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>56.242</t>
+          <t>170.1279</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>-41.447</t>
+          <t>-123.6786</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -7258,12 +7258,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7278,77 +7278,77 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>94.8345</t>
+          <t>1909.087</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>55.0352</t>
+          <t>1100.194</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>10.1986</t>
+          <t>-148.236</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>10.6145</t>
+          <t>588.034</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1.6372</t>
+          <t>111.339</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>30.4437</t>
+          <t>1963.555</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>645.3267</t>
+          <t>27921.871</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>476.4493</t>
+          <t>4313.116</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>0.1075</t>
+          <t>-0.0776</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>0.0155</t>
+          <t>-0.0054</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>0.0216</t>
+          <t>-0.0338</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>11.4067</t>
+          <t>27.2173</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2.3118</t>
+          <t>9.024</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>57.3811</t>
+          <t>146.2789</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>-43.6625</t>
+          <t>-110.0375</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -7357,12 +7357,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7377,77 +7377,77 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>37267.312</t>
+          <t>2105.334</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20008.898</t>
+          <t>1105.459</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>611.516</t>
+          <t>126.005</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>14945.937</t>
+          <t>696.411</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4088.494</t>
+          <t>110.28</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>22052.993</t>
+          <t>1958.66</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>355544.01</t>
+          <t>29137.063</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>98317.427</t>
+          <t>4358.869</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>0.0164</t>
+          <t>0.0599</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>0.0017</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>0.0062</t>
+          <t>0.0291</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>34.9162</t>
+          <t>27.4541</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>18.0058</t>
+          <t>9.0215</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>104.5056</t>
+          <t>159.6619</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>-51.5836</t>
+          <t>-123.1863</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -7464,12 +7464,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7484,77 +7484,77 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>43497.069</t>
+          <t>1561.562</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>22101.435</t>
+          <t>917.935</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3322.548</t>
+          <t>-136.814</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>15751.811</t>
+          <t>633.355</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4157.115</t>
+          <t>103.673</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>24610.107</t>
+          <t>1985.955</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>366301.08</t>
+          <t>36091.311</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>99185.386</t>
+          <t>9148.35</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>0.0764</t>
+          <t>-0.0876</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>0.0092</t>
+          <t>-0.0042</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.0336</t>
+          <t>-0.0203</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>32.1113</t>
+          <t>38.746</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>16.9752</t>
+          <t>10.6052</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>96.0649</t>
+          <t>195.5258</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>-46.9784</t>
+          <t>-146.1746</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -7571,12 +7571,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7591,77 +7591,77 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>41174.584</t>
+          <t>1441.319</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>21956.753</t>
+          <t>888.69</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2667.974</t>
+          <t>-571.999</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>17466.545</t>
+          <t>605.209</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4137.789</t>
+          <t>113.651</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>23955.136</t>
+          <t>1551.973</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>356649.372</t>
+          <t>36535.809</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>94833.336</t>
+          <t>8405.571</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>0.0648</t>
+          <t>-0.3969</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>0.0074</t>
+          <t>-0.0158</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>0.0275</t>
+          <t>-0.0652</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>37.1113</t>
+          <t>39.529</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>17.3781</t>
+          <t>11.249</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>101.7455</t>
+          <t>183.1287</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>-47.2561</t>
+          <t>-132.3507</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -7678,12 +7678,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7698,77 +7698,77 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>43865.7491</t>
+          <t>5972.06</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>22154.6994</t>
+          <t>4316.017</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3237.2946</t>
+          <t>431.441</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>15911.6016</t>
+          <t>1145.08</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3921.4803</t>
+          <t>130.736</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>25606.359</t>
+          <t>1909.206</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>357329.6666</t>
+          <t>38270.77</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>96985.6572</t>
+          <t>8788.435</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>0.0738</t>
+          <t>0.0722</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>0.0091</t>
+          <t>0.0115</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>0.0502</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>35.0021</t>
+          <t>13.4817</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>16.7335</t>
+          <t>2.6047</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>102.905</t>
+          <t>36.8892</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>-51.1693</t>
+          <t>-20.8028</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -7777,7 +7777,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7797,77 +7797,77 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>789.301</t>
+          <t>2344.842</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>332.6197</t>
+          <t>1355.983</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>193.8595</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>89.5299</t>
+          <t>1319.728</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>23.1416</t>
+          <t>131.598</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>268.2755</t>
+          <t>2054.776</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>5725.7918</t>
+          <t>38766.715</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2677.6813</t>
+          <t>8750.937</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>0.2456</t>
+          <t>0.0154</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>0.0009</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>0.0751</t>
+          <t>0.0041</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>9.9049</t>
+          <t>47.3023</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>7.0353</t>
+          <t>8.7059</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>87.0016</t>
+          <t>131.5497</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>-70.0614</t>
+          <t>-75.5416</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -7884,7 +7884,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7904,77 +7904,77 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>433.486</t>
+          <t>1709.084</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>280.8156</t>
+          <t>1068.566</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-21.6962</t>
+          <t>-324.379</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>67.4259</t>
+          <t>1178.171</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20.6785</t>
+          <t>119.126</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>280.6725</t>
+          <t>1621.867</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>5670.2721</t>
+          <t>38218.557</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2655.9851</t>
+          <t>8416.257</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>-0.0501</t>
+          <t>-0.1898</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>-0.0038</t>
+          <t>-0.0084</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>-0.0081</t>
+          <t>-0.0378</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>16.4745</t>
+          <t>66.5002</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>7.1001</t>
+          <t>10.6759</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>88.945</t>
+          <t>156.553</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>-65.3703</t>
+          <t>-79.3769</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -7991,7 +7991,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8011,77 +8011,77 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>478.3312</t>
+          <t>1751.875</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>331.1909</t>
+          <t>1139.186</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-26.0182</t>
+          <t>-422.865</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>78.9921</t>
+          <t>1153.552</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>32.8947</t>
+          <t>124.156</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>503.8692</t>
+          <t>1869.877</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>5846.5963</t>
+          <t>38640.11</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2629.9669</t>
+          <t>7941.989</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>-0.0544</t>
+          <t>-0.2414</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>-0.0045</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>-0.0098</t>
+          <t>-0.0517</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>14.0807</t>
+          <t>61.2254</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>7.4409</t>
+          <t>9.8237</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>108.9671</t>
+          <t>140.9956</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>-87.4455</t>
+          <t>-69.9465</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -8098,7 +8098,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>DUSIT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8118,77 +8118,77 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>823.8227</t>
+          <t>3118.196</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>387.9619</t>
+          <t>1814.581</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>167.549</t>
+          <t>240.259</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>107.3732</t>
+          <t>1482.137</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>36.3419</t>
+          <t>133.654</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>598.6416</t>
+          <t>2068.782</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>6047.5464</t>
+          <t>39722.107</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2797.2204</t>
+          <t>8261.867</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>0.0771</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>0.0282</t>
+          <t>0.0061</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0.0617</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>10.4061</t>
+          <t>38.882</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>8.2093</t>
+          <t>6.5355</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>130.7229</t>
+          <t>99.8458</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>-112.1075</t>
+          <t>-54.4283</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8217,77 +8217,77 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>659.954</t>
+          <t>2135.663</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>188.579</t>
+          <t>836.589</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>159.821</t>
+          <t>362.736</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>61.376</t>
+          <t>160.189</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>27.765</t>
+          <t>41.126</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>162.319</t>
+          <t>175.013</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8195.463</t>
+          <t>25917.3</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>7595.093</t>
+          <t>9919.18</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>0.2422</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>0.0197</t>
+          <t>0.0139</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>0.0213</t>
+          <t>0.0374</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>9.6443</t>
+          <t>8.0622</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>13.4817</t>
+          <t>4.5153</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>94.8007</t>
+          <t>23.7225</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>-71.6747</t>
+          <t>-11.145</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -8297,14 +8297,14 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8324,77 +8324,77 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>401.638</t>
+          <t>1753.339</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>145.967</t>
+          <t>792.994</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-40.895</t>
+          <t>69.78</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>42.973</t>
+          <t>120.711</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>27.609</t>
+          <t>39.848</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>137.849</t>
+          <t>154.434</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>7984.993</t>
+          <t>25764.928</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>7468.704</t>
+          <t>9508.7</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>-0.1018</t>
+          <t>0.0398</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>-0.0051</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>-0.0054</t>
+          <t>0.0072</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>11.8213</t>
+          <t>7.2895</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>17.2609</t>
+          <t>4.6461</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>93.5667</t>
+          <t>18.9028</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>-64.4845</t>
+          <t>-6.9673</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -8404,14 +8404,14 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8431,77 +8431,77 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>467.158</t>
+          <t>1788.638</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>166.785</t>
+          <t>801.101</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>87.081</t>
+          <t>59.797</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>57.888</t>
+          <t>155.074</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>25.864</t>
+          <t>42.315</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>132.189</t>
+          <t>180.07</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>8034.036</t>
+          <t>25461.134</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>7505.949</t>
+          <t>9481.112</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.0334</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0023</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0063</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>9.9316</t>
+          <t>7.0926</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>14.7481</t>
+          <t>4.7179</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>74.4776</t>
+          <t>19.2075</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>-49.798</t>
+          <t>-7.3971</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -8511,14 +8511,14 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8538,77 +8538,77 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>624.6388</t>
+          <t>2259.7525</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>193.8865</t>
+          <t>834.3435</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>34.8966</t>
+          <t>412.4433</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>90.0129</t>
+          <t>232.438</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>27.8828</t>
+          <t>40.396</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>259.24</t>
+          <t>257.323</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8261.9755</t>
+          <t>26459.9264</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>7509.0939</t>
+          <t>9787.1647</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>0.0559</t>
+          <t>0.1825</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>0.0043</t>
+          <t>0.0159</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>0.0046</t>
+          <t>0.0428</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>10.8918</t>
+          <t>7.8883</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>12.7515</t>
+          <t>4.5601</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>92.8674</t>
+          <t>24.1149</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>-69.2241</t>
+          <t>-11.6665</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -8617,7 +8617,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8637,77 +8637,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2649.224</t>
+          <t>97.8812</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1582.956</t>
+          <t>53.115</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>175.544</t>
+          <t>14.114</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>502.606</t>
+          <t>16.1787</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>223.595</t>
+          <t>1.3477</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>865.016</t>
+          <t>29.991</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>36612.798</t>
+          <t>669.2441</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>16235.452</t>
+          <t>452.6589</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>0.0663</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>0.0048</t>
+          <t>0.0207</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0317</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>16.6185</t>
+          <t>13.5146</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>12.9589</t>
+          <t>2.5197</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>52.3113</t>
+          <t>59.3484</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>-22.7338</t>
+          <t>-43.3141</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -8717,14 +8717,14 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8744,77 +8744,77 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2431.997</t>
+          <t>75.445</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1528.045</t>
+          <t>48.0476</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>3.6651</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>331.082</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>220.973</t>
+          <t>1.2802</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>819.563</t>
+          <t>32.1413</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>35934.539</t>
+          <t>668.5211</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>15859.504</t>
+          <t>456.324</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0486</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>0.0055</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>0.0015</t>
+          <t>0.0081</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>15.5974</t>
+          <t>18.0195</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>13.2377</t>
+          <t>2.4886</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>50.1611</t>
+          <t>58.8379</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>-21.3259</t>
+          <t>-38.3298</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -8824,14 +8824,14 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8851,77 +8851,77 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2604.449</t>
+          <t>95.0862</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1544.681</t>
+          <t>57.5382</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>128.587</t>
+          <t>11.84</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>361.827</t>
+          <t>12.9018</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>231.174</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>807.788</t>
+          <t>38.2079</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>35409.916</t>
+          <t>669.4754</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>15649.4</t>
+          <t>468.164</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>0.0494</t>
+          <t>0.1245</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0177</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>0.0082</t>
+          <t>0.0256</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>12.2382</t>
+          <t>12.8692</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>13.4648</t>
+          <t>1.9259</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>48.4619</t>
+          <t>56.242</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>-22.7589</t>
+          <t>-41.447</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -8931,14 +8931,14 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8958,77 +8958,77 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2725.5033</t>
+          <t>94.8345</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1623.9576</t>
+          <t>55.0352</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-1914.3989</t>
+          <t>10.1986</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>406.2581</t>
+          <t>10.6145</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>244.4322</t>
+          <t>1.6372</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>1009.863</t>
+          <t>30.4437</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>33003.4116</t>
+          <t>645.3267</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>13373.2173</t>
+          <t>476.4493</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>-0.7024</t>
+          <t>0.1075</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>0.0155</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>-0.1319</t>
+          <t>0.0216</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>12.9634</t>
+          <t>11.4067</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>13.472</t>
+          <t>2.3118</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>51.4865</t>
+          <t>57.3811</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>-25.0511</t>
+          <t>-43.6625</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -9037,7 +9037,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9057,77 +9057,77 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>427.929</t>
+          <t>37267.312</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>218.02</t>
+          <t>20008.898</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>42.867</t>
+          <t>611.516</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>57.227</t>
+          <t>14945.937</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>4088.494</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>363.318</t>
+          <t>22052.993</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>5699.147</t>
+          <t>355544.01</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1881.959</t>
+          <t>98317.427</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>0.1002</t>
+          <t>0.0164</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>0.0017</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.0062</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>11.8464</t>
+          <t>34.9162</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>6.7108</t>
+          <t>18.0058</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>165.9953</t>
+          <t>104.5056</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>-147.4381</t>
+          <t>-51.5836</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -9144,7 +9144,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9164,77 +9164,77 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>314.521</t>
+          <t>43497.069</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>199.239</t>
+          <t>22101.435</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>11.881</t>
+          <t>3322.548</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>34.675</t>
+          <t>15751.811</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>15.557</t>
+          <t>4157.115</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>269.551</t>
+          <t>24610.107</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>5664.051</t>
+          <t>366301.08</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1853.88</t>
+          <t>99185.386</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>0.0378</t>
+          <t>0.0764</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>0.0092</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>0.0064</t>
+          <t>0.0336</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>13.295</t>
+          <t>32.1113</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>7.1295</t>
+          <t>16.9752</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>144.5276</t>
+          <t>96.0649</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>-124.1032</t>
+          <t>-46.9784</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -9251,7 +9251,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9271,77 +9271,77 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>362.011</t>
+          <t>41174.584</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>21956.753</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>2667.974</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>17466.545</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15.963</t>
+          <t>4137.789</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>245.158</t>
+          <t>23955.136</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>5766.065</t>
+          <t>356649.372</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1855.722</t>
+          <t>94833.336</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>0.0051</t>
+          <t>0.0648</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0074</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.0275</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>10.7887</t>
+          <t>37.1113</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>6.8412</t>
+          <t>17.3781</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>111.7138</t>
+          <t>101.7455</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>-94.0839</t>
+          <t>-47.2561</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -9358,7 +9358,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9378,81 +9378,1761 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>472.7198</t>
+          <t>43865.7491</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>237.0251</t>
+          <t>22154.6994</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>44.1944</t>
+          <t>3237.2946</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>52.9387</t>
+          <t>15911.6016</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20.3805</t>
+          <t>3921.4803</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>238.7387</t>
+          <t>25606.359</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>5770.1542</t>
+          <t>357329.6666</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1894.2679</t>
+          <t>96985.6572</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>0.0935</t>
+          <t>0.0738</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>0.0091</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>0.0236</t>
+          <t>0.0338</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>10.0393</t>
+          <t>35.0021</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>7.0533</t>
+          <t>16.7335</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>93.9109</t>
+          <t>102.905</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>-76.8184</t>
+          <t>-51.1693</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>789.301</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>332.6197</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>193.8595</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>89.5299</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>23.1416</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>268.2755</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>5725.7918</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2677.6813</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>0.2456</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0.0338</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0.0751</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>9.9049</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>7.0353</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>87.0016</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>-70.0614</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>433.486</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>280.8156</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-21.6962</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>67.4259</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20.6785</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>280.6725</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>5670.2721</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2655.9851</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>-0.0501</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>-0.0038</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>-0.0081</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>16.4745</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>7.1001</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>88.945</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>-65.3703</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>478.3312</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>331.1909</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-26.0182</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>78.9921</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>32.8947</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>503.8692</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>5846.5963</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2629.9669</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>-0.0544</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>-0.0045</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>-0.0098</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>14.0807</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>7.4409</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>108.9671</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>-87.4455</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>823.8227</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>387.9619</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>167.549</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>107.3732</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>36.3419</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>598.6416</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>6047.5464</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2797.2204</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>0.2034</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0.0282</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0.0617</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>10.4061</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>8.2093</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>130.7229</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>-112.1075</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>659.954</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>188.579</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>159.821</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>61.376</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>27.765</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>162.319</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>8195.463</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>7595.093</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>0.2422</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0.0197</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0.0213</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>9.6443</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>13.4817</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>94.8007</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>-71.6747</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>401.638</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>145.967</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-40.895</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>42.973</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>27.609</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>137.849</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>7984.993</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>7468.704</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>-0.1018</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>-0.0051</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>-0.0054</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>11.8213</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>17.2609</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>93.5667</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>-64.4845</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>467.158</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>166.785</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>87.081</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>57.888</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>25.864</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>132.189</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>8034.036</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>7505.949</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>0.1864</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0.0116</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>9.9316</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>14.7481</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>74.4776</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>-49.798</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>624.6388</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>193.8865</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>34.8966</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>90.0129</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>27.8828</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>259.24</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>8261.9755</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>7509.0939</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>0.0559</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0.0043</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0.0046</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>10.8918</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>12.7515</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>92.8674</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>-69.2241</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2649.224</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1582.956</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>175.544</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>502.606</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>223.595</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>865.016</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>36612.798</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>16235.452</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>0.0663</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0.0048</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>16.6185</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>12.9589</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>52.3113</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>-22.7338</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2431.997</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1528.045</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>331.082</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>220.973</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>819.563</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>35934.539</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>15859.504</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>15.5974</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>13.2377</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>50.1611</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>-21.3259</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2604.449</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1544.681</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>128.587</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>361.827</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>231.174</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>807.788</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>35409.916</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>15649.4</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>0.0494</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0.0082</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>12.2382</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>13.4648</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>48.4619</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>-22.7589</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2725.5033</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1623.9576</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-1914.3989</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>406.2581</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>244.4322</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1009.863</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>33003.4116</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>13373.2173</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>-0.7024</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>-0.1319</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>12.9634</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>13.472</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>51.4865</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>-25.0511</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>427.929</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>218.02</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>42.867</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>57.227</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>15.662</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>363.318</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>5699.147</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>1881.959</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>0.1002</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>11.8464</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>6.7108</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>165.9953</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>-147.4381</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>314.521</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>199.239</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>11.881</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>34.675</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>15.557</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>269.551</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>5664.051</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>1853.88</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0.0064</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>13.295</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>7.1295</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>144.5276</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>-124.1032</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>362.011</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>211.94</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1.842</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>50.23</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>15.963</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>245.158</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>5766.065</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>1855.722</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>10.7887</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>6.8412</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>111.7138</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>-94.0839</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>472.7198</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>237.0251</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>44.1944</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>52.9387</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>20.3805</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>238.7387</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>5770.1542</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>1894.2679</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>0.0935</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0.0077</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0.0236</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>10.0393</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>7.0533</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>93.9109</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>-76.8184</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -1781,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U89"/>
+  <dimension ref="A1:U105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8217,77 +8217,77 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2135.663</t>
+          <t>390.059</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>836.589</t>
+          <t>315.026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>362.736</t>
+          <t>-512.877</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>160.189</t>
+          <t>66.958</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>41.126</t>
+          <t>40.275</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>175.013</t>
+          <t>103.802</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>25917.3</t>
+          <t>21048.98</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>9919.18</t>
+          <t>3439.943</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>-1.3149</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>0.0139</t>
+          <t>-0.0243</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>0.0374</t>
+          <t>-0.1392</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>8.0622</t>
+          <t>16.5604</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>4.5153</t>
+          <t>12.3536</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>23.7225</t>
+          <t>35.4925</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>-11.145</t>
+          <t>-6.5786</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8324,77 +8324,77 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1753.339</t>
+          <t>269.132</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>792.994</t>
+          <t>284.888</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>69.78</t>
+          <t>-716.788</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>120.711</t>
+          <t>47.166</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>39.848</t>
+          <t>38.527</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>154.434</t>
+          <t>70.728</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>25764.928</t>
+          <t>23603.712</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>9508.7</t>
+          <t>6959.668</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>0.0398</t>
+          <t>-2.6633</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>0.0027</t>
+          <t>-0.0321</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>0.0072</t>
+          <t>-0.1378</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>7.2895</t>
+          <t>19.294</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>4.6461</t>
+          <t>12.5856</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>18.9028</t>
+          <t>27.8745</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>-6.9673</t>
+          <t>4.0051</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8431,77 +8431,77 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1788.638</t>
+          <t>253.762</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>801.101</t>
+          <t>286.682</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>59.797</t>
+          <t>-667.617</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>155.074</t>
+          <t>53.535</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>42.315</t>
+          <t>37.071</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>180.07</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>25461.134</t>
+          <t>23296.713</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>9481.112</t>
+          <t>6309.161</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>0.0334</t>
+          <t>-2.6309</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>0.0023</t>
+          <t>-0.0285</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>0.0063</t>
+          <t>-0.1006</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>7.0926</t>
+          <t>18.2543</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>4.7179</t>
+          <t>12.1302</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>19.2075</t>
+          <t>22.5855</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>-7.3971</t>
+          <t>7.7989</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -8538,77 +8538,77 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2259.7525</t>
+          <t>728.3045</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>834.3435</t>
+          <t>397.5638</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>412.4433</t>
+          <t>-258.09</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>232.438</t>
+          <t>99.8541</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>40.396</t>
+          <t>39.3064</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>257.323</t>
+          <t>142.6759</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>26459.9264</t>
+          <t>22450.2128</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>9787.1647</t>
+          <t>6022.7191</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>0.1825</t>
+          <t>-0.3544</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>0.0159</t>
+          <t>-0.0113</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>0.0428</t>
+          <t>-0.0419</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>7.8883</t>
+          <t>9.6881</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>4.5601</t>
+          <t>8.8372</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>24.1149</t>
+          <t>24.6111</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>-11.6665</t>
+          <t>-6.0857</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -8617,12 +8617,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -8637,77 +8637,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>97.8812</t>
+          <t>646.094</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>53.115</t>
+          <t>404.82</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14.114</t>
+          <t>-324.862</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>16.1787</t>
+          <t>116.99</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1.3477</t>
+          <t>35.258</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>29.991</t>
+          <t>106.87</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>669.2441</t>
+          <t>22388.076</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>452.6589</t>
+          <t>5657.401</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>-0.5028</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>0.0207</t>
+          <t>-0.0145</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>0.0317</t>
+          <t>-0.0556</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>13.5146</t>
+          <t>15.103</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2.5197</t>
+          <t>8.2886</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>59.3484</t>
+          <t>27.7397</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>-43.3141</t>
+          <t>-4.3481</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -8724,12 +8724,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -8744,77 +8744,77 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>75.445</t>
+          <t>1006.085</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>48.0476</t>
+          <t>519.988</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3.6651</t>
+          <t>-143.041</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>115.151</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1.2802</t>
+          <t>37.341</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>32.1413</t>
+          <t>126.184</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>668.5211</t>
+          <t>21250.682</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>456.324</t>
+          <t>5551.743</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>0.0486</t>
+          <t>-0.1422</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>0.0055</t>
+          <t>-0.0066</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>0.0081</t>
+          <t>-0.0255</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>18.0195</t>
+          <t>10.4985</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2.4886</t>
+          <t>6.3526</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>58.8379</t>
+          <t>20.3927</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>-38.3298</t>
+          <t>-3.5416</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -8831,12 +8831,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -8851,77 +8851,77 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>95.0862</t>
+          <t>1289.39</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>57.5382</t>
+          <t>607.211</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>11.84</t>
+          <t>-5.353</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>12.9018</t>
+          <t>145.022</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>38.492</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>38.2079</t>
+          <t>142.653</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>669.4754</t>
+          <t>21433.702</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>468.164</t>
+          <t>5566.029</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>0.1245</t>
+          <t>-0.0042</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>0.0177</t>
+          <t>-0.0003</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>0.0256</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>12.8692</t>
+          <t>9.2819</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>1.9259</t>
+          <t>5.7448</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>56.242</t>
+          <t>20.3661</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>-41.447</t>
+          <t>-5.3394</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -8938,12 +8938,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MANRIN</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8958,77 +8958,77 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>94.8345</t>
+          <t>1775.7185</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>55.0352</t>
+          <t>750.1329</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10.1986</t>
+          <t>260.1939</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>10.6145</t>
+          <t>159.8053</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1.6372</t>
+          <t>43.4666</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>30.4437</t>
+          <t>234.5129</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>645.3267</t>
+          <t>21711.8116</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>476.4493</t>
+          <t>5721.6263</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>0.1075</t>
+          <t>0.1465</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>0.0155</t>
+          <t>0.0121</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>0.0216</t>
+          <t>0.0461</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>11.4067</t>
+          <t>7.8966</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2.3118</t>
+          <t>5.0259</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>57.3811</t>
+          <t>23.1287</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>-43.6625</t>
+          <t>-10.2063</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -9037,12 +9037,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9057,77 +9057,77 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>37267.312</t>
+          <t>1774.625</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20008.898</t>
+          <t>775.229</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>611.516</t>
+          <t>237.391</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>14945.937</t>
+          <t>155.536</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>4088.494</t>
+          <t>37.421</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>22052.993</t>
+          <t>173.704</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>355544.01</t>
+          <t>21482.14</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>98317.427</t>
+          <t>5980.403</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>0.0164</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>0.0017</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>0.0062</t>
+          <t>0.0406</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>34.9162</t>
+          <t>7.9962</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>18.0058</t>
+          <t>4.6953</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>104.5056</t>
+          <t>23.6959</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>-51.5836</t>
+          <t>-11.0043</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -9144,12 +9144,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9164,77 +9164,77 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>43497.069</t>
+          <t>1641.935</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>22101.435</t>
+          <t>726.693</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3322.548</t>
+          <t>143.879</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>15751.811</t>
+          <t>129.797</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>4157.115</t>
+          <t>37.818</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>24610.107</t>
+          <t>150.803</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>366301.08</t>
+          <t>21552.764</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>99185.386</t>
+          <t>6166.695</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>0.0764</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>0.0092</t>
+          <t>0.0067</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>0.0336</t>
+          <t>0.0237</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>32.1113</t>
+          <t>7.9069</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>16.9752</t>
+          <t>4.7109</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>96.0649</t>
+          <t>20.3182</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>-46.9784</t>
+          <t>-7.7003</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -9251,12 +9251,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -9271,77 +9271,77 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>41174.584</t>
+          <t>1742.8</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>21956.753</t>
+          <t>757.077</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2667.974</t>
+          <t>155.228</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>17466.545</t>
+          <t>127.605</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4137.789</t>
+          <t>41.197</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>23955.136</t>
+          <t>180.31</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>356649.372</t>
+          <t>23814.068</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>94833.336</t>
+          <t>6277.706</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>0.0648</t>
+          <t>0.0891</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>0.0074</t>
+          <t>0.0068</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>0.0275</t>
+          <t>0.0249</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>37.1113</t>
+          <t>6.7939</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>17.3781</t>
+          <t>4.801</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>101.7455</t>
+          <t>20.1184</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>-47.2561</t>
+          <t>-8.5235</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -9358,12 +9358,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -9378,77 +9378,77 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>43865.7491</t>
+          <t>1886.9297</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>22154.6994</t>
+          <t>775.5187</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3237.2946</t>
+          <t>223.3788</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>15911.6016</t>
+          <t>169.8269</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3921.4803</t>
+          <t>48.963</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>25606.359</t>
+          <t>226.853</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>357329.6666</t>
+          <t>23674.9307</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>96985.6572</t>
+          <t>6369.9451</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>0.0738</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>0.0091</t>
+          <t>0.0094</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>35.0021</t>
+          <t>7.2509</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>16.7335</t>
+          <t>5.3479</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>102.905</t>
+          <t>24.1509</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>-51.1693</t>
+          <t>-11.5522</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -9457,12 +9457,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -9477,77 +9477,77 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>789.301</t>
+          <t>2119.357</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>332.6197</t>
+          <t>793.662</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>193.8595</t>
+          <t>428.404</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>89.5299</t>
+          <t>150.106</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>23.1416</t>
+          <t>42.976</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>268.2755</t>
+          <t>209.768</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>5725.7918</t>
+          <t>23907.039</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2677.6813</t>
+          <t>6831.886</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>0.2456</t>
+          <t>0.2021</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>0.0751</t>
+          <t>0.0649</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>9.9049</t>
+          <t>6.7931</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>7.0353</t>
+          <t>5.2129</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>87.0016</t>
+          <t>24.7561</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>-70.0614</t>
+          <t>-12.7501</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -9564,12 +9564,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -9584,77 +9584,77 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>433.486</t>
+          <t>1843.268</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>280.8156</t>
+          <t>809.742</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-21.6962</t>
+          <t>365.506</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>67.4259</t>
+          <t>143.792</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>20.6785</t>
+          <t>40.795</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>280.6725</t>
+          <t>192.776</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>5670.2721</t>
+          <t>25567.646</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2655.9851</t>
+          <t>7860.623</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>-0.0501</t>
+          <t>0.1983</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>-0.0038</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>-0.0081</t>
+          <t>0.0498</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>16.4745</t>
+          <t>7.2547</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>7.1001</t>
+          <t>4.7072</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>88.945</t>
+          <t>22.6192</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>-65.3703</t>
+          <t>-10.6574</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -9671,12 +9671,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -9691,77 +9691,77 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>478.3312</t>
+          <t>1856.024</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>331.1909</t>
+          <t>812.235</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-26.0182</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>78.9921</t>
+          <t>139.711</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>32.8947</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>503.8692</t>
+          <t>169.55</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>5846.5963</t>
+          <t>24928.592</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2629.9669</t>
+          <t>7834.106</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>-0.0544</t>
+          <t>0.0671</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>-0.0045</t>
+          <t>0.0049</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>-0.0098</t>
+          <t>0.0159</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>14.0807</t>
+          <t>7.0264</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>7.4409</t>
+          <t>4.676</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>108.9671</t>
+          <t>20.5199</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>-87.4455</t>
+          <t>-8.8176</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -9778,12 +9778,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -9798,77 +9798,77 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>823.8227</t>
+          <t>2235.2768</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>387.9619</t>
+          <t>860.3459</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>167.549</t>
+          <t>394.1058</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>107.3732</t>
+          <t>222.4384</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>36.3419</t>
+          <t>42.8166</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>598.6416</t>
+          <t>266.0093</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>6047.5464</t>
+          <t>26246.0777</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2797.2204</t>
+          <t>9491.8126</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>0.1763</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>0.0282</t>
+          <t>0.0154</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>0.0617</t>
+          <t>0.0455</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>10.4061</t>
+          <t>7.4527</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>8.2093</t>
+          <t>4.5226</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>130.7229</t>
+          <t>23.288</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>-112.1075</t>
+          <t>-11.3127</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -9877,7 +9877,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9897,77 +9897,77 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>659.954</t>
+          <t>2135.663</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>188.579</t>
+          <t>836.589</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>159.821</t>
+          <t>362.736</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>61.376</t>
+          <t>160.189</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>27.765</t>
+          <t>41.126</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>162.319</t>
+          <t>175.013</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>8195.463</t>
+          <t>25917.3</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>7595.093</t>
+          <t>9919.18</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>0.2422</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>0.0197</t>
+          <t>0.0139</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>0.0213</t>
+          <t>0.0374</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>9.6443</t>
+          <t>8.0622</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>13.4817</t>
+          <t>4.5153</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>94.8007</t>
+          <t>23.7225</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>-71.6747</t>
+          <t>-11.145</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -9977,14 +9977,14 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10004,77 +10004,77 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>401.638</t>
+          <t>1753.339</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>145.967</t>
+          <t>792.994</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-40.895</t>
+          <t>69.78</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>42.973</t>
+          <t>120.711</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>27.609</t>
+          <t>39.848</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>137.849</t>
+          <t>154.434</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>7984.993</t>
+          <t>25764.928</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>7468.704</t>
+          <t>9508.7</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>-0.1018</t>
+          <t>0.0398</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>-0.0051</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>-0.0054</t>
+          <t>0.0072</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>11.8213</t>
+          <t>7.2895</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>17.2609</t>
+          <t>4.6461</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>93.5667</t>
+          <t>18.9028</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>-64.4845</t>
+          <t>-6.9673</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -10084,14 +10084,14 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10111,77 +10111,77 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>467.158</t>
+          <t>1788.638</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>166.785</t>
+          <t>801.101</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>87.081</t>
+          <t>59.797</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>57.888</t>
+          <t>155.074</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>25.864</t>
+          <t>42.315</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>132.189</t>
+          <t>180.07</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>8034.036</t>
+          <t>25461.134</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>7505.949</t>
+          <t>9481.112</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.0334</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0023</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0063</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>9.9316</t>
+          <t>7.0926</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>14.7481</t>
+          <t>4.7179</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>74.4776</t>
+          <t>19.2075</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>-49.798</t>
+          <t>-7.3971</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -10191,14 +10191,14 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>ERW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10218,77 +10218,77 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>624.6388</t>
+          <t>2259.7525</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>193.8865</t>
+          <t>834.3435</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>34.8966</t>
+          <t>412.4433</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>90.0129</t>
+          <t>232.438</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>27.8828</t>
+          <t>40.396</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>259.24</t>
+          <t>257.323</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8261.9755</t>
+          <t>26459.9264</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>7509.0939</t>
+          <t>9787.1647</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>0.0559</t>
+          <t>0.1825</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>0.0043</t>
+          <t>0.0159</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>0.0046</t>
+          <t>0.0428</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>10.8918</t>
+          <t>7.8883</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>12.7515</t>
+          <t>4.5601</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>92.8674</t>
+          <t>24.1149</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>-69.2241</t>
+          <t>-11.6665</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -10297,7 +10297,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10317,77 +10317,77 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2649.224</t>
+          <t>97.8812</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1582.956</t>
+          <t>53.115</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>175.544</t>
+          <t>14.114</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>502.606</t>
+          <t>16.1787</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>223.595</t>
+          <t>1.3477</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>865.016</t>
+          <t>29.991</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>36612.798</t>
+          <t>669.2441</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>16235.452</t>
+          <t>452.6589</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>0.0663</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>0.0048</t>
+          <t>0.0207</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0317</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>16.6185</t>
+          <t>13.5146</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>12.9589</t>
+          <t>2.5197</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>52.3113</t>
+          <t>59.3484</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>-22.7338</t>
+          <t>-43.3141</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -10397,14 +10397,14 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10424,77 +10424,77 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2431.997</t>
+          <t>75.445</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1528.045</t>
+          <t>48.0476</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>3.6651</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>331.082</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>220.973</t>
+          <t>1.2802</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>819.563</t>
+          <t>32.1413</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>35934.539</t>
+          <t>668.5211</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>15859.504</t>
+          <t>456.324</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0486</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>0.0055</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>0.0015</t>
+          <t>0.0081</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>15.5974</t>
+          <t>18.0195</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>13.2377</t>
+          <t>2.4886</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>50.1611</t>
+          <t>58.8379</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>-21.3259</t>
+          <t>-38.3298</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -10504,14 +10504,14 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10531,77 +10531,77 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2604.449</t>
+          <t>95.0862</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1544.681</t>
+          <t>57.5382</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>128.587</t>
+          <t>11.84</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>361.827</t>
+          <t>12.9018</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>231.174</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>807.788</t>
+          <t>38.2079</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>35409.916</t>
+          <t>669.4754</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>15649.4</t>
+          <t>468.164</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>0.0494</t>
+          <t>0.1245</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0177</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>0.0082</t>
+          <t>0.0256</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>12.2382</t>
+          <t>12.8692</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>13.4648</t>
+          <t>1.9259</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>48.4619</t>
+          <t>56.242</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>-22.7589</t>
+          <t>-41.447</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -10611,14 +10611,14 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10638,77 +10638,77 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2725.5033</t>
+          <t>94.8345</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1623.9576</t>
+          <t>55.0352</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-1914.3989</t>
+          <t>10.1986</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>406.2581</t>
+          <t>10.6145</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>244.4322</t>
+          <t>1.6372</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>1009.863</t>
+          <t>30.4437</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>33003.4116</t>
+          <t>645.3267</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>13373.2173</t>
+          <t>476.4493</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>-0.7024</t>
+          <t>0.1075</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>0.0155</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>-0.1319</t>
+          <t>0.0216</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>12.9634</t>
+          <t>11.4067</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>13.472</t>
+          <t>2.3118</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>51.4865</t>
+          <t>57.3811</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>-25.0511</t>
+          <t>-43.6625</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -10717,7 +10717,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10737,77 +10737,77 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>427.929</t>
+          <t>37267.312</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>218.02</t>
+          <t>20008.898</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>42.867</t>
+          <t>611.516</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>57.227</t>
+          <t>14945.937</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>4088.494</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>363.318</t>
+          <t>22052.993</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>5699.147</t>
+          <t>355544.01</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1881.959</t>
+          <t>98317.427</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>0.1002</t>
+          <t>0.0164</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>0.0017</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.0062</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>11.8464</t>
+          <t>34.9162</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>6.7108</t>
+          <t>18.0058</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>165.9953</t>
+          <t>104.5056</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>-147.4381</t>
+          <t>-51.5836</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -10824,7 +10824,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10844,77 +10844,77 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>314.521</t>
+          <t>43497.069</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>199.239</t>
+          <t>22101.435</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>11.881</t>
+          <t>3322.548</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>34.675</t>
+          <t>15751.811</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>15.557</t>
+          <t>4157.115</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>269.551</t>
+          <t>24610.107</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>5664.051</t>
+          <t>366301.08</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>1853.88</t>
+          <t>99185.386</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>0.0378</t>
+          <t>0.0764</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>0.0092</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>0.0064</t>
+          <t>0.0336</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>13.295</t>
+          <t>32.1113</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>7.1295</t>
+          <t>16.9752</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>144.5276</t>
+          <t>96.0649</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>-124.1032</t>
+          <t>-46.9784</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -10931,7 +10931,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10951,77 +10951,77 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>362.011</t>
+          <t>41174.584</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>21956.753</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>2667.974</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>17466.545</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>15.963</t>
+          <t>4137.789</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>245.158</t>
+          <t>23955.136</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>5766.065</t>
+          <t>356649.372</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>1855.722</t>
+          <t>94833.336</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>0.0051</t>
+          <t>0.0648</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0074</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.0275</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>10.7887</t>
+          <t>37.1113</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>6.8412</t>
+          <t>17.3781</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>111.7138</t>
+          <t>101.7455</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>-94.0839</t>
+          <t>-47.2561</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -11038,7 +11038,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -11058,81 +11058,1761 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>472.7198</t>
+          <t>43865.7491</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>237.0251</t>
+          <t>22154.6994</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>44.1944</t>
+          <t>3237.2946</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>52.9387</t>
+          <t>15911.6016</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>20.3805</t>
+          <t>3921.4803</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>238.7387</t>
+          <t>25606.359</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>5770.1542</t>
+          <t>357329.6666</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>1894.2679</t>
+          <t>96985.6572</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>0.0935</t>
+          <t>0.0738</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>0.0091</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>0.0236</t>
+          <t>0.0338</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>10.0393</t>
+          <t>35.0021</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>7.0533</t>
+          <t>16.7335</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>93.9109</t>
+          <t>102.905</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>-76.8184</t>
+          <t>-51.1693</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>789.301</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>332.6197</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>193.8595</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>89.5299</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>23.1416</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>268.2755</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>5725.7918</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2677.6813</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>0.2456</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0.0338</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0.0751</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>9.9049</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>7.0353</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>87.0016</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>-70.0614</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>433.486</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>280.8156</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-21.6962</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>67.4259</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>20.6785</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>280.6725</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>5670.2721</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2655.9851</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>-0.0501</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>-0.0038</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>-0.0081</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>16.4745</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>7.1001</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>88.945</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>-65.3703</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>478.3312</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>331.1909</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-26.0182</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>78.9921</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>32.8947</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>503.8692</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>5846.5963</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2629.9669</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>-0.0544</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>-0.0045</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>-0.0098</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>14.0807</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>7.4409</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>108.9671</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>-87.4455</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>823.8227</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>387.9619</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>167.549</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>107.3732</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>36.3419</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>598.6416</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>6047.5464</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2797.2204</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>0.2034</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0.0282</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0.0617</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>10.4061</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>8.2093</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>130.7229</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>-112.1075</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>659.954</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>188.579</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>159.821</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>61.376</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>27.765</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>162.319</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>8195.463</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>7595.093</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>0.2422</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0.0197</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0.0213</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>9.6443</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>13.4817</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>94.8007</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>-71.6747</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>401.638</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>145.967</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-40.895</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>42.973</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>27.609</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>137.849</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>7984.993</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>7468.704</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>-0.1018</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>-0.0051</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>-0.0054</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>11.8213</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>17.2609</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>93.5667</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>-64.4845</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>467.158</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>166.785</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>87.081</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>57.888</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>25.864</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>132.189</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>8034.036</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>7505.949</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>0.1864</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0.0116</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>9.9316</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>14.7481</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>74.4776</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>-49.798</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>624.6388</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>193.8865</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>34.8966</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>90.0129</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>27.8828</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>259.24</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>8261.9755</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>7509.0939</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>0.0559</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0.0043</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0.0046</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>10.8918</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>12.7515</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>92.8674</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>-69.2241</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2649.224</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1582.956</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>175.544</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>502.606</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>223.595</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>865.016</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>36612.798</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>16235.452</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>0.0663</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0.0048</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>16.6185</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>12.9589</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>52.3113</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>-22.7338</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2431.997</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1528.045</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>331.082</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>220.973</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>819.563</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>35934.539</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>15859.504</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>15.5974</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>13.2377</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>50.1611</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>-21.3259</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2604.449</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1544.681</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>128.587</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>361.827</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>231.174</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>807.788</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>35409.916</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>15649.4</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>0.0494</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0.0082</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>12.2382</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>13.4648</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>48.4619</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>-22.7589</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2725.5033</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1623.9576</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-1914.3989</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>406.2581</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>244.4322</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1009.863</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>33003.4116</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>13373.2173</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>-0.7024</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>-0.1319</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>12.9634</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>13.472</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>51.4865</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>-25.0511</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>427.929</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>218.02</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>42.867</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>57.227</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>15.662</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>363.318</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>5699.147</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>1881.959</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>0.1002</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>11.8464</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>6.7108</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>165.9953</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>-147.4381</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>314.521</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>199.239</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>11.881</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>34.675</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>15.557</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>269.551</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>5664.051</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>1853.88</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0.0064</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>13.295</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>7.1295</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>144.5276</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>-124.1032</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>362.011</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>211.94</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1.842</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>50.23</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>15.963</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>245.158</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>5766.065</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>1855.722</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>10.7887</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>6.8412</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>111.7138</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>-94.0839</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>472.7198</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>237.0251</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>44.1944</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>52.9387</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>20.3805</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>238.7387</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>5770.1542</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>1894.2679</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>0.0935</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0.0077</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0.0236</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>10.0393</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>7.0533</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>93.9109</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>-76.8184</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -1781,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U105"/>
+  <dimension ref="A1:U121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -10317,77 +10317,77 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>97.8812</t>
+          <t>9.4142</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>53.115</t>
+          <t>24.1354</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>14.114</t>
+          <t>-16.4885</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>16.1787</t>
+          <t>4.0214</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1.3477</t>
+          <t>1.2365</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>29.991</t>
+          <t>13.4258</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>669.2441</t>
+          <t>871.2496</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>452.6589</t>
+          <t>422.5708</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>-1.7514</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>0.0207</t>
+          <t>-0.0192</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>0.0317</t>
+          <t>-0.0383</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>13.5146</t>
+          <t>33.6825</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2.5197</t>
+          <t>4.905</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>59.3484</t>
+          <t>50.7575</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>-43.3141</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -10424,77 +10424,77 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>75.445</t>
+          <t>4.9164</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>48.0476</t>
+          <t>22.5473</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>3.6651</t>
+          <t>-22.5835</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>4.6339</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1.2802</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>32.1413</t>
+          <t>9.6012</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>668.5211</t>
+          <t>844.104</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>456.324</t>
+          <t>399.9873</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>0.0486</t>
+          <t>-4.5935</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>0.0055</t>
+          <t>-0.0263</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>0.0081</t>
+          <t>-0.0549</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>18.0195</t>
+          <t>80.1026</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2.4886</t>
+          <t>5.3404</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>58.8379</t>
+          <t>46.4679</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>-38.3298</t>
+          <t>38.975</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -10531,77 +10531,77 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>95.0862</t>
+          <t>2.0099</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>57.5382</t>
+          <t>20.7721</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>11.84</t>
+          <t>12.558</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>12.9018</t>
+          <t>5.5734</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>38.2079</t>
+          <t>9.2006</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>669.4754</t>
+          <t>855.513</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>468.164</t>
+          <t>412.5453</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>0.1245</t>
+          <t>6.2482</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>0.0177</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>0.0256</t>
+          <t>0.0309</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>12.8692</t>
+          <t>233.617</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>1.9259</t>
+          <t>6.137</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>56.242</t>
+          <t>41.6369</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>-41.447</t>
+          <t>198.1171</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -10638,91 +10638,99 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>94.8345</t>
+          <t>9.3656</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>55.0352</t>
+          <t>24.0769</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>10.1986</t>
+          <t>-22.3285</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>10.6145</t>
+          <t>5.7672</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1.6372</t>
+          <t>1.2428</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>30.4437</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>645.3267</t>
+          <t>835.4447</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>476.4493</t>
+          <t>390.2168</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>0.1075</t>
+          <t>-2.3841</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>0.0155</t>
+          <t>-0.0264</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>0.0216</t>
+          <t>-0.0556</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>11.4067</t>
+          <t>55.7005</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2.3118</t>
+          <t>4.9753</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>57.3811</t>
+          <t>40.925</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>-43.6625</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
+          <t>19.7508</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Q4_FS.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -10737,77 +10745,77 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>37267.312</t>
+          <t>13.143</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20008.898</t>
+          <t>27.4402</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>611.516</t>
+          <t>-30.2935</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>14945.937</t>
+          <t>6.469</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>4088.494</t>
+          <t>1.0468</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>22052.993</t>
+          <t>16.7151</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>355544.01</t>
+          <t>808.8927</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>98317.427</t>
+          <t>359.9233</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>0.0164</t>
+          <t>-2.3049</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>0.0017</t>
+          <t>-0.0368</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>0.0062</t>
+          <t>-0.0808</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>34.9162</t>
+          <t>41.8953</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>18.0058</t>
+          <t>3.7549</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>104.5056</t>
+          <t>47.4515</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>-51.5836</t>
+          <t>-1.8013</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -10824,12 +10832,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -10844,77 +10852,77 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>43497.069</t>
+          <t>32.0142</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>22101.435</t>
+          <t>34.4279</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>3322.548</t>
+          <t>-12.0503</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>15751.811</t>
+          <t>9.3689</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>4157.115</t>
+          <t>0.9652</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>24610.107</t>
+          <t>22.3781</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>366301.08</t>
+          <t>801.7407</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>99185.386</t>
+          <t>347.873</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>0.0764</t>
+          <t>-0.3764</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>0.0092</t>
+          <t>-0.015</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>0.0336</t>
+          <t>-0.0341</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>32.1113</t>
+          <t>22.5096</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>16.9752</t>
+          <t>2.6591</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>96.0649</t>
+          <t>51.6656</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>-46.9784</t>
+          <t>-26.4969</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -10931,12 +10939,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -10951,77 +10959,77 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>41174.584</t>
+          <t>51.0255</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>21956.753</t>
+          <t>42.7624</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2667.974</t>
+          <t>-4.5026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>17466.545</t>
+          <t>12.3641</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>4137.789</t>
+          <t>0.9851</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>23955.136</t>
+          <t>32.9849</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>356649.372</t>
+          <t>807.069</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>94833.336</t>
+          <t>343.3704</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>0.0648</t>
+          <t>-0.0882</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>0.0074</t>
+          <t>-0.0056</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>0.0275</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>37.1113</t>
+          <t>19.5926</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>17.3781</t>
+          <t>2.0979</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>101.7455</t>
+          <t>59.5546</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>-47.2561</t>
+          <t>-37.8641</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -11038,12 +11046,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MINT</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -11058,91 +11066,99 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>43865.7491</t>
+          <t>71.1109</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>22154.6994</t>
+          <t>48.7387</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>3237.2946</t>
+          <t>6.9614</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>15911.6016</t>
+          <t>10.3819</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>3921.4803</t>
+          <t>1.1838</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>25606.359</t>
+          <t>32.3589</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>357329.6666</t>
+          <t>811.3254</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>96985.6572</t>
+          <t>353.0399</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>0.0738</t>
+          <t>0.0979</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>0.0091</t>
+          <t>0.0086</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>35.0021</t>
+          <t>14.7139</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>16.7335</t>
+          <t>2.047</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>102.905</t>
+          <t>61.672</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>-51.1693</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
+          <t>-44.9112</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Q4_FS.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -11157,77 +11173,77 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>789.301</t>
+          <t>76.0404</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>332.6197</t>
+          <t>51.2652</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>193.8595</t>
+          <t>6.844</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>89.5299</t>
+          <t>11.7441</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>23.1416</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>268.2755</t>
+          <t>26.1553</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>5725.7918</t>
+          <t>804.0502</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2677.6813</t>
+          <t>359.8838</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>0.2456</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>0.0085</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>0.0751</t>
+          <t>0.0192</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>9.9049</t>
+          <t>13.0939</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>7.0353</t>
+          <t>2.1846</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>87.0016</t>
+          <t>51.3631</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>-70.0614</t>
+          <t>-36.0845</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -11244,12 +11260,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -11264,77 +11280,77 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>433.486</t>
+          <t>68.6147</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>280.8156</t>
+          <t>46.198</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-21.6962</t>
+          <t>1.1953</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>67.4259</t>
+          <t>11.0526</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>20.6785</t>
+          <t>1.2169</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>280.6725</t>
+          <t>26.1948</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>5670.2721</t>
+          <t>747.3579</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2655.9851</t>
+          <t>361.0791</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>-0.0501</t>
+          <t>0.0174</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>-0.0038</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>-0.0081</t>
+          <t>0.0033</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>16.4745</t>
+          <t>15.117</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>7.1001</t>
+          <t>2.4838</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>88.945</t>
+          <t>51.5591</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>-65.3703</t>
+          <t>-33.9583</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
@@ -11351,12 +11367,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -11371,77 +11387,77 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>478.3312</t>
+          <t>90.6776</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>331.1909</t>
+          <t>55.0518</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-26.0182</t>
+          <t>15.3714</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>78.9921</t>
+          <t>12.1653</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>32.8947</t>
+          <t>1.2132</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>503.8692</t>
+          <t>26.1061</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>5846.5963</t>
+          <t>754.7019</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2629.9669</t>
+          <t>376.4505</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>-0.0544</t>
+          <t>0.1695</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>-0.0045</t>
+          <t>0.0205</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>-0.0098</t>
+          <t>0.0417</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>14.0807</t>
+          <t>11.7782</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>7.4409</t>
+          <t>2.0305</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>108.9671</t>
+          <t>43.7014</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>-87.4455</t>
+          <t>-29.8926</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -11458,12 +11474,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -11478,91 +11494,99 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>823.8227</t>
+          <t>89.9606</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>387.9619</t>
+          <t>52.5348</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>167.549</t>
+          <t>11.2733</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>107.3732</t>
+          <t>12.2615</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>36.3419</t>
+          <t>1.3299</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>598.6416</t>
+          <t>27.7516</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>6047.5464</t>
+          <t>759.002</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2797.2204</t>
+          <t>387.7238</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>0.0282</t>
+          <t>0.0149</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>0.0617</t>
+          <t>0.0295</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>10.4061</t>
+          <t>12.4902</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>8.2093</t>
+          <t>2.2268</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>130.7229</t>
+          <t>47.1583</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>-112.1075</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
+          <t>-32.4413</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Q4_FS.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -11577,77 +11601,77 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>659.954</t>
+          <t>93.4029</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>188.579</t>
+          <t>50.8233</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>159.821</t>
+          <t>13.7944</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>61.376</t>
+          <t>18.8228</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>27.765</t>
+          <t>1.0385</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>162.319</t>
+          <t>31.3064</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>8195.463</t>
+          <t>722.8177</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>7595.093</t>
+          <t>401.5182</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>0.2422</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>0.0197</t>
+          <t>0.0186</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>0.0213</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>9.6443</t>
+          <t>14.9759</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>13.4817</t>
+          <t>2.097</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>94.8007</t>
+          <t>52.2912</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>-71.6747</t>
+          <t>-35.2182</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -11657,19 +11681,19 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -11684,77 +11708,77 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>401.638</t>
+          <t>80.8305</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>145.967</t>
+          <t>46.844</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-40.895</t>
+          <t>6.8823</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>42.973</t>
+          <t>10.9899</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>27.609</t>
+          <t>1.1612</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>137.849</t>
+          <t>36.1513</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>7984.993</t>
+          <t>698.9993</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>7468.704</t>
+          <t>408.4005</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>-0.1018</t>
+          <t>0.0851</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>-0.0051</t>
+          <t>0.0097</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>-0.0054</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>11.8213</t>
+          <t>16.7818</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>17.2609</t>
+          <t>2.1366</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>93.5667</t>
+          <t>65.5223</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>-64.4845</t>
+          <t>-46.6039</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -11764,19 +11788,19 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -11791,77 +11815,77 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>467.158</t>
+          <t>99.8557</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>166.785</t>
+          <t>55.5979</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>87.081</t>
+          <t>18.1941</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>57.888</t>
+          <t>15.8826</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>25.864</t>
+          <t>1.1124</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>132.189</t>
+          <t>34.5267</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>8034.036</t>
+          <t>699.7538</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>7505.949</t>
+          <t>426.5946</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.1822</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0436</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>9.9316</t>
+          <t>12.3792</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>14.7481</t>
+          <t>1.8811</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>74.4776</t>
+          <t>58.4768</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>-49.798</t>
+          <t>-44.2165</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
@@ -11871,19 +11895,19 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -11898,77 +11922,77 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>624.6388</t>
+          <t>102.6529</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>193.8865</t>
+          <t>57.4153</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>34.8966</t>
+          <t>11.9503</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>90.0129</t>
+          <t>13.2174</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>27.8828</t>
+          <t>1.6264</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>259.24</t>
+          <t>40.0599</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>8261.9755</t>
+          <t>691.6676</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>7509.0939</t>
+          <t>438.5449</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>0.0559</t>
+          <t>0.1164</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>0.0043</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>0.0046</t>
+          <t>0.0276</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>10.8918</t>
+          <t>13.0401</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>12.7515</t>
+          <t>2.1943</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>92.8674</t>
+          <t>59.7574</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>-69.2241</t>
+          <t>-44.5231</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -11977,7 +12001,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11997,77 +12021,77 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2649.224</t>
+          <t>97.8812</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1582.956</t>
+          <t>53.115</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>175.544</t>
+          <t>14.114</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>502.606</t>
+          <t>16.1787</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>223.595</t>
+          <t>1.3477</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>865.016</t>
+          <t>29.991</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>36612.798</t>
+          <t>669.2441</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>16235.452</t>
+          <t>452.6589</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>0.0663</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>0.0048</t>
+          <t>0.0207</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0317</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>16.6185</t>
+          <t>13.5146</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>12.9589</t>
+          <t>2.5197</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>52.3113</t>
+          <t>59.3484</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>-22.7338</t>
+          <t>-43.3141</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -12077,14 +12101,14 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -12104,77 +12128,77 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2431.997</t>
+          <t>75.445</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1528.045</t>
+          <t>48.0476</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>3.6651</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>331.082</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>220.973</t>
+          <t>1.2802</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>819.563</t>
+          <t>32.1413</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>35934.539</t>
+          <t>668.5211</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>15859.504</t>
+          <t>456.324</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0486</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>0.0055</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>0.0015</t>
+          <t>0.0081</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>15.5974</t>
+          <t>18.0195</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>13.2377</t>
+          <t>2.4886</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>50.1611</t>
+          <t>58.8379</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>-21.3259</t>
+          <t>-38.3298</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -12184,14 +12208,14 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -12211,77 +12235,77 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2604.449</t>
+          <t>95.0862</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1544.681</t>
+          <t>57.5382</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>128.587</t>
+          <t>11.84</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>361.827</t>
+          <t>12.9018</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>231.174</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>807.788</t>
+          <t>38.2079</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>35409.916</t>
+          <t>669.4754</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>15649.4</t>
+          <t>468.164</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>0.0494</t>
+          <t>0.1245</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0177</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>0.0082</t>
+          <t>0.0256</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>12.2382</t>
+          <t>12.8692</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>13.4648</t>
+          <t>1.9259</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>48.4619</t>
+          <t>56.242</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>-22.7589</t>
+          <t>-41.447</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -12291,14 +12315,14 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MANRIN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -12318,77 +12342,77 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2725.5033</t>
+          <t>94.8345</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1623.9576</t>
+          <t>55.0352</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-1914.3989</t>
+          <t>10.1986</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>406.2581</t>
+          <t>10.6145</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>244.4322</t>
+          <t>1.6372</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>1009.863</t>
+          <t>30.4437</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>33003.4116</t>
+          <t>645.3267</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>13373.2173</t>
+          <t>476.4493</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>-0.7024</t>
+          <t>0.1075</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>0.0155</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>-0.1319</t>
+          <t>0.0216</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>12.9634</t>
+          <t>11.4067</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>13.472</t>
+          <t>2.3118</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>51.4865</t>
+          <t>57.3811</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>-25.0511</t>
+          <t>-43.6625</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -12397,7 +12421,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -12417,77 +12441,77 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>427.929</t>
+          <t>37267.312</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>218.02</t>
+          <t>20008.898</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>42.867</t>
+          <t>611.516</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>57.227</t>
+          <t>14945.937</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>4088.494</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>363.318</t>
+          <t>22052.993</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>5699.147</t>
+          <t>355544.01</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>1881.959</t>
+          <t>98317.427</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>0.1002</t>
+          <t>0.0164</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>0.0017</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.0062</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>11.8464</t>
+          <t>34.9162</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>6.7108</t>
+          <t>18.0058</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>165.9953</t>
+          <t>104.5056</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>-147.4381</t>
+          <t>-51.5836</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -12504,7 +12528,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -12524,77 +12548,77 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>314.521</t>
+          <t>43497.069</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>199.239</t>
+          <t>22101.435</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>11.881</t>
+          <t>3322.548</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>34.675</t>
+          <t>15751.811</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>15.557</t>
+          <t>4157.115</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>269.551</t>
+          <t>24610.107</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>5664.051</t>
+          <t>366301.08</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>1853.88</t>
+          <t>99185.386</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>0.0378</t>
+          <t>0.0764</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>0.0092</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>0.0064</t>
+          <t>0.0336</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>13.295</t>
+          <t>32.1113</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>7.1295</t>
+          <t>16.9752</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>144.5276</t>
+          <t>96.0649</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>-124.1032</t>
+          <t>-46.9784</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -12611,7 +12635,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -12631,77 +12655,77 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>362.011</t>
+          <t>41174.584</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>21956.753</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>2667.974</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>17466.545</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>15.963</t>
+          <t>4137.789</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>245.158</t>
+          <t>23955.136</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>5766.065</t>
+          <t>356649.372</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>1855.722</t>
+          <t>94833.336</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>0.0051</t>
+          <t>0.0648</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0074</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.0275</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>10.7887</t>
+          <t>37.1113</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>6.8412</t>
+          <t>17.3781</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>111.7138</t>
+          <t>101.7455</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>-94.0839</t>
+          <t>-47.2561</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -12718,7 +12742,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12738,81 +12762,1761 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>472.7198</t>
+          <t>43865.7491</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>237.0251</t>
+          <t>22154.6994</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>44.1944</t>
+          <t>3237.2946</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>52.9387</t>
+          <t>15911.6016</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>20.3805</t>
+          <t>3921.4803</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>238.7387</t>
+          <t>25606.359</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>5770.1542</t>
+          <t>357329.6666</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>1894.2679</t>
+          <t>96985.6572</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>0.0935</t>
+          <t>0.0738</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>0.0091</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>0.0236</t>
+          <t>0.0338</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>10.0393</t>
+          <t>35.0021</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>7.0533</t>
+          <t>16.7335</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>93.9109</t>
+          <t>102.905</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>-76.8184</t>
+          <t>-51.1693</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>789.301</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>332.6197</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>193.8595</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>89.5299</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>23.1416</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>268.2755</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>5725.7918</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2677.6813</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>0.2456</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>0.0338</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>0.0751</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>9.9049</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>7.0353</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>87.0016</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>-70.0614</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>433.486</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>280.8156</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-21.6962</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>67.4259</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>20.6785</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>280.6725</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>5670.2721</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2655.9851</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>-0.0501</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>-0.0038</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>-0.0081</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>16.4745</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>7.1001</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>88.945</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>-65.3703</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>478.3312</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>331.1909</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-26.0182</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>78.9921</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>32.8947</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>503.8692</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>5846.5963</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2629.9669</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>-0.0544</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>-0.0045</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>-0.0098</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>14.0807</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>7.4409</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>108.9671</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>-87.4455</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>823.8227</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>387.9619</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>167.549</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>107.3732</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>36.3419</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>598.6416</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>6047.5464</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2797.2204</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>0.2034</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>0.0282</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>0.0617</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>10.4061</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>8.2093</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>130.7229</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>-112.1075</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>659.954</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>188.579</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>159.821</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>61.376</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>27.765</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>162.319</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>8195.463</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>7595.093</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>0.2422</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>0.0197</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>0.0213</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>9.6443</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>13.4817</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>94.8007</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>-71.6747</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>401.638</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>145.967</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-40.895</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>42.973</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>27.609</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>137.849</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>7984.993</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>7468.704</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>-0.1018</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>-0.0051</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>-0.0054</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>11.8213</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>17.2609</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>93.5667</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>-64.4845</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>467.158</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>166.785</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>87.081</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>57.888</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>25.864</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>132.189</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>8034.036</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>7505.949</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>0.1864</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>0.0116</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>9.9316</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>14.7481</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>74.4776</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>-49.798</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>624.6388</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>193.8865</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>34.8966</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>90.0129</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>27.8828</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>259.24</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>8261.9755</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>7509.0939</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>0.0559</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>0.0043</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>0.0046</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>10.8918</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>12.7515</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>92.8674</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>-69.2241</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2649.224</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>1582.956</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>175.544</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>502.606</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>223.595</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>865.016</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>36612.798</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>16235.452</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>0.0663</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>0.0048</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>16.6185</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>12.9589</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>52.3113</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>-22.7338</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2431.997</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1528.045</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>331.082</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>220.973</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>819.563</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>35934.539</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>15859.504</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>15.5974</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>13.2377</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>50.1611</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>-21.3259</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2604.449</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>1544.681</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>128.587</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>361.827</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>231.174</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>807.788</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>35409.916</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>15649.4</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>0.0494</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>0.0082</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>12.2382</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>13.4648</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>48.4619</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>-22.7589</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2725.5033</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1623.9576</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-1914.3989</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>406.2581</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>244.4322</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>1009.863</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>33003.4116</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>13373.2173</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>-0.7024</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>-0.1319</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>12.9634</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>13.472</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>51.4865</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>-25.0511</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>427.929</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>218.02</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>42.867</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>57.227</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>15.662</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>363.318</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>5699.147</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>1881.959</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>0.1002</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>11.8464</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>6.7108</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>165.9953</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>-147.4381</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>314.521</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>199.239</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>11.881</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>34.675</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>15.557</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>269.551</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>5664.051</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>1853.88</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>0.0064</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>13.295</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>7.1295</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>144.5276</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>-124.1032</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>362.011</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>211.94</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1.842</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>50.23</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>15.963</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>245.158</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>5766.065</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>1855.722</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>10.7887</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>6.8412</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>111.7138</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>-94.0839</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>472.7198</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>237.0251</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>44.1944</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>52.9387</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>20.3805</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>238.7387</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>5770.1542</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>1894.2679</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>0.0935</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>0.0077</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>0.0236</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>10.0393</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>7.0533</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>93.9109</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>-76.8184</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -1781,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -12441,77 +12441,77 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>37267.312</t>
+          <t>12653.858</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>20008.898</t>
+          <t>8670.877</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>611.516</t>
+          <t>-7798.673</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>14945.937</t>
+          <t>12560.738</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>4088.494</t>
+          <t>3667.674</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>22052.993</t>
+          <t>15245.522</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>355544.01</t>
+          <t>353002.88</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>98317.427</t>
+          <t>69419.738</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>0.0164</t>
+          <t>-0.6163</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>0.0017</t>
+          <t>-0.0218</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>0.0062</t>
+          <t>-0.107</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>34.9162</t>
+          <t>88.3603</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>18.0058</t>
+          <t>38.1464</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>104.5056</t>
+          <t>158.5789</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>-51.5836</t>
+          <t>-32.0722</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -12548,77 +12548,77 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>43497.069</t>
+          <t>15840.486</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>22101.435</t>
+          <t>9770.642</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>3322.548</t>
+          <t>-4188.238</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>15751.811</t>
+          <t>12245.698</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>4157.115</t>
+          <t>3636.485</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>24610.107</t>
+          <t>15838.852</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>366301.08</t>
+          <t>362628.36</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>99185.386</t>
+          <t>65612.425</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>0.0764</t>
+          <t>-0.2644</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>0.0092</t>
+          <t>-0.0117</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>0.0336</t>
+          <t>-0.062</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>32.1113</t>
+          <t>71.2537</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>16.9752</t>
+          <t>34.0141</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>96.0649</t>
+          <t>144.7539</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>-46.9784</t>
+          <t>-39.4862</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -12655,77 +12655,77 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>41174.584</t>
+          <t>20789.337</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>21956.753</t>
+          <t>11835.953</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2667.974</t>
+          <t>-551.893</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>17466.545</t>
+          <t>14057.042</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>4137.789</t>
+          <t>3777.876</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>23955.136</t>
+          <t>17618.801</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>356649.372</t>
+          <t>359719.892</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>94833.336</t>
+          <t>63481.21</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>0.0648</t>
+          <t>-0.0265</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>0.0074</t>
+          <t>-0.0015</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>0.0275</t>
+          <t>-0.0086</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>37.1113</t>
+          <t>58.1994</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>17.3781</t>
+          <t>28.8156</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>101.7455</t>
+          <t>130.0319</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>-47.2561</t>
+          <t>-43.0169</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -12762,77 +12762,77 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>43865.7491</t>
+          <t>26927.5804</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>22154.6994</t>
+          <t>12194.2255</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>3237.2946</t>
+          <t>-1636.5656</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>15911.6016</t>
+          <t>14637.9953</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>3921.4803</t>
+          <t>3490.1827</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>25606.359</t>
+          <t>18393.6398</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>357329.6666</t>
+          <t>369632.8896</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>96985.6572</t>
+          <t>79492.4305</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>0.0738</t>
+          <t>-0.0608</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>0.0091</t>
+          <t>-0.0045</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>-0.0229</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>35.0021</t>
+          <t>49.0193</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>16.7335</t>
+          <t>27.4171</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>102.905</t>
+          <t>135.8489</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>-51.1693</t>
+          <t>-59.4125</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -12841,12 +12841,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -12861,77 +12861,77 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>789.301</t>
+          <t>20672.252</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>332.6197</t>
+          <t>13113.487</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>193.8595</t>
+          <t>-4067.712</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>89.5299</t>
+          <t>18889.532</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>23.1416</t>
+          <t>3671.525</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>268.2755</t>
+          <t>18781.601</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>5725.7918</t>
+          <t>363430.987</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2677.6813</t>
+          <t>75663.465</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>0.2456</t>
+          <t>-0.1968</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>-0.0111</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>0.0751</t>
+          <t>-0.0524</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>9.9049</t>
+          <t>72.9838</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>7.0353</t>
+          <t>24.576</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>87.0016</t>
+          <t>127.5699</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>-70.0614</t>
+          <t>-30.0101</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -12948,12 +12948,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -12968,77 +12968,77 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>433.486</t>
+          <t>32348.359</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>280.8156</t>
+          <t>16080.254</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-21.6962</t>
+          <t>1701.487</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>67.4259</t>
+          <t>17198.61</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>20.6785</t>
+          <t>3982.958</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>280.6725</t>
+          <t>19282.544</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>5670.2721</t>
+          <t>364423.437</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2655.9851</t>
+          <t>79308.323</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>-0.0501</t>
+          <t>0.0526</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>-0.0038</t>
+          <t>0.0047</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>-0.0081</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>16.4745</t>
+          <t>50.7602</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>7.1001</t>
+          <t>21.6588</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>88.945</t>
+          <t>107.7047</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>-65.3703</t>
+          <t>-35.2856</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -13055,12 +13055,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -13075,77 +13075,77 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>478.3312</t>
+          <t>35153.927</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>331.1909</t>
+          <t>17222.59</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-26.0182</t>
+          <t>4775.446</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>78.9921</t>
+          <t>18590.806</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>32.8947</t>
+          <t>3907.026</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>503.8692</t>
+          <t>20414.772</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>5846.5963</t>
+          <t>370265.417</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2629.9669</t>
+          <t>84082.853</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>-0.0544</t>
+          <t>0.1358</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>-0.0045</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>-0.0098</t>
+          <t>0.0585</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>14.0807</t>
+          <t>46.8316</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>7.4409</t>
+          <t>21.0734</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>108.9671</t>
+          <t>106.028</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>-87.4455</t>
+          <t>-38.123</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
@@ -13162,12 +13162,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OHTL</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -13182,77 +13182,77 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>823.8227</t>
+          <t>36031.3102</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>387.9619</t>
+          <t>17411.4609</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>167.549</t>
+          <t>2113.4587</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>107.3732</t>
+          <t>17052.2687</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>36.3419</t>
+          <t>3909.1979</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>598.6416</t>
+          <t>21806.5212</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>6047.5464</t>
+          <t>358209.7614</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2797.2204</t>
+          <t>82608.97</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>0.0587</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>0.0282</t>
+          <t>0.0058</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>0.0617</t>
+          <t>0.0254</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>10.4061</t>
+          <t>45.5044</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>8.2093</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>130.7229</t>
+          <t>111.546</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>-112.1075</t>
+          <t>-45.3917</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -13261,12 +13261,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -13281,77 +13281,77 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>659.954</t>
+          <t>32229.34</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>188.579</t>
+          <t>17326.308</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>159.821</t>
+          <t>-940.597</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>61.376</t>
+          <t>17614.873</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>27.765</t>
+          <t>3817.805</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>162.319</t>
+          <t>21635.269</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>8195.463</t>
+          <t>362049.415</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>7595.093</t>
+          <t>92390.46</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>0.2422</t>
+          <t>-0.0292</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>0.0197</t>
+          <t>-0.0026</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>0.0213</t>
+          <t>-0.0107</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>9.6443</t>
+          <t>48.4038</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>13.4817</t>
+          <t>20.0686</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>94.8007</t>
+          <t>112.8273</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>-71.6747</t>
+          <t>-44.3549</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -13361,19 +13361,19 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -13388,77 +13388,77 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>401.638</t>
+          <t>40588.347</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>145.967</t>
+          <t>19634.453</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-40.895</t>
+          <t>3490.163</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>42.973</t>
+          <t>19429.147</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>27.609</t>
+          <t>3981.635</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>137.849</t>
+          <t>24038.032</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>7984.993</t>
+          <t>371204.823</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>7468.704</t>
+          <t>85719.937</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>-0.1018</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>-0.0051</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>-0.0054</t>
+          <t>0.0392</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>11.8213</t>
+          <t>41.5268</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>17.2609</t>
+          <t>18.0741</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>93.5667</t>
+          <t>105.8413</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>-64.4845</t>
+          <t>-46.2404</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -13468,19 +13468,19 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -13495,77 +13495,77 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>467.158</t>
+          <t>39840.815</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>166.785</t>
+          <t>19633.64</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>87.081</t>
+          <t>2323.736</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>57.888</t>
+          <t>19843.861</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>25.864</t>
+          <t>3875.773</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>132.189</t>
+          <t>23542.235</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>8034.036</t>
+          <t>370070.456</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>7505.949</t>
+          <t>88073.206</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.0583</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0063</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0267</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>9.9316</t>
+          <t>45.3444</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>14.7481</t>
+          <t>18.4093</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>74.4776</t>
+          <t>111.4766</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>-49.798</t>
+          <t>-47.723</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
@@ -13575,19 +13575,19 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -13602,77 +13602,77 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>624.6388</t>
+          <t>40390.7396</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>193.8865</t>
+          <t>21556.068</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>34.8966</t>
+          <t>1214.672</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>90.0129</t>
+          <t>18487.3486</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>27.8828</t>
+          <t>3820.4157</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>259.24</t>
+          <t>24953.3081</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>8261.9755</t>
+          <t>359195.9233</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>7509.0939</t>
+          <t>87294.5566</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>0.0559</t>
+          <t>0.0301</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>0.0043</t>
+          <t>0.0033</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>0.0046</t>
+          <t>0.0139</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>10.8918</t>
+          <t>43.6545</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>12.7515</t>
+          <t>16.4234</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>92.8674</t>
+          <t>103.488</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>-69.2241</t>
+          <t>-43.4101</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -13681,12 +13681,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -13701,77 +13701,77 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2649.224</t>
+          <t>37818.351</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1582.956</t>
+          <t>20253.5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>175.544</t>
+          <t>1288.472</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>502.606</t>
+          <t>19703.261</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>223.595</t>
+          <t>3756.272</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>865.016</t>
+          <t>24726.24</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>36612.798</t>
+          <t>368813.476</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>16235.452</t>
+          <t>91861.587</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>0.0663</t>
+          <t>0.0341</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>0.0048</t>
+          <t>0.0035</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>16.6185</t>
+          <t>45.443</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>12.9589</t>
+          <t>16.8342</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>52.3113</t>
+          <t>110.3799</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>-22.7338</t>
+          <t>-48.1028</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -13781,19 +13781,19 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -13808,77 +13808,77 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2431.997</t>
+          <t>44303.008</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1528.045</t>
+          <t>22584.012</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>3031.497</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>331.082</t>
+          <t>20247.792</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>220.973</t>
+          <t>3907.044</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>819.563</t>
+          <t>23792.342</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>35934.539</t>
+          <t>372383.166</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>15859.504</t>
+          <t>94773.579</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0684</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>0.0082</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>0.0015</t>
+          <t>0.0325</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>15.5974</t>
+          <t>41.0305</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>13.2377</t>
+          <t>15.4393</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>50.1611</t>
+          <t>97.7504</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>-21.3259</t>
+          <t>-41.2806</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -13888,19 +13888,19 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -13915,77 +13915,77 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2604.449</t>
+          <t>41612.614</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1544.681</t>
+          <t>21452.758</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>128.587</t>
+          <t>361.424</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>361.827</t>
+          <t>18407.006</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>231.174</t>
+          <t>3908.265</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>807.788</t>
+          <t>22804.063</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>35409.916</t>
+          <t>344558.581</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>15649.4</t>
+          <t>89490.583</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>0.0494</t>
+          <t>0.0087</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>0.0082</t>
+          <t>0.0039</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>12.2382</t>
+          <t>42.7303</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>13.4648</t>
+          <t>16.7579</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>48.4619</t>
+          <t>99.9142</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>-22.7589</t>
+          <t>-40.4259</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -13995,19 +13995,19 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -14022,77 +14022,77 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2725.5033</t>
+          <t>41628.2992</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1623.9576</t>
+          <t>21620.0916</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-1914.3989</t>
+          <t>3920.5313</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>406.2581</t>
+          <t>13970.3414</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>244.4322</t>
+          <t>3917.6361</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>1009.863</t>
+          <t>24414.6113</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>33003.4116</t>
+          <t>346844.9317</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>13373.2173</t>
+          <t>99136.8305</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>-0.7024</t>
+          <t>0.0942</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>0.0113</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>-0.1319</t>
+          <t>0.0416</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>12.9634</t>
+          <t>35.7775</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>13.472</t>
+          <t>16.6508</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>51.4865</t>
+          <t>100.4648</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>-25.0511</t>
+          <t>-48.0365</t>
         </is>
       </c>
       <c r="T117" t="inlineStr"/>
@@ -14101,7 +14101,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -14121,77 +14121,77 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>427.929</t>
+          <t>37267.312</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>218.02</t>
+          <t>20008.898</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>42.867</t>
+          <t>611.516</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>57.227</t>
+          <t>14945.937</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>4088.494</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>363.318</t>
+          <t>22052.993</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>5699.147</t>
+          <t>355544.01</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>1881.959</t>
+          <t>98317.427</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>0.1002</t>
+          <t>0.0164</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>0.0017</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.0062</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>11.8464</t>
+          <t>34.9162</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>6.7108</t>
+          <t>18.0058</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>165.9953</t>
+          <t>104.5056</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>-147.4381</t>
+          <t>-51.5836</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -14208,7 +14208,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -14228,77 +14228,77 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>314.521</t>
+          <t>43497.069</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>199.239</t>
+          <t>22101.435</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>11.881</t>
+          <t>3322.548</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>34.675</t>
+          <t>15751.811</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>15.557</t>
+          <t>4157.115</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>269.551</t>
+          <t>24610.107</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>5664.051</t>
+          <t>366301.08</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>1853.88</t>
+          <t>99185.386</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>0.0378</t>
+          <t>0.0764</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>0.0092</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>0.0064</t>
+          <t>0.0336</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>13.295</t>
+          <t>32.1113</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>7.1295</t>
+          <t>16.9752</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>144.5276</t>
+          <t>96.0649</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>-124.1032</t>
+          <t>-46.9784</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -14315,7 +14315,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -14335,77 +14335,77 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>362.011</t>
+          <t>41174.584</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>21956.753</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>2667.974</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>17466.545</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>15.963</t>
+          <t>4137.789</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>245.158</t>
+          <t>23955.136</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>5766.065</t>
+          <t>356649.372</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>1855.722</t>
+          <t>94833.336</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>0.0051</t>
+          <t>0.0648</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0074</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.0275</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>10.7887</t>
+          <t>37.1113</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>6.8412</t>
+          <t>17.3781</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>111.7138</t>
+          <t>101.7455</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>-94.0839</t>
+          <t>-47.2561</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -14422,7 +14422,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>MINT</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -14442,81 +14442,1761 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>472.7198</t>
+          <t>43865.7491</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>237.0251</t>
+          <t>22154.6994</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>44.1944</t>
+          <t>3237.2946</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>52.9387</t>
+          <t>15911.6016</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>20.3805</t>
+          <t>3921.4803</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>238.7387</t>
+          <t>25606.359</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>5770.1542</t>
+          <t>357329.6666</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>1894.2679</t>
+          <t>96985.6572</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>0.0935</t>
+          <t>0.0738</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>0.0091</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>0.0236</t>
+          <t>0.0338</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>10.0393</t>
+          <t>35.0021</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>7.0533</t>
+          <t>16.7335</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>93.9109</t>
+          <t>102.905</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>-76.8184</t>
+          <t>-51.1693</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>789.301</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>332.6197</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>193.8595</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>89.5299</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>23.1416</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>268.2755</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>5725.7918</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2677.6813</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>0.2456</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>0.0338</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>0.0751</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>9.9049</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>7.0353</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>87.0016</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>-70.0614</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>433.486</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>280.8156</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-21.6962</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>67.4259</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>20.6785</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>280.6725</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>5670.2721</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2655.9851</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>-0.0501</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>-0.0038</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>-0.0081</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>16.4745</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>7.1001</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>88.945</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>-65.3703</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>478.3312</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>331.1909</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-26.0182</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>78.9921</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>32.8947</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>503.8692</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>5846.5963</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2629.9669</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>-0.0544</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>-0.0045</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>-0.0098</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>14.0807</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>7.4409</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>108.9671</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>-87.4455</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>823.8227</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>387.9619</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>167.549</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>107.3732</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>36.3419</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>598.6416</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>6047.5464</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2797.2204</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>0.2034</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>0.0282</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>0.0617</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>10.4061</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>8.2093</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>130.7229</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>-112.1075</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>659.954</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>188.579</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>159.821</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>61.376</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>27.765</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>162.319</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>8195.463</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>7595.093</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>0.2422</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>0.0197</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>0.0213</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>9.6443</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>13.4817</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>94.8007</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>-71.6747</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>401.638</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>145.967</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-40.895</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>42.973</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>27.609</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>137.849</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>7984.993</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>7468.704</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>-0.1018</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>-0.0051</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>-0.0054</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>11.8213</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>17.2609</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>93.5667</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>-64.4845</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>467.158</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>166.785</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>87.081</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>57.888</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>25.864</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>132.189</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>8034.036</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>7505.949</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>0.1864</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>0.0116</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>9.9316</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>14.7481</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>74.4776</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>-49.798</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>624.6388</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>193.8865</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>34.8966</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>90.0129</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>27.8828</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>259.24</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>8261.9755</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>7509.0939</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>0.0559</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>0.0043</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>0.0046</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>10.8918</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>12.7515</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>92.8674</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>-69.2241</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2649.224</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1582.956</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>175.544</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>502.606</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>223.595</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>865.016</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>36612.798</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>16235.452</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>0.0663</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>0.0048</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>16.6185</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>12.9589</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>52.3113</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>-22.7338</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2431.997</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>1528.045</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>331.082</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>220.973</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>819.563</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>35934.539</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>15859.504</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>15.5974</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>13.2377</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>50.1611</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>-21.3259</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2604.449</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1544.681</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>128.587</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>361.827</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>231.174</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>807.788</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>35409.916</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>15649.4</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>0.0494</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>0.0082</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>12.2382</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>13.4648</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>48.4619</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>-22.7589</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2725.5033</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1623.9576</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-1914.3989</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>406.2581</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>244.4322</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>1009.863</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>33003.4116</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>13373.2173</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>-0.7024</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>-0.1319</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>12.9634</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>13.472</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>51.4865</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>-25.0511</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>427.929</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>218.02</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>42.867</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>57.227</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>15.662</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>363.318</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>5699.147</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>1881.959</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>0.1002</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>11.8464</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>6.7108</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>165.9953</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>-147.4381</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>314.521</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>199.239</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>11.881</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>34.675</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>15.557</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>269.551</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>5664.051</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>1853.88</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>0.0064</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>13.295</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>7.1295</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>144.5276</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>-124.1032</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>362.011</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>211.94</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>1.842</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>50.23</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>15.963</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>245.158</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>5766.065</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>1855.722</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>10.7887</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>6.8412</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>111.7138</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>-94.0839</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>472.7198</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>237.0251</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>44.1944</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>52.9387</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>20.3805</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>238.7387</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>5770.1542</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>1894.2679</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>0.0935</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>0.0077</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>0.0236</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>10.0393</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>7.0533</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>93.9109</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>-76.8184</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -1781,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U137"/>
+  <dimension ref="A1:U153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -14541,77 +14541,77 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>789.301</t>
+          <t>150.9211</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>332.6197</t>
+          <t>217.6384</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>193.8595</t>
+          <t>-155.4763</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>89.5299</t>
+          <t>30.2111</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>23.1416</t>
+          <t>18.2184</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>268.2755</t>
+          <t>304.3415</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>5725.7918</t>
+          <t>6566.336</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2677.6813</t>
+          <t>1971.6781</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>0.2456</t>
+          <t>-1.0302</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>0.0338</t>
+          <t>-0.0234</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>0.0751</t>
+          <t>-0.0759</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>9.9049</t>
+          <t>22.8298</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>7.0353</t>
+          <t>7.5352</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>87.0016</t>
+          <t>145.029</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>-70.0614</t>
+          <t>-114.664</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -14648,77 +14648,77 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>433.486</t>
+          <t>84.1603</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>280.8156</t>
+          <t>183.8351</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-21.6962</t>
+          <t>-167.6779</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>67.4259</t>
+          <t>29.3485</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>20.6785</t>
+          <t>20.2541</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>280.6725</t>
+          <t>275.8175</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>5670.2721</t>
+          <t>6436.1775</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2655.9851</t>
+          <t>1803.9684</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>-0.0501</t>
+          <t>-1.9924</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>-0.0038</t>
+          <t>-0.0258</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>-0.0081</t>
+          <t>-0.0888</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>16.4745</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>7.1001</t>
+          <t>9.5221</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>88.945</t>
+          <t>143.5919</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>-65.3703</t>
+          <t>-101.8698</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -14755,77 +14755,77 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>478.3312</t>
+          <t>106.6106</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>331.1909</t>
+          <t>176.1041</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-26.0182</t>
+          <t>-174.2362</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>78.9921</t>
+          <t>45.7348</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>32.8947</t>
+          <t>19.4717</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>503.8692</t>
+          <t>249.3838</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>5846.5963</t>
+          <t>6335.5935</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2629.9669</t>
+          <t>1630.4561</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>-0.0544</t>
+          <t>-1.6343</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>-0.0045</t>
+          <t>-0.0273</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>-0.0098</t>
+          <t>-0.1015</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>14.0807</t>
+          <t>32.3967</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>7.4409</t>
+          <t>10.3767</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>108.9671</t>
+          <t>137.1874</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>-87.4455</t>
+          <t>-94.4139</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -14862,77 +14862,77 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>823.8227</t>
+          <t>220.6755</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>387.9619</t>
+          <t>217.5427</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>167.549</t>
+          <t>-123.251</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>107.3732</t>
+          <t>67.1032</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>36.3419</t>
+          <t>20.5458</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>598.6416</t>
+          <t>294.5062</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>6047.5464</t>
+          <t>6303.015</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2797.2204</t>
+          <t>1559.0963</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>-0.5585</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>0.0282</t>
+          <t>-0.0195</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>0.0617</t>
+          <t>-0.0773</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>10.4061</t>
+          <t>23.5212</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>8.2093</t>
+          <t>8.4618</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>130.7229</t>
+          <t>115.007</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>-112.1075</t>
+          <t>-83.0241</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -14941,12 +14941,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14961,77 +14961,77 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>659.954</t>
+          <t>253.9844</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>188.579</t>
+          <t>235.3374</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>159.821</t>
+          <t>-112.2507</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>61.376</t>
+          <t>48.5313</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>27.765</t>
+          <t>20.2286</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>162.319</t>
+          <t>273.3735</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>8195.463</t>
+          <t>6169.4373</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>7595.093</t>
+          <t>1450.7784</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>0.2422</t>
+          <t>-0.442</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>0.0197</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>0.0213</t>
+          <t>-0.0746</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>9.6443</t>
+          <t>20.4877</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>13.4817</t>
+          <t>7.7967</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>94.8007</t>
+          <t>108.587</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>-71.6747</t>
+          <t>-80.3027</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -15041,19 +15041,19 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -15068,77 +15068,77 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>401.638</t>
+          <t>335.7315</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>145.967</t>
+          <t>264.8354</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-40.895</t>
+          <t>-58.2002</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>42.973</t>
+          <t>61.5592</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>27.609</t>
+          <t>20.9875</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>137.849</t>
+          <t>255.2722</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>7984.993</t>
+          <t>6101.6498</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>7468.704</t>
+          <t>1397.1267</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>-0.1018</t>
+          <t>-0.1734</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>-0.0051</t>
+          <t>-0.0095</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>-0.0054</t>
+          <t>-0.0409</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>11.8213</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>17.2609</t>
+          <t>7.0811</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>93.5667</t>
+          <t>90.8239</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>-64.4845</t>
+          <t>-68.8228</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -15148,19 +15148,19 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -15175,77 +15175,77 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>467.158</t>
+          <t>479.8403</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>166.785</t>
+          <t>321.3138</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>87.081</t>
+          <t>-8.0225</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>57.888</t>
+          <t>68.9837</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>25.864</t>
+          <t>20.8894</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>132.189</t>
+          <t>323.3475</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>8034.036</t>
+          <t>6099.4833</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>7505.949</t>
+          <t>1387.5207</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>-0.0167</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>-0.0013</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>-0.0058</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>9.9316</t>
+          <t>12.5145</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>14.7481</t>
+          <t>5.9952</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>74.4776</t>
+          <t>82.8365</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>-49.798</t>
+          <t>-64.3268</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -15255,19 +15255,19 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHANG</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -15282,77 +15282,77 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>624.6388</t>
+          <t>861.842</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>193.8865</t>
+          <t>371.593</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>34.8966</t>
+          <t>266.6809</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>90.0129</t>
+          <t>120.8099</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>27.8828</t>
+          <t>26.5771</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>259.24</t>
+          <t>344.8985</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>8261.9755</t>
+          <t>6123.6887</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>7509.0939</t>
+          <t>1663.5023</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>0.0559</t>
+          <t>0.3094</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>0.0043</t>
+          <t>0.0436</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>0.0046</t>
+          <t>0.1748</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>10.8918</t>
+          <t>10.1301</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>12.7515</t>
+          <t>5.8759</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>92.8674</t>
+          <t>82.7231</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>-69.2241</t>
+          <t>-66.7171</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -15361,12 +15361,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -15381,77 +15381,77 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2649.224</t>
+          <t>687.6216</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1582.956</t>
+          <t>323.953</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>175.544</t>
+          <t>127.7652</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>502.606</t>
+          <t>87.8005</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>223.595</t>
+          <t>26.7599</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>865.016</t>
+          <t>250.4112</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>36612.798</t>
+          <t>5998.5204</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>16235.452</t>
+          <t>1790.9899</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>0.0663</t>
+          <t>0.1858</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>0.0048</t>
+          <t>0.0211</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>16.6185</t>
+          <t>13.6521</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>12.9589</t>
+          <t>7.409</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>52.3113</t>
+          <t>82.6939</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>-22.7338</t>
+          <t>-61.6328</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -15461,19 +15461,19 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -15488,77 +15488,77 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2431.997</t>
+          <t>546.3819</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1528.045</t>
+          <t>311.2778</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>34.2226</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>331.082</t>
+          <t>94.7157</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>220.973</t>
+          <t>27.0311</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>819.563</t>
+          <t>285.6237</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>35934.539</t>
+          <t>5988.5151</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>15859.504</t>
+          <t>1954.2387</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0626</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>0.0057</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>0.0015</t>
+          <t>0.0183</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>15.5974</t>
+          <t>15.1991</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>13.2377</t>
+          <t>7.8627</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>50.1611</t>
+          <t>78.3531</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>-21.3259</t>
+          <t>-55.2913</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -15568,19 +15568,19 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -15595,77 +15595,77 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2604.449</t>
+          <t>574.5457</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1544.681</t>
+          <t>354.2492</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>128.587</t>
+          <t>16.2047</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>361.827</t>
+          <t>95.655</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>231.174</t>
+          <t>27.7705</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>807.788</t>
+          <t>346.7044</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>35409.916</t>
+          <t>5964.7458</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>15649.4</t>
+          <t>1971.4394</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>0.0494</t>
+          <t>0.0282</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>0.0082</t>
+          <t>0.0083</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>12.2382</t>
+          <t>15.2417</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>13.4648</t>
+          <t>7.1161</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>48.4619</t>
+          <t>82.1091</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>-22.7589</t>
+          <t>-59.7513</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -15675,19 +15675,19 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -15702,77 +15702,77 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2725.5033</t>
+          <t>711.7621</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>1623.9576</t>
+          <t>365.8978</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-1914.3989</t>
+          <t>99.2515</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>406.2581</t>
+          <t>102.6832</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>244.4322</t>
+          <t>32.4615</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>1009.863</t>
+          <t>365.7168</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>33003.4116</t>
+          <t>5948.5656</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>13373.2173</t>
+          <t>2068.992</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>-0.7024</t>
+          <t>0.1394</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>0.0167</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>-0.1319</t>
+          <t>0.0491</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>12.9634</t>
+          <t>12.8183</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>13.472</t>
+          <t>7.5722</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>51.4865</t>
+          <t>89.5643</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>-25.0511</t>
+          <t>-69.1738</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -15781,12 +15781,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -15801,77 +15801,77 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>427.929</t>
+          <t>773.1407</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>218.02</t>
+          <t>348.9028</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>42.867</t>
+          <t>163.0921</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>57.227</t>
+          <t>80.0023</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>24.3724</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>363.318</t>
+          <t>319.664</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>5699.147</t>
+          <t>5904.4805</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>1881.959</t>
+          <t>2230.1437</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>0.1002</t>
+          <t>0.2109</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>0.0275</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.0759</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>11.8464</t>
+          <t>10.6331</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>6.7108</t>
+          <t>7.3302</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>165.9953</t>
+          <t>88.3975</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>-147.4381</t>
+          <t>-70.4343</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -15888,12 +15888,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -15908,77 +15908,77 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>314.521</t>
+          <t>525.6543</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>199.239</t>
+          <t>307.9501</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>11.881</t>
+          <t>35.8379</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>34.675</t>
+          <t>86.3228</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>15.557</t>
+          <t>24.019</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>269.551</t>
+          <t>296.0098</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>5664.051</t>
+          <t>5818.2651</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>1853.88</t>
+          <t>2265.9816</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>0.0378</t>
+          <t>0.0682</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>0.0061</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>0.0064</t>
+          <t>0.0159</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>13.295</t>
+          <t>14.3969</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>7.1295</t>
+          <t>7.1499</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>144.5276</t>
+          <t>90.9666</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>-124.1032</t>
+          <t>-69.4198</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -15995,12 +15995,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -16015,77 +16015,77 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>362.011</t>
+          <t>621.4638</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>368.041</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>57.0653</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>98.3205</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>15.963</t>
+          <t>22.4763</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>245.158</t>
+          <t>343.8427</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>5766.065</t>
+          <t>5820.0681</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>1855.722</t>
+          <t>2323.0469</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>0.0051</t>
+          <t>0.0918</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0098</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.0249</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>10.7887</t>
+          <t>13.6671</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>6.8412</t>
+          <t>5.8113</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>111.7138</t>
+          <t>79.9726</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>-94.0839</t>
+          <t>-60.4943</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
@@ -16102,12 +16102,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>OHTL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -16122,81 +16122,1761 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>472.7198</t>
+          <t>785.4024</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>237.0251</t>
+          <t>368.4952</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>44.1944</t>
+          <t>164.0267</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>52.9387</t>
+          <t>84.2025</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>20.3805</t>
+          <t>28.8604</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>238.7387</t>
+          <t>374.8013</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>5770.1542</t>
+          <t>5742.7004</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>1894.2679</t>
+          <t>2483.8218</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>0.0935</t>
+          <t>0.2088</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>0.0284</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>0.0236</t>
+          <t>0.0682</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>10.0393</t>
+          <t>10.6901</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>7.0533</t>
+          <t>6.4085</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>93.9109</t>
+          <t>89.7098</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>-76.8184</t>
+          <t>-72.6112</t>
         </is>
       </c>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>789.301</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>332.6197</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>193.8595</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>89.5299</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>23.1416</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>268.2755</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>5725.7918</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2677.6813</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>0.2456</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>0.0338</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>0.0751</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>9.9049</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>7.0353</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>87.0016</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>-70.0614</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>433.486</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>280.8156</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-21.6962</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>67.4259</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>20.6785</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>280.6725</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>5670.2721</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2655.9851</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>-0.0501</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>-0.0038</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>-0.0081</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>16.4745</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>7.1001</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>88.945</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>-65.3703</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>478.3312</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>331.1909</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-26.0182</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>78.9921</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>32.8947</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>503.8692</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>5846.5963</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2629.9669</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>-0.0544</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>-0.0045</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>-0.0098</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>14.0807</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>7.4409</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>108.9671</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>-87.4455</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>OHTL</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>823.8227</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>387.9619</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>167.549</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>107.3732</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>36.3419</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>598.6416</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>6047.5464</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2797.2204</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>0.2034</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>0.0282</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>0.0617</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>10.4061</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>8.2093</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>130.7229</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>-112.1075</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>659.954</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>188.579</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>159.821</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>61.376</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>27.765</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>162.319</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>8195.463</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>7595.093</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>0.2422</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>0.0197</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>0.0213</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>9.6443</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>13.4817</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>94.8007</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>-71.6747</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>401.638</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>145.967</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-40.895</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>42.973</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>27.609</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>137.849</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>7984.993</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>7468.704</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>-0.1018</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>-0.0051</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>-0.0054</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>11.8213</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>17.2609</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>93.5667</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>-64.4845</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>467.158</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>166.785</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>87.081</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>57.888</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>25.864</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>132.189</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>8034.036</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>7505.949</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>0.1864</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>0.0116</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>9.9316</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>14.7481</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>74.4776</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>-49.798</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>624.6388</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>193.8865</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>34.8966</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>90.0129</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>27.8828</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>259.24</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>8261.9755</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>7509.0939</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>0.0559</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>0.0043</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>0.0046</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>10.8918</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>12.7515</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>92.8674</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>-69.2241</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2649.224</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1582.956</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>175.544</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>502.606</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>223.595</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>865.016</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>36612.798</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>16235.452</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>0.0663</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>0.0048</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>16.6185</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>12.9589</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>52.3113</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>-22.7338</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2431.997</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1528.045</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>331.082</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>220.973</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>819.563</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>35934.539</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>15859.504</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>15.5974</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>13.2377</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>50.1611</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>-21.3259</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2604.449</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>1544.681</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>128.587</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>361.827</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>231.174</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>807.788</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>35409.916</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>15649.4</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>0.0494</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>0.0082</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>12.2382</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>13.4648</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>48.4619</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>-22.7589</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2725.5033</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>1623.9576</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-1914.3989</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>406.2581</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>244.4322</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>1009.863</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>33003.4116</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>13373.2173</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>-0.7024</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>-0.1319</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>12.9634</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>13.472</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>51.4865</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>-25.0511</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>427.929</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>218.02</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>42.867</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>57.227</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>15.662</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>363.318</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>5699.147</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>1881.959</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>0.1002</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>11.8464</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>6.7108</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>165.9953</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>-147.4381</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>314.521</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>199.239</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>11.881</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>34.675</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>15.557</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>269.551</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>5664.051</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>1853.88</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>0.0064</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>13.295</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>7.1295</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>144.5276</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>-124.1032</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>362.011</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>211.94</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>1.842</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>50.23</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>15.963</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>245.158</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>5766.065</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>1855.722</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>10.7887</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>6.8412</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>111.7138</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>-94.0839</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>472.7198</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>237.0251</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>44.1944</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>52.9387</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>20.3805</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>238.7387</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>5770.1542</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>1894.2679</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>0.0935</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>0.0077</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>0.0236</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>10.0393</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>7.0533</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>93.9109</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>-76.8184</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -1781,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U153"/>
+  <dimension ref="A1:U169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16626,7 +16626,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -16641,77 +16641,77 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>659.954</t>
+          <t>77.037</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>188.579</t>
+          <t>59.991</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>159.821</t>
+          <t>-84.025</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>61.376</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>27.765</t>
+          <t>23.251</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>162.319</t>
+          <t>89.028</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>8195.463</t>
+          <t>7704.899</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>7595.093</t>
+          <t>7425.499</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>0.2422</t>
+          <t>-1.0907</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>0.0197</t>
+          <t>-0.0109</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>0.0213</t>
+          <t>-0.0113</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>9.6443</t>
+          <t>16.1215</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>13.4817</t>
+          <t>36.0699</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>94.8007</t>
+          <t>140.0768</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>-71.6747</t>
+          <t>-87.8853</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
@@ -16733,7 +16733,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -16748,77 +16748,77 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>401.638</t>
+          <t>65.757</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>145.967</t>
+          <t>53.13</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-40.895</t>
+          <t>-107.398</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>42.973</t>
+          <t>5.633</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>27.609</t>
+          <t>22.663</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>137.849</t>
+          <t>74.083</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>7984.993</t>
+          <t>7795.243</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>7468.704</t>
+          <t>7512.439</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>-0.1018</t>
+          <t>-1.6333</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>-0.0051</t>
+          <t>-0.0139</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>-0.0054</t>
+          <t>-0.0144</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>11.8213</t>
+          <t>10.5542</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>17.2609</t>
+          <t>39.3203</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>93.5667</t>
+          <t>139.6866</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>-64.4845</t>
+          <t>-89.8122</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -16855,77 +16855,77 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>467.158</t>
+          <t>72.796</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>166.785</t>
+          <t>57.563</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>87.081</t>
+          <t>-113.631</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>57.888</t>
+          <t>12.294</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>25.864</t>
+          <t>20.033</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>132.189</t>
+          <t>74.588</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>8034.036</t>
+          <t>7761.689</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>7505.949</t>
+          <t>7481.804</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>-1.561</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>-0.0146</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>-0.0152</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>9.9316</t>
+          <t>11.3281</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>14.7481</t>
+          <t>34.1194</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>74.4776</t>
+          <t>118.8066</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>-49.798</t>
+          <t>-73.3591</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -16962,77 +16962,77 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>624.6388</t>
+          <t>140.2838</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>193.8865</t>
+          <t>81.1546</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>34.8966</t>
+          <t>-181.31</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>90.0129</t>
+          <t>28.8968</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>27.8828</t>
+          <t>20.2967</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>259.24</t>
+          <t>99.6522</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>8261.9755</t>
+          <t>7577.4511</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>7509.0939</t>
+          <t>7251.1661</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>0.0559</t>
+          <t>-1.2925</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>0.0043</t>
+          <t>-0.0236</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>0.0046</t>
+          <t>-0.0246</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>10.8918</t>
+          <t>13.5067</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>12.7515</t>
+          <t>22.8596</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>92.8674</t>
+          <t>98.7627</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>-69.2241</t>
+          <t>-62.3963</t>
         </is>
       </c>
       <c r="T145" t="inlineStr"/>
@@ -17041,12 +17041,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>SHANG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -17061,77 +17061,77 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2649.224</t>
+          <t>126.409</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>1582.956</t>
+          <t>67.552</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>175.544</t>
+          <t>-84.618</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>502.606</t>
+          <t>29.831</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>223.595</t>
+          <t>19.427</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>865.016</t>
+          <t>74.864</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>36612.798</t>
+          <t>7445.292</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>16235.452</t>
+          <t>7131.687</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>0.0663</t>
+          <t>-0.6694</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>0.0048</t>
+          <t>-0.0113</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>-0.0118</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>16.6185</t>
+          <t>20.9064</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>12.9589</t>
+          <t>26.4623</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>52.3113</t>
+          <t>116.2544</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>-22.7338</t>
+          <t>-68.8857</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
@@ -17148,12 +17148,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>SHANG</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -17168,77 +17168,77 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2431.997</t>
+          <t>199.551</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>1528.045</t>
+          <t>82.545</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>-43.38</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>331.082</t>
+          <t>43.417</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>220.973</t>
+          <t>19.074</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>819.563</t>
+          <t>90.167</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>35934.539</t>
+          <t>7561.836</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>15859.504</t>
+          <t>7206.907</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.2174</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.0058</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>0.0015</t>
+          <t>-0.0061</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>15.5974</t>
+          <t>16.7014</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>13.2377</t>
+          <t>21.2223</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>50.1611</t>
+          <t>90.9675</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>-21.3259</t>
+          <t>-53.0438</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
@@ -17255,12 +17255,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>SHANG</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -17275,77 +17275,77 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2604.449</t>
+          <t>364.513</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>1544.681</t>
+          <t>128.473</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>128.587</t>
+          <t>62.364</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>361.827</t>
+          <t>76.648</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>231.174</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>807.788</t>
+          <t>113.972</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>35409.916</t>
+          <t>7787.865</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>15649.4</t>
+          <t>7379.094</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>0.0494</t>
+          <t>0.1711</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0081</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>0.0082</t>
+          <t>0.0086</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>12.2382</t>
+          <t>15.1517</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>13.4648</t>
+          <t>13.2744</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>48.4619</t>
+          <t>73.0924</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>-22.7589</t>
+          <t>-44.6662</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
@@ -17362,12 +17362,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SHR</t>
+          <t>SHANG</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -17382,77 +17382,77 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2725.5033</t>
+          <t>510.5389</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>1623.9576</t>
+          <t>169.541</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-1914.3989</t>
+          <t>-8.2596</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>406.2581</t>
+          <t>88.5692</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>244.4322</t>
+          <t>24.1844</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>1009.863</t>
+          <t>192.4815</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>33003.4116</t>
+          <t>7809.042</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>13373.2173</t>
+          <t>7292.631</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>-0.7024</t>
+          <t>-0.0162</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>-0.0011</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>-0.1319</t>
+          <t>-0.0011</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>12.9634</t>
+          <t>14.8862</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>13.472</t>
+          <t>11.4455</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>51.4865</t>
+          <t>83.1472</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>-25.0511</t>
+          <t>-56.8155</t>
         </is>
       </c>
       <c r="T149" t="inlineStr"/>
@@ -17461,12 +17461,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>SHANG</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -17481,77 +17481,77 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>427.929</t>
+          <t>601.976</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>218.02</t>
+          <t>164.22</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>42.867</t>
+          <t>117.248</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>57.227</t>
+          <t>56.896</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>20.793</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>363.318</t>
+          <t>139.563</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>5699.147</t>
+          <t>7829.609</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>1881.959</t>
+          <t>7434.763</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>0.1002</t>
+          <t>0.1948</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.0159</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>11.8464</t>
+          <t>10.8741</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>6.7108</t>
+          <t>12.3247</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>165.9953</t>
+          <t>90.9876</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>-147.4381</t>
+          <t>-67.7888</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
@@ -17561,19 +17561,19 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>Q1_FS.xlsx</t>
+          <t>Q1_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>SHANG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -17588,77 +17588,77 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>314.521</t>
+          <t>448.375</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>199.239</t>
+          <t>140.662</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>11.881</t>
+          <t>102.171</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>34.675</t>
+          <t>42.509</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>15.557</t>
+          <t>23.989</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>269.551</t>
+          <t>143.965</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>5664.051</t>
+          <t>7961.29</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>1853.88</t>
+          <t>7548.144</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>0.0378</t>
+          <t>0.2279</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>0.0129</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>0.0064</t>
+          <t>0.0136</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>13.295</t>
+          <t>10.0874</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>7.1295</t>
+          <t>14.4857</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>144.5276</t>
+          <t>91.7129</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>-124.1032</t>
+          <t>-67.1399</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
@@ -17668,19 +17668,19 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>Q2_FS.xlsx</t>
+          <t>Q2_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>SHANG</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -17695,77 +17695,77 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>362.011</t>
+          <t>508.461</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>176.621</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>66.246</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>74.082</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>15.963</t>
+          <t>24.112</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>245.158</t>
+          <t>156.461</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>5766.065</t>
+          <t>8028.141</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>1855.722</t>
+          <t>7575.094</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>0.0051</t>
+          <t>0.1303</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0083</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>10.7887</t>
+          <t>10.5479</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>6.8412</t>
+          <t>12.5276</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>111.7138</t>
+          <t>78.2444</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>-94.0839</t>
+          <t>-55.1688</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
@@ -17775,19 +17775,19 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>Q3_FS.xlsx</t>
+          <t>Q3_FS.xls</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>SHANG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -17802,81 +17802,1761 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>472.7198</t>
+          <t>627.3777</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>237.0251</t>
+          <t>195.3247</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>44.1944</t>
+          <t>-146.1472</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>52.9387</t>
+          <t>75.4878</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>20.3805</t>
+          <t>31.0397</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>238.7387</t>
+          <t>222.811</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>5770.1542</t>
+          <t>7848.6757</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>1894.2679</t>
+          <t>7298.2782</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>0.0935</t>
+          <t>-0.2329</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>-0.0184</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>0.0236</t>
+          <t>-0.0197</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>10.0393</t>
+          <t>10.9666</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>7.0533</t>
+          <t>12.9885</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>93.9109</t>
+          <t>89.3206</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>-76.8184</t>
+          <t>-65.3655</t>
         </is>
       </c>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>701.44</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>191.092</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>223.647</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>73.267</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>176.546</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>8086.747</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>7610.423</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>0.3188</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>0.0281</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>9.5432</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>13.331</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>94.044</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>-71.1698</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>471.877</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>151.669</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>90.274</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>43.853</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>24.049</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>155.739</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>8060.359</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>7600.249</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>0.1913</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>0.0112</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>0.0119</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>11.2931</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>14.8855</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>99.684</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>-73.5054</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>510.709</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>175.902</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>34.719</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>65.036</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>23.925</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>164.766</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>8007.153</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>7459.225</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>0.068</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>0.0043</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>0.0046</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>9.8077</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>12.5456</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>83.815</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>-61.4617</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>746.1398</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>215.5033</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>22.3365</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>80.0644</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>28.7323</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>234.9568</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>8067.4338</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>7439.2267</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>0.0299</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>0.0028</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>8.9455</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>11.2399</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>85.3223</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>-65.1369</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>659.954</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>188.579</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>159.821</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>61.376</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>27.765</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>162.319</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>8195.463</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>7595.093</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>0.2422</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>0.0197</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>0.0213</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>9.6443</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>13.4817</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>94.8007</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>-71.6747</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>401.638</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>145.967</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-40.895</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>42.973</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>27.609</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>137.849</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>7984.993</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>7468.704</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>-0.1018</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>-0.0051</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>-0.0054</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>11.8213</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>17.2609</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>93.5667</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>-64.4845</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>467.158</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>166.785</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>87.081</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>57.888</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>25.864</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>132.189</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>8034.036</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>7505.949</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>0.1864</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>0.0116</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>9.9316</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>14.7481</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>74.4776</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>-49.798</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>SHANG</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>624.6388</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>193.8865</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>34.8966</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>90.0129</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>27.8828</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>259.24</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>8261.9755</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>7509.0939</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>0.0559</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>0.0043</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>0.0046</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>10.8918</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>12.7515</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>92.8674</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>-69.2241</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2649.224</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>1582.956</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>175.544</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>502.606</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>223.595</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>865.016</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>36612.798</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>16235.452</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>0.0663</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>0.0048</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>16.6185</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>12.9589</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>52.3113</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>-22.7338</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2431.997</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>1528.045</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>331.082</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>220.973</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>819.563</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>35934.539</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>15859.504</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>15.5974</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>13.2377</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>50.1611</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>-21.3259</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2604.449</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>1544.681</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>128.587</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>361.827</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>231.174</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>807.788</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>35409.916</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>15649.4</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>0.0494</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>0.0082</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>12.2382</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>13.4648</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>48.4619</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>-22.7589</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2725.5033</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>1623.9576</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-1914.3989</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>406.2581</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>244.4322</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>1009.863</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>33003.4116</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>13373.2173</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>-0.7024</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>-0.1319</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>12.9634</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>13.472</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>51.4865</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>-25.0511</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>427.929</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>218.02</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>42.867</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>57.227</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>15.662</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>363.318</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>5699.147</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>1881.959</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>0.1002</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>11.8464</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>6.7108</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>165.9953</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>-147.4381</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>314.521</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>199.239</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>11.881</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>34.675</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>15.557</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>269.551</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>5664.051</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>1853.88</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>0.0064</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>13.295</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>7.1295</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>144.5276</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>-124.1032</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>362.011</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>211.94</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>1.842</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>50.23</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>15.963</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>245.158</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>5766.065</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>1855.722</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>10.7887</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>6.8412</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>111.7138</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>-94.0839</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>472.7198</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>237.0251</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>44.1944</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>52.9387</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>20.3805</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>238.7387</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>5770.1542</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>1894.2679</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>0.0935</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>0.0077</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>0.0236</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>10.0393</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>7.0533</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>93.9109</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>-76.8184</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -1781,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U169"/>
+  <dimension ref="A1:U185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -18741,77 +18741,77 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2649.224</t>
+          <t>692.241</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>1582.956</t>
+          <t>566.057</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>175.544</t>
+          <t>-310.898</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>502.606</t>
+          <t>113.022</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>223.595</t>
+          <t>184.864</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>865.016</t>
+          <t>1434.284</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>36612.798</t>
+          <t>36754.953</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>16235.452</t>
+          <t>15954.945</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>0.0663</t>
+          <t>-0.4491</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>0.0048</t>
+          <t>-0.0097</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>0.0109</t>
+          <t>-0.0197</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>16.6185</t>
+          <t>10.7469</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>12.9589</t>
+          <t>28.6688</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>52.3113</t>
+          <t>160.7093</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>-22.7338</t>
+          <t>-121.2936</t>
         </is>
       </c>
       <c r="T162" t="inlineStr">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>Q1_FS.xls</t>
+          <t>Q1_FS.xlsx</t>
         </is>
       </c>
     </row>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -18848,77 +18848,77 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2431.997</t>
+          <t>837.966</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>1528.045</t>
+          <t>785.536</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>-571.435</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>331.082</t>
+          <t>116.663</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>220.973</t>
+          <t>165.008</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>819.563</t>
+          <t>1311.748</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>35934.539</t>
+          <t>37165.42</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>15859.504</t>
+          <t>15819.261</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.6819</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.0155</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>0.0015</t>
+          <t>-0.036</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>15.5974</t>
+          <t>12.4715</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>13.2377</t>
+          <t>20.2654</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>50.1611</t>
+          <t>159.0563</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>-21.3259</t>
+          <t>-126.3195</t>
         </is>
       </c>
       <c r="T163" t="inlineStr">
@@ -18928,7 +18928,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>Q2_FS.xls</t>
+          <t>Q2_FS.xlsx</t>
         </is>
       </c>
     </row>
@@ -18940,7 +18940,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -18955,77 +18955,77 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2604.449</t>
+          <t>1433.64</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>1544.681</t>
+          <t>1018.67</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>128.587</t>
+          <t>-281.861</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>361.827</t>
+          <t>212.509</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>231.174</t>
+          <t>168.977</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>807.788</t>
+          <t>1503.368</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>35409.916</t>
+          <t>38408.151</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>15649.4</t>
+          <t>16238.608</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>0.0494</t>
+          <t>-0.1966</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>-0.0075</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>0.0082</t>
+          <t>-0.0176</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>12.2382</t>
+          <t>10.5619</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>13.4648</t>
+          <t>15.0817</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>48.4619</t>
+          <t>127.122</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>-22.7589</t>
+          <t>-101.4784</t>
         </is>
       </c>
       <c r="T164" t="inlineStr">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>Q3_FS.xls</t>
+          <t>Q3_FS.xlsx</t>
         </is>
       </c>
     </row>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -19062,77 +19062,77 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2725.5033</t>
+          <t>1725.7028</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>1623.9576</t>
+          <t>1225.6937</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>-1914.3989</t>
+          <t>-70.0279</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>406.2581</t>
+          <t>387.2258</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>244.4322</t>
+          <t>197.7769</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>1009.863</t>
+          <t>1634.569</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>33003.4116</t>
+          <t>37214.1185</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>13373.2173</t>
+          <t>15881.8582</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>-0.7024</t>
+          <t>-0.0406</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>-0.0019</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>-0.1319</t>
+          <t>-0.0044</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>12.9634</t>
+          <t>15.9864</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>13.472</t>
+          <t>13.7642</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>51.4865</t>
+          <t>117.7661</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>-25.0511</t>
+          <t>-88.0154</t>
         </is>
       </c>
       <c r="T165" t="inlineStr"/>
@@ -19141,12 +19141,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>SHR</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -19161,77 +19161,77 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>427.929</t>
+          <t>1700.05</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>218.02</t>
+          <t>1258.798</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>42.867</t>
+          <t>-204.086</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>57.227</t>
+          <t>392.217</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>194.508</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>363.318</t>
+          <t>1603.991</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>5699.147</t>
+          <t>36458.411</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>1881.959</t>
+          <t>15549.686</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>0.1002</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>-0.0055</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>11.8464</t>
+          <t>20.6317</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>6.7108</t>
+          <t>14.0236</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>165.9953</t>
+          <t>115.7733</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>-147.4381</t>
+          <t>-81.118</t>
         </is>
       </c>
       <c r="T166" t="inlineStr">
@@ -19248,12 +19248,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>SHR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -19268,77 +19268,77 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>314.521</t>
+          <t>2094.021</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>199.239</t>
+          <t>1427.143</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>11.881</t>
+          <t>-96.879</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>34.675</t>
+          <t>439.668</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>15.557</t>
+          <t>205.79</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>269.551</t>
+          <t>1687.776</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>5664.051</t>
+          <t>37047.483</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>1853.88</t>
+          <t>15997.386</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>0.0378</t>
+          <t>-0.0463</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>-0.0026</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>0.0064</t>
+          <t>-0.0061</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>13.295</t>
+          <t>18.0756</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>7.1295</t>
+          <t>12.7623</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>144.5276</t>
+          <t>104.9477</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>-124.1032</t>
+          <t>-74.1098</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
@@ -19355,12 +19355,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>SHR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -19375,77 +19375,77 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>362.011</t>
+          <t>2466.344</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>1528.194</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>207.484</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>464.506</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>15.963</t>
+          <t>214.535</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>245.158</t>
+          <t>1535.406</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>5766.065</t>
+          <t>38433.024</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>1855.722</t>
+          <t>17083.078</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>0.0051</t>
+          <t>0.0841</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>0.0055</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.0125</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>10.7887</t>
+          <t>16.8638</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>6.8412</t>
+          <t>12.6522</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>111.7138</t>
+          <t>97.0206</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>-94.0839</t>
+          <t>-67.5047</t>
         </is>
       </c>
       <c r="T168" t="inlineStr">
@@ -19462,12 +19462,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>VRANDA</t>
+          <t>SHR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -19482,81 +19482,1761 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>472.7198</t>
+          <t>2563.8734</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>237.0251</t>
+          <t>1593.3079</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>44.1944</t>
+          <t>107.8633</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>52.9387</t>
+          <t>501.3555</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>20.3805</t>
+          <t>228.5058</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>238.7387</t>
+          <t>1710.6341</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>5770.1542</t>
+          <t>36449.5989</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>1894.2679</t>
+          <t>16019.1693</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>0.0935</t>
+          <t>0.0421</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>0.0236</t>
+          <t>0.0065</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>10.0393</t>
+          <t>17.3291</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>7.0533</t>
+          <t>12.7909</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>93.9109</t>
+          <t>93.7156</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>-76.8184</t>
+          <t>-63.5956</t>
         </is>
       </c>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2576.759</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>1604.888</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>124.881</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>437.075</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>222.848</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>1726.671</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>36139.858</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>15973.516</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>0.0485</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>0.0078</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>16.3886</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>12.6557</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>96.3798</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>-67.3355</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2318.612</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>1598.95</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>3.004</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>443.983</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>233.082</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>1764.509</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>38010.378</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>16580.939</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>0.0013</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>0.0002</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>17.2897</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>12.974</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>99.3456</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>-69.0819</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2495.846</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>1548.071</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>15.01</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>386.003</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>230.417</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>1719.383</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>38311.374</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>16834.999</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>0.0004</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>15.2972</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>13.7726</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>103.5218</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>-74.452</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2705.5375</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>1574.5075</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-56.4881</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>534.5558</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>230.9514</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>1666.9483</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>37722.7035</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>16091.0474</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>-0.0209</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>-0.0015</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>-0.0034</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>15.6515</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>13.4791</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>98.9333</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>-69.8027</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2781.537</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1633.455</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>111.624</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>480.556</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>219.271</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>1545.236</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>39325.93</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>17091.248</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>0.0401</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>0.0029</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>0.0067</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>16.4226</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>12.4032</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>88.4924</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>-59.6666</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2527.774</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1657.384</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-71.592</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>343.433</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>220.927</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>1017.739</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>38844.783</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>17119.998</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>-0.0283</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>-0.0018</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>-0.0042</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>14.8318</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>12.0847</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>70.3611</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>-43.4446</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2538.71</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>1565.109</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-53.396</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>316.165</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>199.997</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>934.721</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>35396.49</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>15365.781</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>-0.021</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>-0.0014</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>-0.0033</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>11.9515</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>12.3713</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>57.3846</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>-33.0617</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2710.2248</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1594.265</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>147.298</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>475.753</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>232.259</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>975.1275</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>36325.3586</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>15925.8378</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>0.0543</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>0.0041</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>0.0094</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>13.441</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>12.4721</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>55.1057</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>-29.1926</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2649.224</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>1582.956</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>175.544</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>502.606</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>223.595</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>865.016</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>36612.798</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>16235.452</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>0.0663</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>0.0048</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>0.0109</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>16.6185</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>12.9589</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>52.3113</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>-22.7338</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Q1_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2431.997</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>1528.045</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>331.082</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>220.973</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>819.563</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>35934.539</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>15859.504</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>15.5974</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>13.2377</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>50.1611</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>-21.3259</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Q2_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2604.449</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>1544.681</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>128.587</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>361.827</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>231.174</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>807.788</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>35409.916</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>15649.4</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>0.0494</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>0.0082</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>12.2382</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>13.4648</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>48.4619</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>-22.7589</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Q3_FS.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>SHR</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2725.5033</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>1623.9576</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-1914.3989</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>406.2581</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>244.4322</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>1009.863</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>33003.4116</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>13373.2173</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>-0.7024</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>-0.1319</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>12.9634</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>13.472</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>51.4865</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>-25.0511</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>427.929</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>218.02</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>42.867</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>57.227</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>15.662</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>363.318</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>5699.147</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>1881.959</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>0.1002</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>11.8464</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>6.7108</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>165.9953</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>-147.4381</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>314.521</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>199.239</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>11.881</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>34.675</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>15.557</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>269.551</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>5664.051</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>1853.88</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>0.0064</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>13.295</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>7.1295</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>144.5276</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>-124.1032</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>362.011</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>211.94</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>1.842</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>50.23</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>15.963</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>245.158</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>5766.065</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>1855.722</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>10.7887</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>6.8412</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>111.7138</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>-94.0839</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>472.7198</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>237.0251</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>44.1944</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>52.9387</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>20.3805</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>238.7387</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>5770.1542</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>1894.2679</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>0.0935</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>0.0077</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>0.0236</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>10.0393</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>7.0533</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>93.9109</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>-76.8184</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -1781,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U185"/>
+  <dimension ref="A1:U201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20826,7 +20826,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -20841,77 +20841,77 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>427.929</t>
+          <t>356.129</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>218.02</t>
+          <t>111.345</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>42.867</t>
+          <t>-34.673</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>57.227</t>
+          <t>25.334</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>20.845</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>363.318</t>
+          <t>180.669</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>5699.147</t>
+          <t>5081.931</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>1881.959</t>
+          <t>2034.573</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>0.1002</t>
+          <t>-0.0974</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>0.0076</t>
+          <t>-0.0066</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>-0.0169</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>11.8464</t>
+          <t>7.3149</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>6.7108</t>
+          <t>17.6617</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>165.9953</t>
+          <t>178.4663</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>-147.4381</t>
+          <t>-153.4896</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -20948,77 +20948,77 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>314.521</t>
+          <t>314.481</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>199.239</t>
+          <t>89.117</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>11.881</t>
+          <t>-35.359</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>34.675</t>
+          <t>26.575</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>15.557</t>
+          <t>21.035</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>269.551</t>
+          <t>176.007</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>5664.051</t>
+          <t>4908.636</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>1853.88</t>
+          <t>1967.246</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>0.0378</t>
+          <t>-0.1124</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>0.0021</t>
+          <t>-0.0071</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>0.0064</t>
+          <t>-0.0177</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>13.295</t>
+          <t>7.5103</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>7.1295</t>
+          <t>21.3825</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>144.5276</t>
+          <t>182.1062</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>-124.1032</t>
+          <t>-153.2134</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -21055,77 +21055,77 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>362.011</t>
+          <t>239.763</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>90.499</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>-49.808</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>50.23</t>
+          <t>34.836</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>15.963</t>
+          <t>20.024</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>245.158</t>
+          <t>174.968</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>5766.065</t>
+          <t>4850.744</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>1855.722</t>
+          <t>1917.438</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>0.0051</t>
+          <t>-0.2077</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>0.0003</t>
+          <t>-0.0102</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>-0.0256</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>10.7887</t>
+          <t>11.7821</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>6.8412</t>
+          <t>20.87</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>111.7138</t>
+          <t>178.3981</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>-94.0839</t>
+          <t>-145.746</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -21162,81 +21162,1761 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>472.7198</t>
+          <t>397.0995</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>237.0251</t>
+          <t>142.7711</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>44.1944</t>
+          <t>12.5906</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>52.9387</t>
+          <t>42.6836</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>20.3805</t>
+          <t>18.876</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>238.7387</t>
+          <t>184.9125</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>5770.1542</t>
+          <t>4795.433</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>1894.2679</t>
+          <t>1930.0283</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>0.0935</t>
+          <t>0.0317</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>0.0026</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>0.0236</t>
+          <t>0.0065</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>10.0393</t>
+          <t>8.9799</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>7.0533</t>
+          <t>12.5333</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>93.9109</t>
+          <t>115.9514</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>-76.8184</t>
+          <t>-94.4382</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2565</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>306.885</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>130.674</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-21.359</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>36.444</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>17.516</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>163.586</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>4707.634</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>1908.669</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>-0.0696</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>-0.0045</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>-0.0111</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>11.6029</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>12.5323</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>120.0121</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>-95.8769</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2565</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>323.864</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>152.008</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>1.719</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>40.884</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>17.115</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>166.155</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>4631.572</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>1910.388</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>0.0053</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>0.0004</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>10.8639</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>10.366</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>98.7002</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>-77.4703</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2565</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>329.927</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>166.305</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>39.706</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>17.758</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>161.027</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>4558.176</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>1912.418</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>0.0062</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>0.0004</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>0.0011</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>11.2362</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>9.6459</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>90.4986</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>-69.6165</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2565</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>405.1436</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>190.5591</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>18.7222</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>52.7419</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>19.8723</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>196.3301</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>4740.7028</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>1931.1405</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>0.0462</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>0.0097</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>10.4965</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>9.0838</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>86.2642</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>-66.6839</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>382.669</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>180.764</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>7.072</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>43.357</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>18.562</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>185.14</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>4656.829</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>1938.213</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>0.0185</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>0.0037</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>11.3008</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>9.5679</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>94.9644</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>-74.0958</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>315.369</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>175.78</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-14.771</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>37.041</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>18.568</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>185.093</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>4621.775</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>1923.442</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>-0.0468</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>-0.0032</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>-0.0077</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>11.5995</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>9.611</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>95.8334</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>-74.623</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>328.523</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>177.091</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-20.352</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>44.533</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>17.729</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>221.45</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>4701.844</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>1903.09</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>-0.062</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>-0.0044</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>-0.0106</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>11.422</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>9.4283</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>105.601</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>-84.7506</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>375.9069</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>189.7555</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-112.7177</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>55.106</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>17.4014</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>280.5517</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>4803.4835</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>1787.9047</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>-0.2999</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>-0.0237</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>-0.0611</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>12.1929</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>8.5162</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>121.6939</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>-100.9848</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>420.897</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>189.69</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>36.301</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>49.507</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>14.345</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>300.211</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>4873.268</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>1824.206</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>0.0862</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>0.0075</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>0.0201</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>11.1846</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>7.5311</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>137.7739</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>-119.0582</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>348.916</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>174.55</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>52.801</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>13.825</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>323.586</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>5061.003</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>1824.873</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>0.0004</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>13.3414</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>7.3431</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>162.6053</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>-141.9209</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>389.591</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>178.731</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>5.086</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>38.157</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>13.835</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>331.171</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>5255.116</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>1829.959</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>0.0131</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>0.0028</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>10.7396</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>7.1189</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>168.5148</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>-150.6563</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>378.0287</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>196.7738</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>9.1337</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>55.4272</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>16.8507</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>440.9111</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>5614.7583</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>1839.0923</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>0.0242</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>0.0017</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>11.3877</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>7.1734</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>180.4904</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>-161.9293</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>427.929</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>218.02</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>42.867</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>57.227</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>15.662</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>363.318</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>5699.147</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>1881.959</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>0.1002</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>0.0076</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>11.8464</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>6.7108</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>165.9953</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>-147.4381</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Q1_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>314.521</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>199.239</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>11.881</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>34.675</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>15.557</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>269.551</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>5664.051</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>1853.88</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>0.0064</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>13.295</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>7.1295</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>144.5276</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>-124.1032</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Q2_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>362.011</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>211.94</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>1.842</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>50.23</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>15.963</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>245.158</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>5766.065</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>1855.722</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>10.7887</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>6.8412</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>111.7138</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>-94.0839</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Q3_FS.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>VRANDA</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>472.7198</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>237.0251</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>44.1944</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>52.9387</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>20.3805</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>238.7387</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>5770.1542</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>1894.2679</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>0.0935</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>0.0077</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>0.0236</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>10.0393</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>7.0533</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>93.9109</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>-76.8184</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -1781,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U201"/>
+  <dimension ref="A1:V201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1885,10 +1885,15 @@
       </c>
       <c r="T1" s="2" t="inlineStr">
         <is>
+          <t>rev_low</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
           <t>balance_ok</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -1990,12 +1995,13 @@
           <t>90.3468</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -2097,12 +2103,13 @@
           <t>104.9533</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -2204,12 +2211,13 @@
           <t>121.8953</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -2313,6 +2321,7 @@
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2410,12 +2419,13 @@
           <t>84.9768</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -2517,12 +2527,13 @@
           <t>71.5805</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -2624,12 +2635,13 @@
           <t>56.34</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -2733,6 +2745,7 @@
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2830,12 +2843,13 @@
           <t>49.1502</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -2937,12 +2951,13 @@
           <t>52.4888</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -3044,12 +3059,13 @@
           <t>50.1435</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -3153,6 +3169,7 @@
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3250,12 +3267,13 @@
           <t>41.324</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -3357,12 +3375,13 @@
           <t>41.7304</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -3464,12 +3483,13 @@
           <t>36.1948</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -3573,6 +3593,7 @@
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3670,12 +3691,13 @@
           <t>27.6284</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -3777,12 +3799,13 @@
           <t>30.5733</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -3884,12 +3907,13 @@
           <t>31.439</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -3993,6 +4017,7 @@
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4090,12 +4115,13 @@
           <t>-34.1986</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -4197,12 +4223,13 @@
           <t>-36.7226</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -4304,12 +4331,13 @@
           <t>-50.6431</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -4413,6 +4441,7 @@
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4510,12 +4539,13 @@
           <t>-52.0574</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -4617,12 +4647,13 @@
           <t>-46.6762</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -4724,12 +4755,13 @@
           <t>-50.1574</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -4833,6 +4865,7 @@
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4930,12 +4963,13 @@
           <t>-48.5433</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -5037,12 +5071,13 @@
           <t>-39.2266</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -5144,12 +5179,13 @@
           <t>-35.557</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -5253,6 +5289,7 @@
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5350,12 +5387,13 @@
           <t>-41.5612</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -5457,12 +5495,13 @@
           <t>-48.2738</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -5564,12 +5603,13 @@
           <t>-59.7923</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -5673,6 +5713,7 @@
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5770,12 +5811,13 @@
           <t>-63.8475</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -5877,12 +5919,13 @@
           <t>-50.0908</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -5984,12 +6027,13 @@
           <t>-56.3605</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -6093,6 +6137,7 @@
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6190,12 +6235,13 @@
           <t>-138.4739</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -6297,12 +6343,13 @@
           <t>-206.4327</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -6404,12 +6451,13 @@
           <t>-149.5471</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -6513,6 +6561,7 @@
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6610,12 +6659,13 @@
           <t>-121.4683</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -6717,12 +6767,13 @@
           <t>-124.8645</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -6824,12 +6875,13 @@
           <t>-134.0293</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -6933,6 +6985,7 @@
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7030,12 +7083,13 @@
           <t>-135.334</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -7137,12 +7191,13 @@
           <t>-136.2981</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -7244,12 +7299,13 @@
           <t>-123.6786</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -7353,6 +7409,7 @@
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7450,12 +7507,13 @@
           <t>-123.1863</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -7557,12 +7615,13 @@
           <t>-146.1746</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -7664,12 +7723,13 @@
           <t>-132.3507</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -7773,6 +7833,7 @@
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7870,12 +7931,13 @@
           <t>-75.5416</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -7977,12 +8039,13 @@
           <t>-79.3769</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -8084,12 +8147,13 @@
           <t>-69.9465</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -8193,6 +8257,7 @@
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8292,10 +8357,15 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -8399,10 +8469,15 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -8506,10 +8581,15 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -8613,6 +8693,7 @@
       </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8712,10 +8793,15 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -8817,12 +8903,13 @@
           <t>-3.5416</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -8924,12 +9011,13 @@
           <t>-5.3394</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -9033,6 +9121,7 @@
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9130,12 +9219,13 @@
           <t>-11.0043</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -9237,12 +9327,13 @@
           <t>-7.7003</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -9344,12 +9435,13 @@
           <t>-8.5235</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="V72" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -9453,6 +9545,7 @@
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9550,12 +9643,13 @@
           <t>-12.7501</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="V74" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -9657,12 +9751,13 @@
           <t>-10.6574</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -9764,12 +9859,13 @@
           <t>-8.8176</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -9873,6 +9969,7 @@
       </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9970,12 +10067,13 @@
           <t>-11.145</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="V78" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -10077,12 +10175,13 @@
           <t>-6.9673</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="V79" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -10184,12 +10283,13 @@
           <t>-7.3971</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="V80" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -10293,6 +10393,7 @@
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10392,10 +10493,15 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="V82" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -10499,10 +10605,15 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="V83" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -10606,10 +10717,15 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="V84" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -10713,10 +10829,15 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="V85" t="inlineStr">
         <is>
           <t>Q4_FS.xlsx</t>
         </is>
@@ -10820,10 +10941,15 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="V86" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -10925,12 +11051,13 @@
           <t>-26.4969</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="V87" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -11032,12 +11159,13 @@
           <t>-37.8641</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="V88" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -11139,12 +11267,13 @@
           <t>-44.9112</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="V89" t="inlineStr">
         <is>
           <t>Q4_FS.xlsx</t>
         </is>
@@ -11246,12 +11375,13 @@
           <t>-36.0845</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="V90" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -11353,12 +11483,13 @@
           <t>-33.9583</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="V91" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -11460,12 +11591,13 @@
           <t>-29.8926</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="V92" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -11567,12 +11699,13 @@
           <t>-32.4413</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="V93" t="inlineStr">
         <is>
           <t>Q4_FS.xlsx</t>
         </is>
@@ -11674,12 +11807,13 @@
           <t>-35.2182</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="V94" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -11781,12 +11915,13 @@
           <t>-46.6039</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="V95" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -11888,12 +12023,13 @@
           <t>-44.2165</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="V96" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -11997,6 +12133,7 @@
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12094,12 +12231,13 @@
           <t>-43.3141</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="V98" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -12201,12 +12339,13 @@
           <t>-38.3298</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="V99" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -12308,12 +12447,13 @@
           <t>-41.447</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="V100" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -12417,6 +12557,7 @@
       </c>
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12516,10 +12657,15 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="V102" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -12621,12 +12767,13 @@
           <t>-39.4862</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr">
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="V103" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -12728,12 +12875,13 @@
           <t>-43.0169</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="V104" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -12837,6 +12985,7 @@
       </c>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -12934,12 +13083,13 @@
           <t>-30.0101</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="V106" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -13041,12 +13191,13 @@
           <t>-35.2856</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr">
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="V107" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -13148,12 +13299,13 @@
           <t>-38.123</t>
         </is>
       </c>
-      <c r="T108" t="inlineStr">
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="V108" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -13257,6 +13409,7 @@
       </c>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13354,12 +13507,13 @@
           <t>-44.3549</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr">
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="V110" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -13461,12 +13615,13 @@
           <t>-46.2404</t>
         </is>
       </c>
-      <c r="T111" t="inlineStr">
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="V111" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -13568,12 +13723,13 @@
           <t>-47.723</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr">
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="V112" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -13677,6 +13833,7 @@
       </c>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -13774,12 +13931,13 @@
           <t>-48.1028</t>
         </is>
       </c>
-      <c r="T114" t="inlineStr">
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="V114" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -13881,12 +14039,13 @@
           <t>-41.2806</t>
         </is>
       </c>
-      <c r="T115" t="inlineStr">
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="V115" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -13988,12 +14147,13 @@
           <t>-40.4259</t>
         </is>
       </c>
-      <c r="T116" t="inlineStr">
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="V116" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -14097,6 +14257,7 @@
       </c>
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14194,12 +14355,13 @@
           <t>-51.5836</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr">
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="V118" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -14301,12 +14463,13 @@
           <t>-46.9784</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="V119" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -14408,12 +14571,13 @@
           <t>-47.2561</t>
         </is>
       </c>
-      <c r="T120" t="inlineStr">
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="V120" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -14517,6 +14681,7 @@
       </c>
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -14616,10 +14781,15 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="V122" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -14723,10 +14893,15 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="V123" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -14830,10 +15005,15 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="V124" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -14937,6 +15117,7 @@
       </c>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15034,12 +15215,13 @@
           <t>-80.3027</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr">
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="V126" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -15141,12 +15323,13 @@
           <t>-68.8228</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="V127" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -15248,12 +15431,13 @@
           <t>-64.3268</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr">
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="V128" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -15357,6 +15541,7 @@
       </c>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15454,12 +15639,13 @@
           <t>-61.6328</t>
         </is>
       </c>
-      <c r="T130" t="inlineStr">
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="V130" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -15561,12 +15747,13 @@
           <t>-55.2913</t>
         </is>
       </c>
-      <c r="T131" t="inlineStr">
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="V131" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -15668,12 +15855,13 @@
           <t>-59.7513</t>
         </is>
       </c>
-      <c r="T132" t="inlineStr">
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="V132" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -15777,6 +15965,7 @@
       </c>
       <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -15874,12 +16063,13 @@
           <t>-70.4343</t>
         </is>
       </c>
-      <c r="T134" t="inlineStr">
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="V134" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -15981,12 +16171,13 @@
           <t>-69.4198</t>
         </is>
       </c>
-      <c r="T135" t="inlineStr">
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="V135" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -16088,12 +16279,13 @@
           <t>-60.4943</t>
         </is>
       </c>
-      <c r="T136" t="inlineStr">
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="V136" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -16197,6 +16389,7 @@
       </c>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -16294,12 +16487,13 @@
           <t>-70.0614</t>
         </is>
       </c>
-      <c r="T138" t="inlineStr">
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="V138" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -16401,12 +16595,13 @@
           <t>-65.3703</t>
         </is>
       </c>
-      <c r="T139" t="inlineStr">
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="V139" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -16508,12 +16703,13 @@
           <t>-87.4455</t>
         </is>
       </c>
-      <c r="T140" t="inlineStr">
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="V140" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -16617,6 +16813,7 @@
       </c>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -16716,10 +16913,15 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="V142" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -16823,10 +17025,15 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="V143" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -16930,10 +17137,15 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="V144" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -17035,8 +17247,13 @@
           <t>-62.3963</t>
         </is>
       </c>
-      <c r="T145" t="inlineStr"/>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -17136,10 +17353,15 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="V146" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -17241,12 +17463,13 @@
           <t>-53.0438</t>
         </is>
       </c>
-      <c r="T147" t="inlineStr">
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="V147" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -17348,12 +17571,13 @@
           <t>-44.6662</t>
         </is>
       </c>
-      <c r="T148" t="inlineStr">
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="V148" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -17457,6 +17681,7 @@
       </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -17554,12 +17779,13 @@
           <t>-67.7888</t>
         </is>
       </c>
-      <c r="T150" t="inlineStr">
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="V150" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -17661,12 +17887,13 @@
           <t>-67.1399</t>
         </is>
       </c>
-      <c r="T151" t="inlineStr">
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="V151" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -17768,12 +17995,13 @@
           <t>-55.1688</t>
         </is>
       </c>
-      <c r="T152" t="inlineStr">
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="V152" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -17877,6 +18105,7 @@
       </c>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -17974,12 +18203,13 @@
           <t>-71.1698</t>
         </is>
       </c>
-      <c r="T154" t="inlineStr">
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="V154" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -18081,12 +18311,13 @@
           <t>-73.5054</t>
         </is>
       </c>
-      <c r="T155" t="inlineStr">
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="V155" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -18188,12 +18419,13 @@
           <t>-61.4617</t>
         </is>
       </c>
-      <c r="T156" t="inlineStr">
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="V156" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -18297,6 +18529,7 @@
       </c>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -18394,12 +18627,13 @@
           <t>-71.6747</t>
         </is>
       </c>
-      <c r="T158" t="inlineStr">
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="V158" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -18501,12 +18735,13 @@
           <t>-64.4845</t>
         </is>
       </c>
-      <c r="T159" t="inlineStr">
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="V159" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -18608,12 +18843,13 @@
           <t>-49.798</t>
         </is>
       </c>
-      <c r="T160" t="inlineStr">
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="V160" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -18717,6 +18953,7 @@
       </c>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -18816,10 +19053,15 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="V162" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -18923,10 +19165,15 @@
       </c>
       <c r="T163" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="V163" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -19028,12 +19275,13 @@
           <t>-101.4784</t>
         </is>
       </c>
-      <c r="T164" t="inlineStr">
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="V164" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -19137,6 +19385,7 @@
       </c>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -19234,12 +19483,13 @@
           <t>-81.118</t>
         </is>
       </c>
-      <c r="T166" t="inlineStr">
+      <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="V166" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -19341,12 +19591,13 @@
           <t>-74.1098</t>
         </is>
       </c>
-      <c r="T167" t="inlineStr">
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="V167" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -19448,12 +19699,13 @@
           <t>-67.5047</t>
         </is>
       </c>
-      <c r="T168" t="inlineStr">
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="V168" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -19557,6 +19809,7 @@
       </c>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -19654,12 +19907,13 @@
           <t>-67.3355</t>
         </is>
       </c>
-      <c r="T170" t="inlineStr">
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="V170" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -19761,12 +20015,13 @@
           <t>-69.0819</t>
         </is>
       </c>
-      <c r="T171" t="inlineStr">
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="V171" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -19868,12 +20123,13 @@
           <t>-74.452</t>
         </is>
       </c>
-      <c r="T172" t="inlineStr">
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="V172" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -19977,6 +20233,7 @@
       </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -20074,12 +20331,13 @@
           <t>-59.6666</t>
         </is>
       </c>
-      <c r="T174" t="inlineStr">
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="V174" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -20181,12 +20439,13 @@
           <t>-43.4446</t>
         </is>
       </c>
-      <c r="T175" t="inlineStr">
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="V175" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -20288,12 +20547,13 @@
           <t>-33.0617</t>
         </is>
       </c>
-      <c r="T176" t="inlineStr">
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="V176" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -20397,6 +20657,7 @@
       </c>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -20494,12 +20755,13 @@
           <t>-22.7338</t>
         </is>
       </c>
-      <c r="T178" t="inlineStr">
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="V178" t="inlineStr">
         <is>
           <t>Q1_FS.xls</t>
         </is>
@@ -20601,12 +20863,13 @@
           <t>-21.3259</t>
         </is>
       </c>
-      <c r="T179" t="inlineStr">
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="V179" t="inlineStr">
         <is>
           <t>Q2_FS.xls</t>
         </is>
@@ -20708,12 +20971,13 @@
           <t>-22.7589</t>
         </is>
       </c>
-      <c r="T180" t="inlineStr">
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="V180" t="inlineStr">
         <is>
           <t>Q3_FS.xls</t>
         </is>
@@ -20817,6 +21081,7 @@
       </c>
       <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -20914,12 +21179,13 @@
           <t>-153.4896</t>
         </is>
       </c>
-      <c r="T182" t="inlineStr">
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="V182" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -21021,12 +21287,13 @@
           <t>-153.2134</t>
         </is>
       </c>
-      <c r="T183" t="inlineStr">
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="V183" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -21128,12 +21395,13 @@
           <t>-145.746</t>
         </is>
       </c>
-      <c r="T184" t="inlineStr">
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="V184" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -21237,6 +21505,7 @@
       </c>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -21334,12 +21603,13 @@
           <t>-95.8769</t>
         </is>
       </c>
-      <c r="T186" t="inlineStr">
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="V186" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -21441,12 +21711,13 @@
           <t>-77.4703</t>
         </is>
       </c>
-      <c r="T187" t="inlineStr">
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="V187" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -21548,12 +21819,13 @@
           <t>-69.6165</t>
         </is>
       </c>
-      <c r="T188" t="inlineStr">
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="V188" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -21657,6 +21929,7 @@
       </c>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -21754,12 +22027,13 @@
           <t>-74.0958</t>
         </is>
       </c>
-      <c r="T190" t="inlineStr">
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="V190" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -21861,12 +22135,13 @@
           <t>-74.623</t>
         </is>
       </c>
-      <c r="T191" t="inlineStr">
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="V191" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -21968,12 +22243,13 @@
           <t>-84.7506</t>
         </is>
       </c>
-      <c r="T192" t="inlineStr">
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="V192" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -22077,6 +22353,7 @@
       </c>
       <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -22174,12 +22451,13 @@
           <t>-119.0582</t>
         </is>
       </c>
-      <c r="T194" t="inlineStr">
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="V194" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -22281,12 +22559,13 @@
           <t>-141.9209</t>
         </is>
       </c>
-      <c r="T195" t="inlineStr">
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="V195" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -22388,12 +22667,13 @@
           <t>-150.6563</t>
         </is>
       </c>
-      <c r="T196" t="inlineStr">
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="V196" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -22497,6 +22777,7 @@
       </c>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -22594,12 +22875,13 @@
           <t>-147.4381</t>
         </is>
       </c>
-      <c r="T198" t="inlineStr">
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="V198" t="inlineStr">
         <is>
           <t>Q1_FS.xlsx</t>
         </is>
@@ -22701,12 +22983,13 @@
           <t>-124.1032</t>
         </is>
       </c>
-      <c r="T199" t="inlineStr">
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="V199" t="inlineStr">
         <is>
           <t>Q2_FS.xlsx</t>
         </is>
@@ -22808,12 +23091,13 @@
           <t>-94.0839</t>
         </is>
       </c>
-      <c r="T200" t="inlineStr">
+      <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="V200" t="inlineStr">
         <is>
           <t>Q3_FS.xlsx</t>
         </is>
@@ -22917,6 +23201,7 @@
       </c>
       <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -550,7 +550,7 @@
         <v>17.9</v>
       </c>
       <c r="I3" t="n">
-        <v>12.8</v>
+        <v>56.4</v>
       </c>
       <c r="J3" t="n">
         <v>0.75</v>
@@ -1055,10 +1055,10 @@
         <v>17.8</v>
       </c>
       <c r="D4" t="n">
-        <v>12.7</v>
+        <v>58.2</v>
       </c>
       <c r="E4" t="n">
-        <v>30.8</v>
+        <v>-14.7</v>
       </c>
       <c r="F4" t="n">
         <v>23.8</v>
@@ -1067,10 +1067,10 @@
         <v>17.9</v>
       </c>
       <c r="H4" t="n">
-        <v>12.8</v>
+        <v>56.4</v>
       </c>
       <c r="I4" t="n">
-        <v>28.9</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="5">
@@ -1423,13 +1423,13 @@
         <v>2566</v>
       </c>
       <c r="C4" t="n">
-        <v>44.8</v>
+        <v>49.8</v>
       </c>
       <c r="D4" t="n">
         <v>45.18</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4</v>
+        <v>4.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1495,13 +1495,13 @@
         <v>2566</v>
       </c>
       <c r="C7" t="n">
-        <v>-90.09999999999999</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="D7" t="n">
         <v>-104.02</v>
       </c>
       <c r="E7" t="n">
-        <v>13.9</v>
+        <v>18.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.226</t>
+          <t>103.5567</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1987,12 +1987,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>11.255</t>
+          <t>63.7345</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>90.3468</t>
+          <t>37.8673</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.1074</t>
+          <t>86.5767</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.1676</t>
+          <t>57.4638</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>104.9533</t>
+          <t>56.6571</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.5136</t>
+          <t>92.3838</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>10.6051</t>
+          <t>60.02</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>121.8953</t>
+          <t>72.4804</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.1313</t>
+          <t>82.438</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.3592</t>
+          <t>50.121</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>116.8573</t>
+          <t>76.0955</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16.5148</t>
+          <t>82.7726</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.5246</t>
+          <t>45.9555</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>84.9768</t>
+          <t>47.5459</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.6809</t>
+          <t>100.259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.6938</t>
+          <t>46.4519</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>71.5805</t>
+          <t>34.8223</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.0261</t>
+          <t>109.0545</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>10.4548</t>
+          <t>47.8776</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>18.9172</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24.9257</t>
+          <t>116.1073</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>10.941</t>
+          <t>50.3249</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>49.5479</t>
+          <t>10.164</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>27.178</t>
+          <t>125.4391</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>10.6664</t>
+          <t>49.4483</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>49.1502</t>
+          <t>10.3683</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.9274</t>
+          <t>118.8396</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2943,12 +2943,12 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>10.7569</t>
+          <t>50.4302</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>52.4888</t>
+          <t>12.8155</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.8009</t>
+          <t>118.1475</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>10.8526</t>
+          <t>48.777</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>50.1435</t>
+          <t>12.2191</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>27.1355</t>
+          <t>118.7525</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>11.8743</t>
+          <t>51.2052</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>49.5423</t>
+          <t>10.2114</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>29.7245</t>
+          <t>123.5575</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>11.6141</t>
+          <t>49.4938</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>41.324</t>
+          <t>3.4443</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28.1357</t>
+          <t>123.9741</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>11.844</t>
+          <t>50.67</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>41.7304</t>
+          <t>2.9044</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>34.2695</t>
+          <t>122.2089</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>11.8794</t>
+          <t>46.8634</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>36.1948</t>
+          <t>1.2108</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>33.1553</t>
+          <t>140.7969</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>13.0858</t>
+          <t>51.0442</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>31.8043</t>
+          <t>-6.154</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>122.0333</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>12.5444</t>
+          <t>50.7199</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>27.6284</t>
+          <t>-10.547</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28.0287</t>
+          <t>118.6004</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>11.6437</t>
+          <t>46.7922</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>30.5733</t>
+          <t>-4.5753</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>27.6193</t>
+          <t>119.9902</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>10.8187</t>
+          <t>46.3853</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>31.439</t>
+          <t>-4.1276</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>32.8516</t>
+          <t>150.3216</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>11.6477</t>
+          <t>52.0667</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>27.1333</t>
+          <t>-13.2856</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>12560.738</t>
+          <t>14721.379</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>88.3603</t>
+          <t>104.0029</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>-32.0722</t>
+          <t>-16.4296</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>12245.698</t>
+          <t>14396.577</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>71.2537</t>
+          <t>83.638</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>-39.4862</t>
+          <t>-27.1019</t>
         </is>
       </c>
       <c r="T103" t="inlineStr"/>
@@ -12817,7 +12817,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>14057.042</t>
+          <t>16127.792</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>58.1994</t>
+          <t>67.5404</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>-43.0169</t>
+          <t>-33.6759</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>14637.9953</t>
+          <t>16864.8165</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>49.0193</t>
+          <t>56.3608</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>-59.4125</t>
+          <t>-52.071</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>18889.532</t>
+          <t>20758.575</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>72.9838</t>
+          <t>81.8998</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>-30.0101</t>
+          <t>-21.0941</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>17198.61</t>
+          <t>19195.547</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>50.7602</t>
+          <t>56.198</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>-35.2856</t>
+          <t>-29.8479</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>18590.806</t>
+          <t>20887.878</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>46.8316</t>
+          <t>52.4504</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>-38.123</t>
+          <t>-32.5041</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -13349,7 +13349,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>17052.2687</t>
+          <t>19372.9974</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>45.5044</t>
+          <t>51.3997</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>-45.3917</t>
+          <t>-39.4963</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -13449,7 +13449,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>17614.873</t>
+          <t>20232.1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>48.4038</t>
+          <t>55.2984</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -13504,7 +13504,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>-44.3549</t>
+          <t>-37.4603</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>19429.147</t>
+          <t>21612.902</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>41.5268</t>
+          <t>46.9087</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>-46.2404</t>
+          <t>-40.8585</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>19843.861</t>
+          <t>22006.368</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>45.3444</t>
+          <t>50.3626</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>-47.723</t>
+          <t>-42.7048</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>18487.3486</t>
+          <t>20564.3268</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>43.6545</t>
+          <t>48.4827</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>-43.4101</t>
+          <t>-38.5819</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>

--- a/tour-finance/output/ratios_report.xlsx
+++ b/tour-finance/output/ratios_report.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -672,7 +672,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="G11" t="n">
